--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -487,16 +487,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -520,16 +512,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,16 +537,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -581,21 +557,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -619,16 +583,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -652,16 +608,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -685,16 +633,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -718,16 +658,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -751,16 +683,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -784,16 +708,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -812,21 +728,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -850,16 +754,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -883,16 +779,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -916,16 +804,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -949,16 +829,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -982,16 +854,8 @@
           <t>benz_running_program_2026​</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1015,16 +879,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1048,16 +904,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1081,16 +929,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1109,21 +949,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1142,21 +970,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1175,21 +991,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1208,32 +1012,20 @@
           <t>Paid Ad</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>303607</t>
+          <t>303585</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1241,32 +1033,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>kk_4829979824</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>303497</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1274,32 +1054,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>303644</t>
+          <t>303607</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1307,32 +1075,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>303663</t>
+          <t>303644</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1340,32 +1096,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_4829348219</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>303497</t>
+          <t>303468</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1373,32 +1117,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4829348219</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>303468</t>
+          <t>303576</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1406,32 +1138,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>303576</t>
+          <t>303663</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1439,21 +1159,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1472,21 +1180,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,50 +456,44 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>last_category</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>top_product</t>
+          <t>purchase_product_name</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kk_4831361074</t>
+          <t>kk_4830885654</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>303574</t>
+          <t>303562</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kk_4830254905</t>
+          <t>kk_4831895164</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>303513</t>
+          <t>303616</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -509,22 +503,21 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kk_4832204677</t>
+          <t>ydh1184</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>303653</t>
+          <t>303696</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -534,193 +527,189 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_4830885654</t>
+          <t>kk_4832961884</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>303562</t>
+          <t>303698</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_4831895164</t>
+          <t>kk_4832593419</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>303616</t>
+          <t>303677</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>kk_4831740520</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>303476</t>
+          <t>303601</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_4829818548</t>
+          <t>kk_4830523585</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>303491</t>
+          <t>303530</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_4831740520</t>
+          <t>kk_4833676515</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>303601</t>
+          <t>303738</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_4830523585</t>
+          <t>kk_4833576113</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>303530</t>
+          <t>303731</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_4830030364</t>
+          <t>kk_4832799612</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>303499</t>
+          <t>303686</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_4830247238</t>
+          <t>kk_4832659421</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>303510</t>
+          <t>303680</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -728,34 +717,36 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_4830591832</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>303539</t>
+          <t>303728</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -780,7 +771,6 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -805,18 +795,17 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kk_4832293158</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>303662</t>
+          <t>303761</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -830,18 +819,17 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kk_4832162309</t>
+          <t>kk_4832293158</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>303643</t>
+          <t>303662</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -851,160 +839,165 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_4831572710</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>303590</t>
+          <t>303747</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kda01126</t>
+          <t>kk_4833855255</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>303656</t>
+          <t>303757</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>masterk</t>
+          <t>kk_4832162309</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>303524</t>
+          <t>303643</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_4832411690</t>
+          <t>kk_4833840470</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>303666</t>
+          <t>303756</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026​</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_4832425261</t>
+          <t>kk_4830212469</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>303667</t>
+          <t>303509</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4832425669</t>
+          <t>kk_4833715500</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>303668</t>
+          <t>303745</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>naversa_mo</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_4832345614</t>
+          <t>masterk</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>303664</t>
+          <t>303524</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1012,20 +1005,23 @@
           <t>Paid Ad</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>sjjeon1928</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>303749</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1033,20 +1029,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>303497</t>
+          <t>303679</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1054,20 +1053,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>303607</t>
+          <t>303683</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1075,20 +1077,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4833682381</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>303644</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1096,20 +1101,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4829348219</t>
+          <t>whitehole147</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>303468</t>
+          <t>303673</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1117,20 +1125,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4833013784</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>303576</t>
+          <t>303703</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1138,20 +1149,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>303663</t>
+          <t>303750</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1159,20 +1173,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_4829294214</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>303466</t>
+          <t>303678</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1180,9 +1197,1308 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>arumabc</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>303689</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>kk_4832411690</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>303666</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>(organic)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>kk_4833617385</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>303734</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>kk_4833733292</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>303746</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>lily50</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>303714</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>kk_4832556634</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>303674</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>kk_4833397488</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>303723</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>kk_4833698569</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>303743</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>kk_4833115356</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>303707</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>dave1102</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>303697</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>kk_4832345614</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>303664</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>kk_4832562814</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>303675</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>kk_4833867742</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>303760</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>kk_4832564458</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>303676</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>kk_4832425261</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>303667</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>kk_4832735078</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>303682</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>kk_4832986577</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>303701</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>wngml5609</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>303704</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>kk_4832771015</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>303685</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ckddbs4958</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>303722</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>kk_4833234218</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>303711</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>kk_4833435690</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>303726</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>kk_4833215714</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>303709</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>kk_4832874454</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>303691</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>kk_4833692238</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>303741</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>[PF]전환_회원가입(유사)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>kk_4833915167</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>303764</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>[PF]트래픽_유사+관심사</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>kk_4833289287</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>303716</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>kk_4833588305</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>303733</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>kk_4833858368</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>303758</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>kk_4833937502</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>303767</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>kk_4832963009</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>303699</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>kk_4832497383</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>303669</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>kk_4833788564</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>303748</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026​</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>hlpt10</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>303715</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>kk_4832855902</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>303690</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>kk_4832804456</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>303687</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>kk_4832888908</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>303693</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>mystyle1999</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>303695</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>kk_4832527479</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>303672</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_pc</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>kk_4832745335</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>303684</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_pc</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>jinchoi24</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>303754</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_pc</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>kk_4832811973</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>303688</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>naversa_mo</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>kk_4833676329</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>303737</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>kk_4833836842</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>303753</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>hotsnoopy</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>303585</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>thdud9181</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>303644</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>kk_4831402433</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>303576</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>kk_4833961109</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>303770</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>kk_4833294708</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>303717</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>kk_4831784738</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>303607</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>kk_4833706874</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>303744</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>kk_4832310183</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>303663</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>kk_4833232918</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>303710</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>pjj1758</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>303708</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -799,13 +799,13 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kk_4833894015</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>303761</t>
+          <t>303747</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -847,13 +847,13 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_4833753902</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>303747</t>
+          <t>303761</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1039,13 +1039,13 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4832656308</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>303679</t>
+          <t>303678</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1063,13 +1063,13 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4832738942</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>303683</t>
+          <t>303679</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1087,13 +1087,13 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_4833682381</t>
+          <t>arumabc</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>303739</t>
+          <t>303689</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1111,13 +1111,13 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>whitehole147</t>
+          <t>kk_4833682381</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>303673</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1135,13 +1135,13 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4833013784</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>303703</t>
+          <t>303683</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1159,13 +1159,13 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4833797203</t>
+          <t>kk_4833013784</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>303750</t>
+          <t>303703</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1183,13 +1183,13 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_4832648970</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>303678</t>
+          <t>303750</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1207,13 +1207,13 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>arumabc</t>
+          <t>whitehole147</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>303689</t>
+          <t>303673</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1255,13 +1255,13 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4833617385</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>303734</t>
+          <t>303714</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1303,13 +1303,13 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>lily50</t>
+          <t>kk_4833617385</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>303714</t>
+          <t>303734</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1351,13 +1351,13 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_4833397488</t>
+          <t>kk_4832564458</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>303723</t>
+          <t>303676</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1375,13 +1375,13 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4833698569</t>
+          <t>kk_4833397488</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>303743</t>
+          <t>303723</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1399,13 +1399,13 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4833115356</t>
+          <t>kk_4833867742</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>303707</t>
+          <t>303760</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1447,13 +1447,13 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_4832345614</t>
+          <t>ckddbs4958</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>303664</t>
+          <t>303722</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1471,13 +1471,13 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4832562814</t>
+          <t>kk_4833115356</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>303675</t>
+          <t>303707</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1495,13 +1495,13 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4833867742</t>
+          <t>kk_4832735078</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>303760</t>
+          <t>303682</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1519,13 +1519,13 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4832564458</t>
+          <t>kk_4832986577</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>303676</t>
+          <t>303701</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1543,13 +1543,13 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_4832425261</t>
+          <t>kk_4833698569</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>303667</t>
+          <t>303743</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1567,13 +1567,13 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_4832735078</t>
+          <t>kk_4832345614</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>303682</t>
+          <t>303664</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1591,13 +1591,13 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4832986577</t>
+          <t>wngml5609</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>303701</t>
+          <t>303704</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1615,13 +1615,13 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>wngml5609</t>
+          <t>kk_4832425261</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>303704</t>
+          <t>303667</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1663,13 +1663,13 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ckddbs4958</t>
+          <t>kk_4832562814</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>303722</t>
+          <t>303675</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1687,13 +1687,13 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4833234218</t>
+          <t>kk_4832874454</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>303711</t>
+          <t>303691</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1759,13 +1759,13 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4832874454</t>
+          <t>kk_4833234218</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>303691</t>
+          <t>303711</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1831,13 +1831,13 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4833289287</t>
+          <t>kk_4833937502</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>303716</t>
+          <t>303767</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1855,13 +1855,13 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4833588305</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>303733</t>
+          <t>303716</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1879,13 +1879,13 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4833858368</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>303758</t>
+          <t>303669</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1903,13 +1903,13 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4833937502</t>
+          <t>kk_4833858368</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>303767</t>
+          <t>303758</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1951,13 +1951,13 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4832497383</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>303669</t>
+          <t>303733</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1999,13 +1999,13 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>hlpt10</t>
+          <t>kk_4832855902</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>303715</t>
+          <t>303690</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2023,13 +2023,13 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4832855902</t>
+          <t>kk_4832888908</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>303690</t>
+          <t>303693</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2071,13 +2071,13 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4832888908</t>
+          <t>mystyle1999</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>303693</t>
+          <t>303695</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2095,13 +2095,13 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>mystyle1999</t>
+          <t>hlpt10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>303695</t>
+          <t>303715</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2119,13 +2119,13 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4832527479</t>
+          <t>kk_4832745335</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>303672</t>
+          <t>303684</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2143,13 +2143,13 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4832745335</t>
+          <t>kk_4832527479</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>303684</t>
+          <t>303672</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2263,13 +2263,13 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>303576</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2287,13 +2287,13 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4833294708</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>303644</t>
+          <t>303717</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2311,13 +2311,13 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4833232918</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>303576</t>
+          <t>303710</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2335,13 +2335,13 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4833961109</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>303770</t>
+          <t>303663</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2359,13 +2359,13 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4833294708</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>303717</t>
+          <t>303644</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2383,13 +2383,13 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>pjj1758</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>303607</t>
+          <t>303708</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2407,13 +2407,13 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4833706874</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>303744</t>
+          <t>303607</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2431,13 +2431,13 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>303663</t>
+          <t>303585</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2455,13 +2455,13 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4833232918</t>
+          <t>kk_4833706874</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>303710</t>
+          <t>303744</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2479,13 +2479,13 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>pjj1758</t>
+          <t>kk_4833961109</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>303708</t>
+          <t>303770</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -593,17 +593,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_3182623010</t>
+          <t>kig0268</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01094128645</t>
+          <t>01053928207</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>227908</t>
+          <t>301007</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -613,24 +613,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kig0268</t>
+          <t>kk_3182623010</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01053928207</t>
+          <t>01094128645</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>301007</t>
+          <t>227908</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -640,61 +640,61 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_3789625265</t>
+          <t>kk_3407332090</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01029773942</t>
+          <t>01073480423</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>256664</t>
+          <t>241393</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_3407332090</t>
+          <t>kk_3789625265</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01073480423</t>
+          <t>01029773942</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>241393</t>
+          <t>256664</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -782,17 +782,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>joohpark87</t>
+          <t>kk_4507190107</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01062437622</t>
+          <t>01091780704</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>121373</t>
+          <t>285496</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kk_4507190107</t>
+          <t>joohpark87</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01091780704</t>
+          <t>01062437622</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>285496</t>
+          <t>121373</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -1160,17 +1160,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_2760596791</t>
+          <t>kk_3692762833</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01087827701</t>
+          <t>01087630523</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>208450</t>
+          <t>250938</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1180,24 +1180,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4226246986</t>
+          <t>kk_4291314607</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01048263393</t>
+          <t>01088119636</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>273085</t>
+          <t>275953</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1207,51 +1207,51 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_3692762833</t>
+          <t>gbk888</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01087630523</t>
+          <t>01063271523</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>250938</t>
+          <t>264430</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_2850432473</t>
+          <t>kk_2760596791</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01026771240</t>
+          <t>01087827701</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>213403</t>
+          <t>208450</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1261,105 +1261,105 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>namki9545</t>
+          <t>pkcomon</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01073099545</t>
+          <t>01063208976</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>27441</t>
+          <t>198932</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>jung9916</t>
+          <t>namki9545</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01091576210</t>
+          <t>01073099545</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>171554</t>
+          <t>27441</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pkcomon</t>
+          <t>kk_4226246986</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01063208976</t>
+          <t>01048263393</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>198932</t>
+          <t>273085</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4291314607</t>
+          <t>kk_3340113031</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01088119636</t>
+          <t>01098338138</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>275953</t>
+          <t>239100</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
@@ -1403,44 +1403,44 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>darius27</t>
+          <t>jung9916</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01091911224</t>
+          <t>01091576210</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>292238</t>
+          <t>171554</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_3340113031</t>
+          <t>kk_2850432473</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01098338138</t>
+          <t>01026771240</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>239100</t>
+          <t>213403</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1450,34 +1450,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gbk888</t>
+          <t>darius27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01063271523</t>
+          <t>01091911224</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>264430</t>
+          <t>292238</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -1511,44 +1511,44 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_3241814751</t>
+          <t>kk_4278011504</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01048808215</t>
+          <t>01045289321</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>234712</t>
+          <t>275167</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>djmin57</t>
+          <t>juhan3489</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01034585986</t>
+          <t>01037693092</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>52890</t>
+          <t>214043</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1558,24 +1558,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_3097460767</t>
+          <t>aram2016</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01048597145</t>
+          <t>01071670785</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>221400</t>
+          <t>225250</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1585,24 +1585,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4694268987</t>
+          <t>kk_3793101024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01025088964</t>
+          <t>01082844287</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>295680</t>
+          <t>257080</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1612,24 +1612,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4790899014</t>
+          <t>kk_4838420487</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01024708415</t>
+          <t>01050618241</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>302058</t>
+          <t>304051</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1639,51 +1639,51 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4201661917</t>
+          <t>kk_4743669054</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01052228247</t>
+          <t>01036749627</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>271984</t>
+          <t>300361</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>aram2016</t>
+          <t>kk_2762251625</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01071670785</t>
+          <t>01032085585</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>225250</t>
+          <t>208548</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1693,51 +1693,51 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_3795564177</t>
+          <t>stonehinge</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01044552859</t>
+          <t>01027275105</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>257673</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>lms_ecom_0401_springhiking</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4838420487</t>
+          <t>kk_3097460767</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01050618241</t>
+          <t>01048597145</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>304051</t>
+          <t>221400</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1747,105 +1747,105 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_4837990320</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01085815097</t>
+          <t>01024175652</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>303542</t>
+          <t>304030</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>juhan3489</t>
+          <t>kk_3795564177</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01037693092</t>
+          <t>01044552859</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>214043</t>
+          <t>257673</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4828047673</t>
+          <t>kk_4746910410</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01087502319</t>
+          <t>01047502488</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>303388</t>
+          <t>300629</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4746910410</t>
+          <t>kk_4201661917</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01047502488</t>
+          <t>01052228247</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>300629</t>
+          <t>271984</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1855,24 +1855,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4509280340</t>
+          <t>leecs11124</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01088521558</t>
+          <t>01037870639</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>285569</t>
+          <t>260560</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1882,24 +1882,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0214</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_3793101024</t>
+          <t>kk_4509280340</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01082844287</t>
+          <t>01088521558</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>257080</t>
+          <t>285569</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1909,105 +1909,105 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4743669054</t>
+          <t>kk_3241814751</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01036749627</t>
+          <t>01048808215</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>300361</t>
+          <t>234712</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4278011504</t>
+          <t>djmin57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01045289321</t>
+          <t>01034585986</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>275167</t>
+          <t>52890</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>leecs11124</t>
+          <t>kk_4828047673</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01037870639</t>
+          <t>01087502319</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>260560</t>
+          <t>303388</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>stonehinge</t>
+          <t>kk_3827025148</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01027275105</t>
+          <t>01090399900</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>263356</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2017,24 +2017,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>lms_ecom_0401_springhiking</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_2762251625</t>
+          <t>kk_2783594999</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01032085585</t>
+          <t>01095317357</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>208548</t>
+          <t>209807</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2044,24 +2044,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_2783594999</t>
+          <t>kk_4790899014</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01095317357</t>
+          <t>01024708415</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>209807</t>
+          <t>302058</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2071,159 +2071,159 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4837990320</t>
+          <t>kk_4694268987</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01024175652</t>
+          <t>01025088964</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>304030</t>
+          <t>295680</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_3827025148</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01090399900</t>
+          <t>01085815097</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>263356</t>
+          <t>303542</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4833493849</t>
+          <t>kk_3778874557</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01083936762</t>
+          <t>01094017193</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>303728</t>
+          <t>256071</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4299847976</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01091384892</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>276488</t>
+          <t>168147</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ssbok0806</t>
+          <t>kk_3967220863</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01093267531</t>
+          <t>01087902066</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>223278</t>
+          <t>270700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_3707105860</t>
+          <t>ssbok0806</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01059290508</t>
+          <t>01093267531</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>251625</t>
+          <t>223278</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2233,51 +2233,51 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4285105163</t>
+          <t>p7181</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01083283220</t>
+          <t>01056288360</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>275559</t>
+          <t>250858</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>6941110100332</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>endruns</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01020716852</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>168147</t>
+          <t>176346</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2287,78 +2287,78 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_3727979047</t>
+          <t>cgkrry</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01079273404</t>
+          <t>01085513271</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>252685</t>
+          <t>48578</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4793026063</t>
+          <t>kk_4285105163</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01072703070</t>
+          <t>01083283220</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>302125</t>
+          <t>275559</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>cgkrry</t>
+          <t>jcahn12</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01085513271</t>
+          <t>01038358052</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>48578</t>
+          <t>59346</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2368,34 +2368,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>joocho629</t>
+          <t>kk_3707105860</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01038056919</t>
+          <t>01059290508</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>162948</t>
+          <t>251625</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>EDM_0224</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -2429,17 +2429,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_3734181513</t>
+          <t>kk_3186268807</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01066389021</t>
+          <t>01055175130</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>253177</t>
+          <t>230244</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2449,51 +2449,51 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_3967220863</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01087902066</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>270700</t>
+          <t>244619</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>klim202</t>
+          <t>joocho629</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01064368836</t>
+          <t>01038056919</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>168762</t>
+          <t>162948</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2503,51 +2503,51 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>EDM_0224</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4817738509</t>
+          <t>kk_4793026063</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01085325672</t>
+          <t>01072703070</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>302840</t>
+          <t>302125</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_3727979047</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01079273404</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>252685</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2557,78 +2557,78 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_3778874557</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01094017193</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>256071</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>endruns</t>
+          <t>klim202</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01020716852</t>
+          <t>01064368836</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>176346</t>
+          <t>168762</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_3290809343</t>
+          <t>kk_3734181513</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01057206001</t>
+          <t>01066389021</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>237059</t>
+          <t>253177</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2638,78 +2638,78 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_3203549435</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01033608209</t>
+          <t>01083936762</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>230719</t>
+          <t>303728</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_4837763007</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01088993992</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>304013</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_3866200904</t>
+          <t>kk_3203549435</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01062556776</t>
+          <t>01033608209</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>265988</t>
+          <t>230719</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2719,51 +2719,51 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>jcahn12</t>
+          <t>kk_4817738509</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01038358052</t>
+          <t>01085325672</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>59346</t>
+          <t>302840</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4837763007</t>
+          <t>kk_4299847976</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01088993992</t>
+          <t>01091384892</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>304013</t>
+          <t>276488</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2773,51 +2773,51 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>p7181</t>
+          <t>kk_3866200904</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01056288360</t>
+          <t>01062556776</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>250858</t>
+          <t>265988</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_3229351319</t>
+          <t>kk_3290809343</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01090969959</t>
+          <t>01057206001</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>233446</t>
+          <t>237059</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2827,78 +2827,78 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>abejung</t>
+          <t>kk_3229351319</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01023320007</t>
+          <t>01090969959</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>158025</t>
+          <t>233446</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_3186268807</t>
+          <t>abejung</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01055175130</t>
+          <t>01023320007</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>230244</t>
+          <t>158025</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>jeshurun76</t>
+          <t>scubaktk</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01051236012</t>
+          <t>01028951833</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>191849</t>
+          <t>51328</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2908,78 +2908,78 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_2975660270</t>
+          <t>wlcnstjs12</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01065565496</t>
+          <t>01040240293</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>217640</t>
+          <t>149195</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_3456892694</t>
+          <t>kk_4508257846</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01057443264</t>
+          <t>01092499867</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>243269</t>
+          <t>285541</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>gilinim</t>
+          <t>kk_3774156950</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01032351966</t>
+          <t>01041159966</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>302594</t>
+          <t>255778</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2989,24 +2989,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>optimal11</t>
+          <t>godo2027</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01083258827</t>
+          <t>01075835624</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>129148</t>
+          <t>179139</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3016,56 +3016,56 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>wlcnstjs12</t>
+          <t>tinykim</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01040240293</t>
+          <t>01035630719</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>149195</t>
+          <t>65922</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_3795672557</t>
+          <t>chelius</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01091179346</t>
+          <t>01024880126</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>257697</t>
+          <t>300985</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3077,17 +3077,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4443559736</t>
+          <t>kk_4839929131</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01064021269</t>
+          <t>01044408612</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>282199</t>
+          <t>304116</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3097,78 +3097,78 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>EDM_0331</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4838385004</t>
+          <t>kk_4443559736</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01088158446</t>
+          <t>01064021269</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>304048</t>
+          <t>282199</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>EDM_0331</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4475486602</t>
+          <t>goppagi</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01041949661</t>
+          <t>01052632529</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>284059</t>
+          <t>179049</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4839929131</t>
+          <t>kmhjm</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01044408612</t>
+          <t>01095316235</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>304116</t>
+          <t>181953</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3178,105 +3178,105 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>plus7431</t>
+          <t>jinny6716</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01084748664</t>
+          <t>01039376458</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>251388</t>
+          <t>95121</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4525960790</t>
+          <t>kk_4440711181</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01084170327</t>
+          <t>01063263543</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>286541</t>
+          <t>282110</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_3943654079</t>
+          <t>kbh2639</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01053762357</t>
+          <t>01026514411</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>269510</t>
+          <t>159679</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4217088689</t>
+          <t>jeshurun76</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01077710204</t>
+          <t>01051236012</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>272648</t>
+          <t>191849</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3286,83 +3286,83 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4755147673</t>
+          <t>junghyunpak</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01062968675</t>
+          <t>01028120688</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>301054</t>
+          <t>58618</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>scp0103</t>
+          <t>kk_3795672557</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01033083314</t>
+          <t>01091179346</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>214558</t>
+          <t>257697</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>haein607</t>
+          <t>kk_4755147673</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01023369606</t>
+          <t>01062968675</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>151209</t>
+          <t>301054</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3374,44 +3374,44 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>chunsadl</t>
+          <t>kk_4475486602</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01087804011</t>
+          <t>01041949661</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>167610</t>
+          <t>284059</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_3246970011</t>
+          <t>kk_4217088689</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01080703392</t>
+          <t>01077710204</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>235053</t>
+          <t>272648</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3421,51 +3421,51 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>godo2027</t>
+          <t>comic0828</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01075835624</t>
+          <t>01096390888</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>179139</t>
+          <t>140326</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>luvsena</t>
+          <t>gilinim</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01089625349</t>
+          <t>01032351966</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>172100</t>
+          <t>302594</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3475,24 +3475,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ferix1999</t>
+          <t>kk_4828776483</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01026339659</t>
+          <t>01092690887</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>191848</t>
+          <t>303428</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3502,51 +3502,51 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>kk_3898041727</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01092690887</t>
+          <t>01091030227</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>303428</t>
+          <t>267643</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_3901736373</t>
+          <t>kk_4282126610</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01072562998</t>
+          <t>01037415807</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>267789</t>
+          <t>275374</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3556,105 +3556,105 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>scubaktk</t>
+          <t>kk_4838385004</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01028951833</t>
+          <t>01088158446</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>51328</t>
+          <t>304048</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_3898041727</t>
+          <t>kk_3901736373</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01091030227</t>
+          <t>01072562998</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>267643</t>
+          <t>267789</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>goppagi</t>
+          <t>kk_3943654079</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01052632529</t>
+          <t>01053762357</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>179049</t>
+          <t>269510</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>junghyunpak</t>
+          <t>hansoi93</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01028120688</t>
+          <t>01072262346</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>58618</t>
+          <t>60217</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3664,24 +3664,24 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4634804186</t>
+          <t>kk_4610571768</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01089506651</t>
+          <t>01094092580</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>292029</t>
+          <t>290026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3691,78 +3691,78 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4282126610</t>
+          <t>luvsena</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01037415807</t>
+          <t>01089625349</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>275374</t>
+          <t>172100</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>chelius</t>
+          <t>kk_2975660270</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01024880126</t>
+          <t>01065565496</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>300985</t>
+          <t>217640</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4288079130</t>
+          <t>ferix1999</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01056697298</t>
+          <t>01026339659</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>275750</t>
+          <t>191848</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3772,105 +3772,105 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4508257846</t>
+          <t>kk_4310987668</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01092499867</t>
+          <t>01027962045</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>285541</t>
+          <t>277132</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kbh2639</t>
+          <t>kk_3801427305</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01026514411</t>
+          <t>01097820998</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>159679</t>
+          <t>259073</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_4310987668</t>
+          <t>kk_4634804186</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01027962045</t>
+          <t>01089506651</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>277132</t>
+          <t>292029</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_3825294168</t>
+          <t>plus7431</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01076290208</t>
+          <t>01084748664</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>263146</t>
+          <t>251388</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3880,24 +3880,24 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kmhjm</t>
+          <t>ko7417</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01095316235</t>
+          <t>01041821439</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>181953</t>
+          <t>21776</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3907,34 +3907,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>comic0828</t>
+          <t>haein607</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01096390888</t>
+          <t>01023369606</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>140326</t>
+          <t>151209</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -3968,71 +3968,71 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_3774156950</t>
+          <t>kk_3456892694</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01041159966</t>
+          <t>01057443264</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>255778</t>
+          <t>243269</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4440711181</t>
+          <t>kk_3825294168</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01063263543</t>
+          <t>01076290208</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>282110</t>
+          <t>263146</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>tinykim</t>
+          <t>optimal11</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01035630719</t>
+          <t>01083258827</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>65922</t>
+          <t>129148</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4042,24 +4042,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>jinny6716</t>
+          <t>delta12</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01039376458</t>
+          <t>01071339709</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>95121</t>
+          <t>192352</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4076,125 +4076,125 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ko7417</t>
+          <t>scp0103</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01041821439</t>
+          <t>01033083314</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>21776</t>
+          <t>214558</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>delta12</t>
+          <t>kk_4525960790</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01071339709</t>
+          <t>01084170327</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>192352</t>
+          <t>286541</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_3718281230</t>
+          <t>kk_3246970011</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01067711528</t>
+          <t>01080703392</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>252078</t>
+          <t>235053</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>hansoi93</t>
+          <t>kk_4288079130</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01072262346</t>
+          <t>01056697298</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>60217</t>
+          <t>275750</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_3801427305</t>
+          <t>kk_3718281230</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01097820998</t>
+          <t>01067711528</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>259073</t>
+          <t>252078</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4211,17 +4211,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4610571768</t>
+          <t>chunsadl</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01094092580</t>
+          <t>01087804011</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>290026</t>
+          <t>167610</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4238,17 +4238,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>pkd2001</t>
+          <t>kk_3736097865</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01043345927</t>
+          <t>01089447248</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>169815</t>
+          <t>253356</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4258,24 +4258,24 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>water4853</t>
+          <t>kk_4212123801</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01020542351</t>
+          <t>01083862682</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>178866</t>
+          <t>272414</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -4319,44 +4319,44 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_3601774804</t>
+          <t>kslee9011</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01046513357</t>
+          <t>01031716463</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>247059</t>
+          <t>48237</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>tkfkdtmfjs79</t>
+          <t>kimchhgood</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01044809033</t>
+          <t>01092133961</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>153239</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4366,51 +4366,51 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4612713787</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01095027601</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>290278</t>
+          <t>287573</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_2989316682</t>
+          <t>kk_3601774804</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01037375641</t>
+          <t>01046513357</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>218263</t>
+          <t>247059</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4420,78 +4420,78 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>lynx246</t>
+          <t>kk_3775794718</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01041241323</t>
+          <t>01085983536</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>196113</t>
+          <t>255860</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_4464127061</t>
+          <t>kk_3631606950</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01073655835</t>
+          <t>01063256163</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>283300</t>
+          <t>248164</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>eccomi21</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01084717525</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>164951</t>
+          <t>143557</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4501,159 +4501,159 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_3694865986</t>
+          <t>kkemc11</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01083470708</t>
+          <t>01072822359</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>251070</t>
+          <t>224851</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4835837819</t>
+          <t>kk_3798545067</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01044119822</t>
+          <t>01023751319</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>303896</t>
+          <t>258449</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4672701053</t>
+          <t>kk_3766082784</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01088807653</t>
+          <t>01092342302</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>294426</t>
+          <t>255139</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>soojst</t>
+          <t>fimajun</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01097431003</t>
+          <t>01035668051</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>209447</t>
+          <t>230171</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_3776403631</t>
+          <t>kk_4835267037</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01034755755</t>
+          <t>01047143494</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>255908</t>
+          <t>303847</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_3798545067</t>
+          <t>anirim</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01023751319</t>
+          <t>01026146239</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>258449</t>
+          <t>303897</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4670,44 +4670,44 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4530117802</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01094437239</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>286792</t>
+          <t>280163</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_3736097865</t>
+          <t>kk_3258483317</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01089447248</t>
+          <t>01075584654</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>253356</t>
+          <t>235788</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4717,24 +4717,24 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>kk_4838748515</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01034435700</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>303885</t>
+          <t>304070</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4744,78 +4744,78 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4835826103</t>
+          <t>water4853</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01082133090</t>
+          <t>01020542351</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>303894</t>
+          <t>178866</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>fimajun</t>
+          <t>csnoopy</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01035668051</t>
+          <t>01063730741</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>230171</t>
+          <t>110007</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>eccomi21</t>
+          <t>kk_3804201157</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01084717525</t>
+          <t>01055152547</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>143557</t>
+          <t>259728</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4825,213 +4825,213 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>colorum</t>
+          <t>kk_4838514193</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01054844416</t>
+          <t>01028513978</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>146276</t>
+          <t>304057</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_3766082784</t>
+          <t>jth0122</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01092342302</t>
+          <t>01088989856</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>255139</t>
+          <t>96490</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>jth0122</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01088989856</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>96490</t>
+          <t>304107</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kslee9011</t>
+          <t>kk_3465759734</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01031716463</t>
+          <t>01045550499</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>48237</t>
+          <t>243732</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_3793412568</t>
+          <t>kk_4819536073</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01049200546</t>
+          <t>01039113089</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>257211</t>
+          <t>302942</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_4835267037</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01047143494</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>303847</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>anirim</t>
+          <t>kk_2989316682</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01026146239</t>
+          <t>01037375641</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>303897</t>
+          <t>218263</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_3258483317</t>
+          <t>whtjdfo11</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01075584654</t>
+          <t>01075377523</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>235788</t>
+          <t>185516</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5041,56 +5041,56 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>tomcurse02</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01022070282</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>280163</t>
+          <t>96444</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>csnoopy</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01063730741</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>110007</t>
+          <t>304098</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5102,17 +5102,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_3804201157</t>
+          <t>kk_4720019874</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01055152547</t>
+          <t>01052578634</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>259728</t>
+          <t>297465</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5122,105 +5122,105 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>jment1983</t>
+          <t>kk_4703414773</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01088991983</t>
+          <t>01093547510</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>271329</t>
+          <t>296108</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>ohey2003</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01034151656</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>116157</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>myjjangga</t>
+          <t>kk_4681484279</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01083364898</t>
+          <t>01022642776</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>87940</t>
+          <t>294947</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>raneelim</t>
+          <t>hjh3127</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01051598929</t>
+          <t>01054261891</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>72197</t>
+          <t>52538</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5230,51 +5230,51 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kk_4838635909</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01098131007</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>304064</t>
+          <t>164951</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kimchhgood</t>
+          <t>kk_4835837819</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01092133961</t>
+          <t>01044119822</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>303896</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5284,24 +5284,24 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_3776403631</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01034755755</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>255908</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5318,17 +5318,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kkemc11</t>
+          <t>kk_4530117802</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01072822359</t>
+          <t>01094437239</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>224851</t>
+          <t>286792</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5345,17 +5345,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4222073058</t>
+          <t>kk_4672701053</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01046077586</t>
+          <t>01088807653</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>272870</t>
+          <t>294426</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5365,24 +5365,24 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4825242022</t>
+          <t>kk_4612713787</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01025208267</t>
+          <t>01095027601</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>303235</t>
+          <t>290278</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5392,78 +5392,78 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_3913679442</t>
+          <t>lynx246</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01085569215</t>
+          <t>01041241323</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>268330</t>
+          <t>196113</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_4681484279</t>
+          <t>jment1983</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01022642776</t>
+          <t>01088991983</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>294947</t>
+          <t>271329</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_3465759734</t>
+          <t>raneelim</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01045550499</t>
+          <t>01051598929</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>243732</t>
+          <t>72197</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5473,24 +5473,24 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_4446020087</t>
+          <t>myjjangga</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01089773053</t>
+          <t>01083364898</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>282273</t>
+          <t>87940</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5500,51 +5500,51 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>whtjdfo11</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01075377523</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>185516</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>kk_4703414773</t>
+          <t>kk_4446020087</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01093547510</t>
+          <t>01089773053</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>296108</t>
+          <t>282273</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5554,294 +5554,294 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ohey2003</t>
+          <t>kk_4839598883</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01034151656</t>
+          <t>01032207906</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>116157</t>
+          <t>304105</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kk_4478716748</t>
+          <t>colorum</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01071630157</t>
+          <t>01054844416</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>284194</t>
+          <t>146276</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kk_4838646680</t>
+          <t>soojst</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01034311248</t>
+          <t>01097431003</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>304066</t>
+          <t>209447</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>[pf]트래픽_유사+관심사</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>kk_4839598883</t>
+          <t>kk_3694865986</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01032207906</t>
+          <t>01083470708</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>304105</t>
+          <t>251070</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>kk_4838514193</t>
+          <t>kk_2999650964</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01028513978</t>
+          <t>01073667501</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>304057</t>
+          <t>218535</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>bizboard</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>kk_4819536073</t>
+          <t>kk_4825242022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01039113089</t>
+          <t>01025208267</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>302942</t>
+          <t>303235</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>kk_3631606950</t>
+          <t>kk_3793412568</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01063256163</t>
+          <t>01049200546</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>248164</t>
+          <t>257211</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kk_3913679442</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01085569215</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>304107</t>
+          <t>268330</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kiraeo</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01085072563</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>195029</t>
+          <t>303885</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>hjh3127</t>
+          <t>kk_4835826103</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01054261891</t>
+          <t>01082133090</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>52538</t>
+          <t>303894</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kk_2999650964</t>
+          <t>kk_4838646680</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01073667501</t>
+          <t>01034311248</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>218535</t>
+          <t>304066</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>[pf]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>tomcurse02</t>
+          <t>kk_3633964155</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01022070282</t>
+          <t>01097743709</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>96444</t>
+          <t>248300</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5878,51 +5878,51 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>kk_4720019874</t>
+          <t>kk_4838635909</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01052578634</t>
+          <t>01098131007</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>297465</t>
+          <t>304064</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>kk_3633964155</t>
+          <t>kiraeo</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01097743709</t>
+          <t>01085072563</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>248300</t>
+          <t>195029</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5932,51 +5932,51 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>tkfkdtmfjs79</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01044809033</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>304098</t>
+          <t>153239</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>kk_4212123801</t>
+          <t>pkd2001</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01083862682</t>
+          <t>01043345927</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>272414</t>
+          <t>169815</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5986,105 +5986,105 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>kk_4344215691</t>
+          <t>kk_4478716748</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01020192399</t>
+          <t>01071630157</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>279044</t>
+          <t>284194</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4222073058</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01046077586</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>287573</t>
+          <t>272870</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_4838748515</t>
+          <t>kk_4344215691</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01034435700</t>
+          <t>01020192399</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>304070</t>
+          <t>279044</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kk_3775794718</t>
+          <t>kk_4464127061</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01085983536</t>
+          <t>01073655835</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>255860</t>
+          <t>283300</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6094,24 +6094,24 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6128,17 +6128,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>hhpp123</t>
+          <t>kk_4538201048</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01042621121</t>
+          <t>01071790372</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>294450</t>
+          <t>287217</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6155,17 +6155,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kk_4484370599</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01052246899</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>284447</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6182,125 +6182,125 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>kk_4212258541</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01047138543</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>268974</t>
+          <t>272420</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>kk_4838947856</t>
+          <t>kk_3220401027</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>01094709458</t>
+          <t>01037591063</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>304075</t>
+          <t>232602</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>EDM_0413</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>jeonhyel</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>01077942894</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>304102</t>
+          <t>304101</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>kk_4357899204</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01082772838</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>219219</t>
+          <t>279564</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>279909</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6317,44 +6317,44 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>kyong74</t>
+          <t>kk_4838947856</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>01088245591</t>
+          <t>01094709458</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>22857</t>
+          <t>304075</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>229454</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6371,44 +6371,44 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>kk_4221652535</t>
+          <t>kk_3380246984</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>01036858276</t>
+          <t>01040750851</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>272849</t>
+          <t>240492</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>221630</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6425,44 +6425,44 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>kk_4288273717</t>
+          <t>kk_3170564464</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>01020746624</t>
+          <t>01099188001</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>275762</t>
+          <t>224948</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>kk_2950194486</t>
+          <t>kk_2915134680</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>01076104875</t>
+          <t>01085224711</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>216766</t>
+          <t>215670</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6472,24 +6472,24 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>kk_4375333989</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>01091513985</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>280145</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6499,78 +6499,78 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>kk_3170564464</t>
+          <t>kk_3960572616</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>01099188001</t>
+          <t>01072737379</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>224948</t>
+          <t>270384</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>kk_4840198421</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>01053706365</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>304132</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>kk_4727505000</t>
+          <t>he0218</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>01066573797</t>
+          <t>01049289998</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>298110</t>
+          <t>254710</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6580,24 +6580,24 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>hodong1014</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01044530048</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>64397</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6607,51 +6607,51 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>richjm</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>01082909799</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>122482</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>232010</t>
+          <t>219525</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -6661,24 +6661,24 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>304126</t>
+          <t>304100</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -6688,24 +6688,24 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6722,179 +6722,179 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>kk_4212258541</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>01047138543</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>272420</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>304100</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>kk_4839821563</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01027951809</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>304101</t>
+          <t>304112</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>136050</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>68751</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>140860</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>jsu2080</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>01094582080</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>275256</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6911,125 +6911,125 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>227343</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>kk_4237700483</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01063041087</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>292319</t>
+          <t>273719</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>chlwoghk83</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>01038851983</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>145712</t>
+          <t>123130</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>mooner82</t>
+          <t>kk_3466706406</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>01037861045</t>
+          <t>01055441553</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>148696</t>
+          <t>243779</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>268974</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -7039,105 +7039,105 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>maksim04</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01063557978</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>202013</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>coverdn</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>01086426866</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>172406</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -7154,44 +7154,44 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>kk_4670878863</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>01067207833</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>294326</t>
+          <t>292319</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>304129</t>
+          <t>219219</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -7208,17 +7208,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -7235,98 +7235,98 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>chlwoghk83</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01038851983</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>145712</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>kk_3501053454</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>01093015628</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>245323</t>
+          <t>304126</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>kk_3466706406</t>
+          <t>kk_4839542021</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>01055441553</t>
+          <t>01089909663</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>243779</t>
+          <t>304103</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>kk_2950194486</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01076104875</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>216766</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -7343,17 +7343,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>136050</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7370,44 +7370,44 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>kwon9493</t>
+          <t>kk_4838920250</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>01035589493</t>
+          <t>01065688860</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>304074</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>kk_4840174486</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>01064087457</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>304131</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -7417,24 +7417,24 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>fjsjhw</t>
+          <t>kk_3794951359</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>01050468291</t>
+          <t>01066481842</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>192240</t>
+          <t>257520</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -7444,24 +7444,24 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>chaser1</t>
+          <t>jsu2080</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>01038304145</t>
+          <t>01094582080</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>178090</t>
+          <t>275256</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -7478,17 +7478,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>143826</t>
+          <t>270708</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -7498,51 +7498,51 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>hodong1014</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>01044530048</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>64397</t>
+          <t>304129</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>270708</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7552,105 +7552,105 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>kk_4375333989</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01091513985</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>280145</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>kk_4517851709</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01066445714</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>286074</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>221630</t>
+          <t>275998</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>varam11</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>01071373327</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>102004</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7660,24 +7660,24 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>kk_4536846819</t>
+          <t>coverdn</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>01038223781</t>
+          <t>01086426866</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>287146</t>
+          <t>172406</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7687,24 +7687,24 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0413</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>174291</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7721,44 +7721,44 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>kk_4839283126</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01024419045</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>304093</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>kk_3501053454</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01093015628</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>245323</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -7768,24 +7768,24 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>kk_3750120343</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01092908890</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>285491</t>
+          <t>254168</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -7795,24 +7795,24 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7829,179 +7829,179 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>kk_4839027252</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>01084518813</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>304083</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>kk_4839765445</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01076118972</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>219525</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>kk_3134493871</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01035918800</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>222420</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>304086</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>kk_4840198421</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01053706365</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>304132</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>motamsi</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01090344665</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>96716</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>he0218</t>
+          <t>varam11</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>01049289998</t>
+          <t>01071373327</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>254710</t>
+          <t>102004</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -8011,24 +8011,24 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>EDM_0413</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>kk_3678962368</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01041028567</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>229454</t>
+          <t>250374</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8045,71 +8045,71 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>js0987</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>01052819790</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>110955</t>
+          <t>186218</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>208245</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>kk_4680971786</t>
+          <t>hhpp123</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>01074443726</t>
+          <t>01042621121</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>294917</t>
+          <t>294450</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8126,44 +8126,44 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>seopme</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>01074122238</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>304125</t>
+          <t>174291</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>123130</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8173,24 +8173,24 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8207,179 +8207,179 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>kk_4839765445</t>
+          <t>fjsjhw</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>01076118972</t>
+          <t>01050468291</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>304111</t>
+          <t>192240</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>kk_4221652535</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01036858276</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>272849</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>kk_3134493871</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>01035918800</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>222420</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>ganjing78</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01065121424</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>78590</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>kk_4357899204</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>01082772838</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>279564</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>kk_4212157104</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01062437191</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>180321</t>
+          <t>272417</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>kk_4838920250</t>
+          <t>seopme</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>01065688860</t>
+          <t>01074122238</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>304074</t>
+          <t>304125</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8389,24 +8389,24 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>kk_3750120343</t>
+          <t>jinoh</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>01092908890</t>
+          <t>01024150539</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>254168</t>
+          <t>270445</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8423,44 +8423,44 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>kwon9493</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01035589493</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>107077</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>jinoh</t>
+          <t>byun7707</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>01024150539</t>
+          <t>01077391740</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>270445</t>
+          <t>161371</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8470,24 +8470,24 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>279909</t>
+          <t>140860</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -8504,17 +8504,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>kk_4727505000</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01066573797</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>298110</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8524,51 +8524,51 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>kk_4237700483</t>
+          <t>kyong74</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>01063041087</t>
+          <t>01088245591</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>273719</t>
+          <t>22857</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>kk_4517851709</t>
+          <t>kk_4680971786</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>01066445714</t>
+          <t>01074443726</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>286074</t>
+          <t>294917</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8585,17 +8585,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>kk_3380246984</t>
+          <t>kk_4536846819</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>01040750851</t>
+          <t>01038223781</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>240492</t>
+          <t>287146</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8612,17 +8612,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>kk_4839542021</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>01089909663</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>304103</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8632,51 +8632,51 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>kk_4839821563</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>01027951809</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>304112</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8693,17 +8693,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>162562</t>
+          <t>285491</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8713,24 +8713,24 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8747,206 +8747,206 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>isaackwak</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01090599860</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>275913</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>kk_4670878863</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01067207833</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>304124</t>
+          <t>294326</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>kk_2915134680</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>01085224711</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>215670</t>
+          <t>304086</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>kk_4839241951</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>01079146776</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>304090</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>kk_4288273717</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01020746624</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>304104</t>
+          <t>275762</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>richjm</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01082909799</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>122482</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>304109</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>kk_3796517297</t>
+          <t>chaser1</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>01040802850</t>
+          <t>01038304145</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>257878</t>
+          <t>178090</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8963,44 +8963,44 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>jung1481</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>01024193371</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>205735</t>
+          <t>68751</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9010,24 +9010,24 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>kk_3220401027</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>01037591063</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>232602</t>
+          <t>143826</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9037,213 +9037,213 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>kk_3794951359</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>01066481842</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>257520</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>kk_4840035519</t>
+          <t>jung1481</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>01086385010</t>
+          <t>01024193371</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>304121</t>
+          <t>205735</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_4839027252</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01084518813</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>304083</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>kk_4840035519</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01086385010</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>304121</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>motamsi</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>01090344665</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>96716</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ganjing78</t>
+          <t>jeonhyel</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>01065121424</t>
+          <t>01077942894</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>78590</t>
+          <t>304102</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>180321</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9260,71 +9260,71 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>304104</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>kk_3678962368</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>01041028567</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>250374</t>
+          <t>304113</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>kk_4538201048</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>01071790372</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>287217</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9341,71 +9341,71 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>isaackwak</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>01090599860</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>275913</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>maksim04</t>
+          <t>mooner82</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>01063557978</t>
+          <t>01037861045</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>202013</t>
+          <t>148696</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_3796517297</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01040802850</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>257878</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9422,17 +9422,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>byun7707</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>01077391740</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>161371</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9442,24 +9442,24 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>kk_4839283126</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>01024419045</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>304093</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9469,24 +9469,24 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9496,24 +9496,24 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>227343</t>
+          <t>172790</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9530,17 +9530,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>kk_2985598511</t>
+          <t>js0987</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>01086703302</t>
+          <t>01052819790</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>218005</t>
+          <t>110955</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9557,71 +9557,71 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>kk_2985598511</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01086703302</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>218005</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_4840174486</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01064087457</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>298138</t>
+          <t>304131</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>kk_3960572616</t>
+          <t>kk_4484370599</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>01072737379</t>
+          <t>01052246899</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>270384</t>
+          <t>284447</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9638,71 +9638,71 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>kk_4212157104</t>
+          <t>kk_4839241951</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>01062437191</t>
+          <t>01079146776</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>272417</t>
+          <t>304090</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9719,17 +9719,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>289364</t>
+          <t>232010</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -593,17 +593,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kig0268</t>
+          <t>kk_3182623010</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01053928207</t>
+          <t>01094128645</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>301007</t>
+          <t>227908</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -613,61 +613,61 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_3182623010</t>
+          <t>kk_3407332090</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01094128645</t>
+          <t>01073480423</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>227908</t>
+          <t>241393</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_3407332090</t>
+          <t>kig0268</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01073480423</t>
+          <t>01053928207</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>241393</t>
+          <t>301007</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
     </row>
@@ -782,17 +782,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kk_4507190107</t>
+          <t>sagepcs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01091780704</t>
+          <t>01058583300</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>285496</t>
+          <t>201749</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -802,78 +802,78 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kk_3243338539</t>
+          <t>joohpark87</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01025098649</t>
+          <t>01062437622</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>234832</t>
+          <t>121373</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sagepcs</t>
+          <t>kk_3243338539</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01058583300</t>
+          <t>01025098649</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>201749</t>
+          <t>234832</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>joohpark87</t>
+          <t>kk_4507190107</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01062437622</t>
+          <t>01091780704</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>121373</t>
+          <t>285496</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
         </is>
       </c>
     </row>
@@ -917,17 +917,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hbnetsys</t>
+          <t>kk_3794046073</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01052810852</t>
+          <t>01056918495</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>282445</t>
+          <t>257320</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -937,61 +937,61 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_4772822345</t>
+          <t>hbnetsys</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01036338705</t>
+          <t>01052810852</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>301574</t>
+          <t>282445</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_3794046073</t>
+          <t>kk_4772822345</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01056918495</t>
+          <t>01036338705</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>257320</t>
+          <t>301574</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
     </row>
@@ -1025,54 +1025,54 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cutebear88</t>
+          <t>staylus11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01039942456</t>
+          <t>01055097903</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>212858</t>
+          <t>200332</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>staylus11</t>
+          <t>cutebear88</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01055097903</t>
+          <t>01039942456</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>200332</t>
+          <t>212858</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1106,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_3959240760</t>
+          <t>kk_3340113031</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01035045875</t>
+          <t>01098338138</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>270320</t>
+          <t>239100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1126,51 +1126,51 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>astro77</t>
+          <t>namki9545</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01091518663</t>
+          <t>01073099545</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>167514</t>
+          <t>27441</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_3692762833</t>
+          <t>kk_3338448571</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01087630523</t>
+          <t>01050068417</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>250938</t>
+          <t>239011</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1180,105 +1180,105 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4291314607</t>
+          <t>astro77</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01088119636</t>
+          <t>01091518663</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>275953</t>
+          <t>167514</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>120212705670680427</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gbk888</t>
+          <t>kk_3959240760</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01063271523</t>
+          <t>01035045875</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>264430</t>
+          <t>270320</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_2760596791</t>
+          <t>gbk888</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01087827701</t>
+          <t>01063271523</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>208450</t>
+          <t>264430</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pkcomon</t>
+          <t>kk_3628696638_2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01063208976</t>
+          <t>01038262132</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>198932</t>
+          <t>302884</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1288,51 +1288,51 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>namki9545</t>
+          <t>pkcomon</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01073099545</t>
+          <t>01063208976</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>27441</t>
+          <t>198932</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_4226246986</t>
+          <t>kk_3692762833</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01048263393</t>
+          <t>01087630523</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>273085</t>
+          <t>250938</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1342,24 +1342,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_3340113031</t>
+          <t>kk_4226246986</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01098338138</t>
+          <t>01048263393</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>239100</t>
+          <t>273085</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1369,78 +1369,78 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_3628696638_2</t>
+          <t>kk_2760596791</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01038262132</t>
+          <t>01087827701</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>302884</t>
+          <t>208450</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>jung9916</t>
+          <t>kk_2850432473</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01091576210</t>
+          <t>01026771240</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>171554</t>
+          <t>213403</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_2850432473</t>
+          <t>kk_4291314607</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01026771240</t>
+          <t>01088119636</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>213403</t>
+          <t>275953</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1484,44 +1484,44 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_3338448571</t>
+          <t>jung9916</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01050068417</t>
+          <t>01091576210</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>239011</t>
+          <t>171554</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4278011504</t>
+          <t>kk_2783594999</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01045289321</t>
+          <t>01095317357</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>275167</t>
+          <t>209807</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1531,78 +1531,78 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>juhan3489</t>
+          <t>kk_4828047673</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01037693092</t>
+          <t>01087502319</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>214043</t>
+          <t>303388</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>aram2016</t>
+          <t>kk_4743669054</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01071670785</t>
+          <t>01036749627</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>225250</t>
+          <t>300361</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_3793101024</t>
+          <t>kk_4201661917</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01082844287</t>
+          <t>01052228247</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>257080</t>
+          <t>271984</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1612,24 +1612,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4838420487</t>
+          <t>kk_2762251625</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01050618241</t>
+          <t>01032085585</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>304051</t>
+          <t>208548</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1639,51 +1639,51 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4743669054</t>
+          <t>kk_4838420487</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01036749627</t>
+          <t>01050618241</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>300361</t>
+          <t>304051</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_2762251625</t>
+          <t>aram2016</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01032085585</t>
+          <t>01071670785</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>208548</t>
+          <t>225250</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1693,24 +1693,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>stonehinge</t>
+          <t>kk_4509280340</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01027275105</t>
+          <t>01088521558</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>285569</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1720,51 +1720,51 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>lms_ecom_0401_springhiking</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_3097460767</t>
+          <t>kk_4746910410</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01048597145</t>
+          <t>01047502488</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>221400</t>
+          <t>300629</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4837990320</t>
+          <t>kk_4278011504</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01024175652</t>
+          <t>01045289321</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>304030</t>
+          <t>275167</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1774,24 +1774,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_3795564177</t>
+          <t>kk_4837990320</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01044552859</t>
+          <t>01024175652</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>257673</t>
+          <t>304030</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1801,24 +1801,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4746910410</t>
+          <t>juhan3489</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01047502488</t>
+          <t>01037693092</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>300629</t>
+          <t>214043</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1828,24 +1828,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4201661917</t>
+          <t>kk_4694268987</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01052228247</t>
+          <t>01025088964</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>271984</t>
+          <t>295680</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
     </row>
@@ -1889,71 +1889,71 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_4509280340</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01088521558</t>
+          <t>01085815097</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>285569</t>
+          <t>303542</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_3241814751</t>
+          <t>djmin57</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01048808215</t>
+          <t>01034585986</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>234712</t>
+          <t>52890</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>djmin57</t>
+          <t>kk_3793101024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01034585986</t>
+          <t>01082844287</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>52890</t>
+          <t>257080</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1963,34 +1963,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_4828047673</t>
+          <t>stonehinge</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01087502319</t>
+          <t>01027275105</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>303388</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>lms_ecom_0401_springhiking</t>
         </is>
       </c>
     </row>
@@ -2024,27 +2024,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_2783594999</t>
+          <t>kk_3241814751</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01095317357</t>
+          <t>01048808215</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>209807</t>
+          <t>234712</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -2078,243 +2078,243 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4694268987</t>
+          <t>kk_3097460767</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01025088964</t>
+          <t>01048597145</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>295680</t>
+          <t>221400</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_3795564177</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01085815097</t>
+          <t>01044552859</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>303542</t>
+          <t>257673</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_3778874557</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01094017193</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>256071</t>
+          <t>244619</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01083936762</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>168147</t>
+          <t>303728</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_3967220863</t>
+          <t>endruns</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01087902066</t>
+          <t>01020716852</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>270700</t>
+          <t>176346</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ssbok0806</t>
+          <t>kk_3203549435</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01093267531</t>
+          <t>01033608209</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>223278</t>
+          <t>230719</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>p7181</t>
+          <t>kk_4837763007</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01056288360</t>
+          <t>01088993992</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>250858</t>
+          <t>304013</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>endruns</t>
+          <t>kk_3778874557</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01020716852</t>
+          <t>01094017193</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>176346</t>
+          <t>256071</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>cgkrry</t>
+          <t>kk_3707105860</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01085513271</t>
+          <t>01059290508</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>48578</t>
+          <t>251625</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -2348,98 +2348,98 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>jcahn12</t>
+          <t>kk_4817738509</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01038358052</t>
+          <t>01085325672</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>59346</t>
+          <t>302840</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_3707105860</t>
+          <t>joocho629</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01059290508</t>
+          <t>01038056919</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>251625</t>
+          <t>162948</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0224</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4614762502</t>
+          <t>p7181</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01064155845</t>
+          <t>01056288360</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>290560</t>
+          <t>250858</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6941110100332</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_3186268807</t>
+          <t>kk_3967220863</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01055175130</t>
+          <t>01087902066</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>230244</t>
+          <t>270700</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2449,51 +2449,51 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_4614762502</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01064155845</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>290560</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>joocho629</t>
+          <t>klim202</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01038056919</t>
+          <t>01064368836</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>162948</t>
+          <t>168762</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2503,78 +2503,78 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>EDM_0224</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4793026063</t>
+          <t>cgkrry</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01072703070</t>
+          <t>01085513271</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>302125</t>
+          <t>48578</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_3727979047</t>
+          <t>kk_3866200904</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01079273404</t>
+          <t>01062556776</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>252685</t>
+          <t>265988</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>ssbok0806</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01093267531</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>223278</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2584,51 +2584,51 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>klim202</t>
+          <t>abejung</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01064368836</t>
+          <t>01023320007</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>168762</t>
+          <t>158025</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_3734181513</t>
+          <t>kk_3186268807</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01066389021</t>
+          <t>01055175130</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>253177</t>
+          <t>230244</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2638,78 +2638,78 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4833493849</t>
+          <t>kk_3229351319</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01083936762</t>
+          <t>01090969959</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>303728</t>
+          <t>233446</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4837763007</t>
+          <t>kk_3727979047</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01088993992</t>
+          <t>01079273404</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>304013</t>
+          <t>252685</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_3203549435</t>
+          <t>jcahn12</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01033608209</t>
+          <t>01038358052</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>230719</t>
+          <t>59346</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2719,78 +2719,78 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_4817738509</t>
+          <t>kk_3734181513</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01085325672</t>
+          <t>01066389021</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>302840</t>
+          <t>253177</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4299847976</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01091384892</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>276488</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_3866200904</t>
+          <t>kk_3290809343</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01062556776</t>
+          <t>01057206001</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>265988</t>
+          <t>237059</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2800,105 +2800,105 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_3290809343</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01057206001</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>237059</t>
+          <t>168147</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_3229351319</t>
+          <t>kk_4793026063</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01090969959</t>
+          <t>01072703070</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>233446</t>
+          <t>302125</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>abejung</t>
+          <t>kk_4299847976</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01023320007</t>
+          <t>01091384892</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>158025</t>
+          <t>276488</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>scubaktk</t>
+          <t>gilinim</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01028951833</t>
+          <t>01032351966</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>51328</t>
+          <t>302594</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2908,51 +2908,51 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>wlcnstjs12</t>
+          <t>kk_4508257846</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01040240293</t>
+          <t>01092499867</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>149195</t>
+          <t>285541</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4508257846</t>
+          <t>kk_4443559736</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01092499867</t>
+          <t>01064021269</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>285541</t>
+          <t>282199</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2962,24 +2962,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0331</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_3774156950</t>
+          <t>chunsadl</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01041159966</t>
+          <t>01087804011</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>255778</t>
+          <t>167610</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2989,34 +2989,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>godo2027</t>
+          <t>ferix1999</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01075835624</t>
+          <t>01026339659</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>179139</t>
+          <t>191848</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -3050,44 +3050,44 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>chelius</t>
+          <t>kk_3801427305</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01024880126</t>
+          <t>01097820998</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>300985</t>
+          <t>259073</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4839929131</t>
+          <t>godo2027</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01044408612</t>
+          <t>01075835624</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>304116</t>
+          <t>179139</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3097,78 +3097,78 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4443559736</t>
+          <t>kk_4288079130</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01064021269</t>
+          <t>01056697298</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>282199</t>
+          <t>275750</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>EDM_0331</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>goppagi</t>
+          <t>chelius</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01052632529</t>
+          <t>01024880126</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>179049</t>
+          <t>300985</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kmhjm</t>
+          <t>optimal11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01095316235</t>
+          <t>01083258827</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>181953</t>
+          <t>129148</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
@@ -3212,17 +3212,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4440711181</t>
+          <t>kk_4839929131</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01063263543</t>
+          <t>01044408612</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>282110</t>
+          <t>304116</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3232,51 +3232,51 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kbh2639</t>
+          <t>kk_4525960790</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01026514411</t>
+          <t>01084170327</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>159679</t>
+          <t>286541</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>jeshurun76</t>
+          <t>kk_3795672557</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01051236012</t>
+          <t>01091179346</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>191849</t>
+          <t>257697</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3286,51 +3286,51 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>junghyunpak</t>
+          <t>kk_4282126610</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01028120688</t>
+          <t>01037415807</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>58618</t>
+          <t>275374</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_3795672557</t>
+          <t>kk_4217088689</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01091179346</t>
+          <t>01077710204</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>257697</t>
+          <t>272648</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3340,29 +3340,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4755147673</t>
+          <t>haein607</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01062968675</t>
+          <t>01023369606</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>301054</t>
+          <t>151209</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3374,98 +3374,98 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4475486602</t>
+          <t>hansoi93</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01041949661</t>
+          <t>01072262346</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>284059</t>
+          <t>60217</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4217088689</t>
+          <t>scp0103</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01077710204</t>
+          <t>01033083314</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>272648</t>
+          <t>214558</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>comic0828</t>
+          <t>kk_2975660270</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01096390888</t>
+          <t>01065565496</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>140326</t>
+          <t>217640</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>gilinim</t>
+          <t>kk_3246970011</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01032351966</t>
+          <t>01080703392</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>302594</t>
+          <t>235053</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3475,186 +3475,186 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>jeshurun76</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01092690887</t>
+          <t>01051236012</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>303428</t>
+          <t>191849</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_3898041727</t>
+          <t>kk_4475486602</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01091030227</t>
+          <t>01041949661</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>267643</t>
+          <t>284059</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_4282126610</t>
+          <t>kmhjm</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01037415807</t>
+          <t>01095316235</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>275374</t>
+          <t>181953</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4838385004</t>
+          <t>kk_4828776483</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01088158446</t>
+          <t>01092690887</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>304048</t>
+          <t>303428</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_3901736373</t>
+          <t>wlcnstjs12</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01072562998</t>
+          <t>01040240293</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>267789</t>
+          <t>149195</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_3943654079</t>
+          <t>kk_3774156950</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01053762357</t>
+          <t>01041159966</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>269510</t>
+          <t>255778</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>hansoi93</t>
+          <t>kk_3898041727</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01072262346</t>
+          <t>01091030227</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>60217</t>
+          <t>267643</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3664,78 +3664,78 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4610571768</t>
+          <t>sbstkd</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01094092580</t>
+          <t>01084506080</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>290026</t>
+          <t>137269</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>luvsena</t>
+          <t>plus7431</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01089625349</t>
+          <t>01084748664</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>172100</t>
+          <t>251388</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_2975660270</t>
+          <t>kbh2639</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01065565496</t>
+          <t>01026514411</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>217640</t>
+          <t>159679</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3745,29 +3745,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ferix1999</t>
+          <t>goppagi</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01026339659</t>
+          <t>01052632529</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>191848</t>
+          <t>179049</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3779,71 +3779,71 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4310987668</t>
+          <t>kk_4755147673</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01027962045</t>
+          <t>01062968675</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>277132</t>
+          <t>301054</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_3801427305</t>
+          <t>scubaktk</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01097820998</t>
+          <t>01028951833</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>259073</t>
+          <t>51328</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_4634804186</t>
+          <t>luvsena</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01089506651</t>
+          <t>01089625349</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>292029</t>
+          <t>172100</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3853,34 +3853,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>plus7431</t>
+          <t>kk_4610571768</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01084748664</t>
+          <t>01094092580</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>251388</t>
+          <t>290026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
@@ -3914,44 +3914,44 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>haein607</t>
+          <t>kk_3718281230</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01023369606</t>
+          <t>01067711528</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>151209</t>
+          <t>252078</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>sbstkd</t>
+          <t>kk_3456892694</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01084506080</t>
+          <t>01057443264</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>137269</t>
+          <t>243269</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3961,132 +3961,132 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_3456892694</t>
+          <t>junghyunpak</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01057443264</t>
+          <t>01028120688</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>243269</t>
+          <t>58618</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_3825294168</t>
+          <t>kk_4634804186</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01076290208</t>
+          <t>01089506651</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>263146</t>
+          <t>292029</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>optimal11</t>
+          <t>kk_4838385004</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01083258827</t>
+          <t>01088158446</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>129148</t>
+          <t>304048</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>delta12</t>
+          <t>comic0828</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01071339709</t>
+          <t>01096390888</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>192352</t>
+          <t>140326</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>scp0103</t>
+          <t>kk_3825294168</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01033083314</t>
+          <t>01076290208</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>214558</t>
+          <t>263146</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4096,78 +4096,78 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4525960790</t>
+          <t>delta12</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01084170327</t>
+          <t>01071339709</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>286541</t>
+          <t>192352</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_3246970011</t>
+          <t>kk_4310987668</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01080703392</t>
+          <t>01027962045</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>235053</t>
+          <t>277132</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4288079130</t>
+          <t>kk_3943654079</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01056697298</t>
+          <t>01053762357</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>275750</t>
+          <t>269510</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4177,240 +4177,240 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_3718281230</t>
+          <t>kk_4440711181</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01067711528</t>
+          <t>01063263543</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>252078</t>
+          <t>282110</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>chunsadl</t>
+          <t>kk_3901736373</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01087804011</t>
+          <t>01072562998</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>167610</t>
+          <t>267789</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_3736097865</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01089447248</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>253356</t>
+          <t>303885</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_4212123801</t>
+          <t>kk_3694865986</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01083862682</t>
+          <t>01083470708</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>272414</t>
+          <t>251070</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4840238333</t>
+          <t>kk_3631606950</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01087443182</t>
+          <t>01063256163</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>304135</t>
+          <t>248164</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kslee9011</t>
+          <t>eccomi21</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01031716463</t>
+          <t>01084717525</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>48237</t>
+          <t>143557</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kimchhgood</t>
+          <t>kk_3798545067</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01092133961</t>
+          <t>01023751319</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>258449</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4530117802</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01094437239</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>287573</t>
+          <t>286792</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_3601774804</t>
+          <t>kk_4825242022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01046513357</t>
+          <t>01025208267</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>247059</t>
+          <t>303235</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4420,24 +4420,24 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_3775794718</t>
+          <t>kk_3776403631</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01085983536</t>
+          <t>01034755755</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>255860</t>
+          <t>255908</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4447,78 +4447,78 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_3631606950</t>
+          <t>jth0122</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01063256163</t>
+          <t>01088989856</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>248164</t>
+          <t>96490</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>eccomi21</t>
+          <t>kk_4838635909</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01084717525</t>
+          <t>01098131007</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>143557</t>
+          <t>304064</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kkemc11</t>
+          <t>kk_3633964155</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01072822359</t>
+          <t>01097743709</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>224851</t>
+          <t>248300</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4528,24 +4528,24 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_3798545067</t>
+          <t>kk_4835826103</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01023751319</t>
+          <t>01082133090</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>258449</t>
+          <t>303894</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4555,250 +4555,250 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_3766082784</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01092342302</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>255139</t>
+          <t>304098</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>fimajun</t>
+          <t>lynx246</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01035668051</t>
+          <t>01041241323</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>230171</t>
+          <t>196113</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_4835267037</t>
+          <t>kk_3913679442</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01047143494</t>
+          <t>01085569215</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>303847</t>
+          <t>268330</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>anirim</t>
+          <t>kk_4212123801</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01026146239</t>
+          <t>01083862682</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>303897</t>
+          <t>272414</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>kimchhgood</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01092133961</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>280163</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_3258483317</t>
+          <t>kk_4681484279</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01075584654</t>
+          <t>01022642776</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>235788</t>
+          <t>294947</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4838748515</t>
+          <t>kk_4720019874</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01034435700</t>
+          <t>01052578634</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>304070</t>
+          <t>297465</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>water4853</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01020542351</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>178866</t>
+          <t>304107</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>csnoopy</t>
+          <t>jment1983</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01063730741</t>
+          <t>01088991983</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>110007</t>
+          <t>271329</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -4832,17 +4832,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4838514193</t>
+          <t>kk_4839598883</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01028513978</t>
+          <t>01032207906</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>304057</t>
+          <t>304105</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4859,71 +4859,71 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>jth0122</t>
+          <t>kk_4835267037</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01088989856</t>
+          <t>01047143494</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>96490</t>
+          <t>303847</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>304107</t>
+          <t>287573</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kk_3465759734</t>
+          <t>tkfkdtmfjs79</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01045550499</t>
+          <t>01044809033</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>243732</t>
+          <t>153239</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4933,78 +4933,78 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_4819536073</t>
+          <t>kk_3775794718</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01039113089</t>
+          <t>01085983536</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>302942</t>
+          <t>255860</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_3766082784</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01092342302</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>255139</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_2989316682</t>
+          <t>kk_2999650964</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01037375641</t>
+          <t>01073667501</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>218263</t>
+          <t>218535</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5014,24 +5014,24 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>bizboard</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>whtjdfo11</t>
+          <t>fimajun</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01075377523</t>
+          <t>01035668051</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>185516</t>
+          <t>230171</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5041,24 +5041,24 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>tomcurse02</t>
+          <t>kk_3601774804</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01022070282</t>
+          <t>01046513357</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>96444</t>
+          <t>247059</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5068,78 +5068,78 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>kk_4838646680</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01034311248</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>304098</t>
+          <t>304066</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[pf]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_4720019874</t>
+          <t>kk_4840238333</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01052578634</t>
+          <t>01087443182</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>297465</t>
+          <t>304135</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_4703414773</t>
+          <t>kk_2989316682</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01093547510</t>
+          <t>01037375641</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>296108</t>
+          <t>218263</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5149,51 +5149,51 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ohey2003</t>
+          <t>csnoopy</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01034151656</t>
+          <t>01063730741</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>116157</t>
+          <t>110007</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kk_4681484279</t>
+          <t>kk_4838748515</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01022642776</t>
+          <t>01034435700</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>294947</t>
+          <t>304070</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5203,78 +5203,78 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>hjh3127</t>
+          <t>kk_4838514193</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01054261891</t>
+          <t>01028513978</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>52538</t>
+          <t>304057</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>kk_4478716748</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01071630157</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>164951</t>
+          <t>284194</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_4835837819</t>
+          <t>colorum</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01044119822</t>
+          <t>01054844416</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>303896</t>
+          <t>146276</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5284,24 +5284,24 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kk_3776403631</t>
+          <t>kiraeo</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01034755755</t>
+          <t>01085072563</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>255908</t>
+          <t>195029</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5311,78 +5311,78 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kk_4530117802</t>
+          <t>kk_3793412568</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01094437239</t>
+          <t>01049200546</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>286792</t>
+          <t>257211</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4672701053</t>
+          <t>kk_4819536073</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01088807653</t>
+          <t>01039113089</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>294426</t>
+          <t>302942</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4612713787</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01095027601</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>290278</t>
+          <t>164951</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5399,71 +5399,71 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>lynx246</t>
+          <t>kk_4672701053</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01041241323</t>
+          <t>01088807653</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>196113</t>
+          <t>294426</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>jment1983</t>
+          <t>water4853</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01088991983</t>
+          <t>01020542351</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>271329</t>
+          <t>178866</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>raneelim</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01051598929</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>72197</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5473,78 +5473,78 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>myjjangga</t>
+          <t>soojst</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01083364898</t>
+          <t>01097431003</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>87940</t>
+          <t>209447</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>raneelim</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01051598929</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>72197</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>kk_4446020087</t>
+          <t>kk_4344215691</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01089773053</t>
+          <t>01020192399</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>282273</t>
+          <t>279044</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5561,71 +5561,71 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>kk_4839598883</t>
+          <t>kk_3736097865</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01032207906</t>
+          <t>01089447248</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>304105</t>
+          <t>253356</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>colorum</t>
+          <t>kslee9011</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01054844416</t>
+          <t>01031716463</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>146276</t>
+          <t>48237</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>soojst</t>
+          <t>anirim</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01097431003</t>
+          <t>01026146239</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>209447</t>
+          <t>303897</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5635,51 +5635,51 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>kk_3694865986</t>
+          <t>kk_4222073058</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01083470708</t>
+          <t>01046077586</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>251070</t>
+          <t>272870</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>kk_2999650964</t>
+          <t>kk_3465759734</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01073667501</t>
+          <t>01045550499</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>218535</t>
+          <t>243732</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5689,24 +5689,24 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>kk_4825242022</t>
+          <t>kk_4464127061</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01025208267</t>
+          <t>01073655835</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>303235</t>
+          <t>283300</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5716,132 +5716,132 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>kk_3793412568</t>
+          <t>kk_4446020087</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01049200546</t>
+          <t>01089773053</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>257211</t>
+          <t>282273</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>kk_3913679442</t>
+          <t>myjjangga</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01085569215</t>
+          <t>01083364898</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>268330</t>
+          <t>87940</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>kkemc11</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01072822359</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>303885</t>
+          <t>224851</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_4835826103</t>
+          <t>kk_4703414773</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01082133090</t>
+          <t>01093547510</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>303894</t>
+          <t>296108</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kk_4838646680</t>
+          <t>tomcurse02</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01034311248</t>
+          <t>01022070282</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>304066</t>
+          <t>96444</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>[pf]트래픽_유사+관심사</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>kk_3633964155</t>
+          <t>ohey2003</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01097743709</t>
+          <t>01034151656</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>248300</t>
+          <t>116157</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5878,51 +5878,51 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>kk_4838635909</t>
+          <t>kk_3258483317</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01098131007</t>
+          <t>01075584654</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>304064</t>
+          <t>235788</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>kiraeo</t>
+          <t>hjh3127</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01085072563</t>
+          <t>01054261891</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>195029</t>
+          <t>52538</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5932,24 +5932,24 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>tkfkdtmfjs79</t>
+          <t>whtjdfo11</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01044809033</t>
+          <t>01075377523</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>153239</t>
+          <t>185516</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -5993,44 +5993,44 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>kk_4478716748</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01071630157</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>284194</t>
+          <t>280163</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>kk_4222073058</t>
+          <t>kk_4835837819</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01046077586</t>
+          <t>01044119822</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>272870</t>
+          <t>303896</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6040,24 +6040,24 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_4344215691</t>
+          <t>kk_4612713787</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01020192399</t>
+          <t>01095027601</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>279044</t>
+          <t>290278</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6074,71 +6074,71 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kk_4464127061</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01073655835</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>283300</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kk_4538201048</t>
+          <t>kk_3466706406</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01071790372</t>
+          <t>01055441553</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>287217</t>
+          <t>243779</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6155,17 +6155,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6182,17 +6182,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kk_4212258541</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01047138543</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>272420</t>
+          <t>270708</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6209,152 +6209,152 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>kk_3220401027</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>01037591063</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>232602</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>304101</t>
+          <t>143826</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>kk_4357899204</t>
+          <t>kk_2950194486</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>01082772838</t>
+          <t>01076104875</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>279564</t>
+          <t>216766</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>seopme</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01074122238</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>279909</t>
+          <t>304125</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>kk_4838947856</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>01094709458</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>304075</t>
+          <t>219525</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>229454</t>
+          <t>279909</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6371,17 +6371,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>kk_3380246984</t>
+          <t>kk_4840174486</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>01040750851</t>
+          <t>01064087457</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>240492</t>
+          <t>304131</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6391,24 +6391,24 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>221630</t>
+          <t>136050</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6425,17 +6425,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>kk_3170564464</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>01099188001</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>224948</t>
+          <t>304104</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6445,24 +6445,24 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>kk_2915134680</t>
+          <t>kk_4517851709</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>01085224711</t>
+          <t>01066445714</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>215670</t>
+          <t>286074</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6472,24 +6472,24 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>fjsjhw</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01050468291</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>192240</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6499,51 +6499,51 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>kk_3960572616</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>01072737379</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>270384</t>
+          <t>292319</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6560,17 +6560,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>he0218</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>01049289998</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>254710</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6580,24 +6580,24 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>hodong1014</t>
+          <t>jung1481</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>01044530048</t>
+          <t>01024193371</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>64397</t>
+          <t>205735</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6614,17 +6614,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6634,24 +6634,24 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>kk_3134493871</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01035918800</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>219525</t>
+          <t>222420</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -6661,51 +6661,51 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>304100</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>kk_3796517297</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01040802850</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>257878</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6722,17 +6722,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>304101</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -6742,24 +6742,24 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>kk_3501053454</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01093015628</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>245323</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -6769,132 +6769,132 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>kk_4839821563</t>
+          <t>jinoh</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>01027951809</t>
+          <t>01024150539</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>304112</t>
+          <t>270445</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>285491</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>kk_4839765445</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01076118972</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>kk_4212258541</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01047138543</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>272420</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>172790</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6911,17 +6911,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>kk_3750120343</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01092908890</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>227343</t>
+          <t>254168</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -6938,125 +6938,125 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>kk_4237700483</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>01063041087</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>273719</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>123130</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>kk_3466706406</t>
+          <t>kk_4838920250</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>01055441553</t>
+          <t>01065688860</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>243779</t>
+          <t>304074</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>268974</t>
+          <t>123130</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>maksim04</t>
+          <t>kk_3678962368</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>01063557978</t>
+          <t>01041028567</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>202013</t>
+          <t>250374</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -7073,71 +7073,71 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>304109</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>kk_4839283126</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01024419045</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>304093</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>byun7707</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01077391740</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>161371</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -7147,213 +7147,213 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>kk_4840198421</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01053706365</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>292319</t>
+          <t>304132</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>219219</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>304129</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>chlwoghk83</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>01038851983</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>145712</t>
+          <t>275998</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>304126</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>kk_4839542021</t>
+          <t>kk_4727505000</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>01089909663</t>
+          <t>01066573797</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>304103</t>
+          <t>298110</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>kk_2950194486</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>01076104875</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>216766</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>136050</t>
+          <t>186218</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7370,71 +7370,71 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>kk_4838920250</t>
+          <t>kk_4357899204</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>01065688860</t>
+          <t>01082772838</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>304074</t>
+          <t>279564</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>kk_2985598511</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01086703302</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>218005</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>kk_3794951359</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>01066481842</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>257520</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -7451,125 +7451,125 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>jsu2080</t>
+          <t>kk_4840035519</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>01094582080</t>
+          <t>01086385010</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>275256</t>
+          <t>304121</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>270708</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>304129</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>kk_4375333989</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>01091513985</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>280145</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -7579,78 +7579,78 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>kk_4517851709</t>
+          <t>jeonhyel</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>01066445714</t>
+          <t>01077942894</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>286074</t>
+          <t>304102</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>kk_4670878863</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01067207833</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>294326</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>kk_2915134680</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01085224711</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>215670</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7660,132 +7660,132 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>coverdn</t>
+          <t>kk_4212157104</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>01086426866</t>
+          <t>01062437191</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>172406</t>
+          <t>272417</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>298138</t>
+          <t>219219</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>kk_4839283126</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>01024419045</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>304093</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>kk_3501053454</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>01093015628</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>245323</t>
+          <t>68751</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>kk_3750120343</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>01092908890</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>254168</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -7802,17 +7802,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>ganjing78</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01065121424</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>78590</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7829,71 +7829,71 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_4839241951</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01079146776</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>304090</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>kk_4839765445</t>
+          <t>kk_4237700483</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>01076118972</t>
+          <t>01063041087</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>304111</t>
+          <t>273719</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>kk_3134493871</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>01035918800</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>222420</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7903,105 +7903,105 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>268974</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>kk_4840198421</t>
+          <t>isaackwak</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>01053706365</t>
+          <t>01090599860</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>304132</t>
+          <t>275913</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>motamsi</t>
+          <t>kk_4536846819</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>01090344665</t>
+          <t>01038223781</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>96716</t>
+          <t>287146</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>varam11</t>
+          <t>kk_4680971786</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>01071373327</t>
+          <t>01074443726</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>102004</t>
+          <t>294917</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -8011,51 +8011,51 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>kk_3678962368</t>
+          <t>richjm</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>01041028567</t>
+          <t>01082909799</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>250374</t>
+          <t>122482</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8065,24 +8065,24 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8099,17 +8099,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>hhpp123</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>01042621121</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>294450</t>
+          <t>140860</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8126,44 +8126,44 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>174291</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>hhpp123</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01042621121</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>294450</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8180,17 +8180,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_4375333989</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01091513985</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>280145</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8200,24 +8200,24 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>fjsjhw</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>01050468291</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>192240</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8227,51 +8227,51 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>kk_4221652535</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>01036858276</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>272849</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>mooner82</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01037861045</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>148696</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8288,135 +8288,135 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ganjing78</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>01065121424</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>78590</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>304124</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>kk_4212157104</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>01062437191</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>272417</t>
+          <t>304100</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>seopme</t>
+          <t>js0987</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>01074122238</t>
+          <t>01052819790</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>304125</t>
+          <t>110955</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>jinoh</t>
+          <t>kk_4839821563</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>01024150539</t>
+          <t>01027951809</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>270445</t>
+          <t>304112</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -8450,17 +8450,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>byun7707</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>01077391740</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>161371</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8470,51 +8470,51 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>kk_4838947856</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01094709458</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>140860</t>
+          <t>304075</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>kk_4727505000</t>
+          <t>he0218</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>01066573797</t>
+          <t>01049289998</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>298110</t>
+          <t>254710</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8524,24 +8524,24 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>kyong74</t>
+          <t>kk_3960572616</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>01088245591</t>
+          <t>01072737379</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>22857</t>
+          <t>270384</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8558,17 +8558,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>kk_4680971786</t>
+          <t>jsu2080</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>01074443726</t>
+          <t>01094582080</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>294917</t>
+          <t>275256</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8585,17 +8585,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>kk_4536846819</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>01038223781</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>287146</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8605,51 +8605,51 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>chaser1</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01038304145</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>178090</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>232010</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8659,51 +8659,51 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>162562</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>285491</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8713,24 +8713,24 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>hodong1014</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01044530048</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>64397</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8747,44 +8747,44 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>isaackwak</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>01090599860</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>275913</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>kk_4670878863</t>
+          <t>kk_4288273717</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>01067207833</t>
+          <t>01020746624</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>294326</t>
+          <t>275762</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8801,71 +8801,71 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>304086</t>
+          <t>208245</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>174291</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>kk_4288273717</t>
+          <t>kk_4538201048</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>01020746624</t>
+          <t>01071790372</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>275762</t>
+          <t>287217</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8882,71 +8882,71 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>richjm</t>
+          <t>varam11</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>01082909799</t>
+          <t>01071373327</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>122482</t>
+          <t>102004</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EDM_0413</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>chaser1</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>01038304145</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>178090</t>
+          <t>227343</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8963,44 +8963,44 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>maksim04</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01063557978</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>68751</t>
+          <t>202013</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>180321</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9017,211 +9017,211 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>kk_4839027252</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01084518813</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>143826</t>
+          <t>304083</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>coverdn</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01086426866</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>172406</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EDM_0413</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>jung1481</t>
+          <t>kk_4221652535</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>01024193371</t>
+          <t>01036858276</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>205735</t>
+          <t>272849</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>kk_4839027252</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>01084518813</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>304083</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>chlwoghk83</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01038851983</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>145712</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>kk_4840035519</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>01086385010</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>304121</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>motamsi</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01090344665</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>96716</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>jeonhyel</t>
+          <t>kk_4839542021</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>01077942894</t>
+          <t>01089909663</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>304102</t>
+          <t>304103</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -9233,17 +9233,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>180321</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9260,71 +9260,71 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>kk_3380246984</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01040750851</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>304104</t>
+          <t>240492</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9341,71 +9341,71 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>kk_4484370599</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01052246899</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>284447</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>mooner82</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>01037861045</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>148696</t>
+          <t>229454</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>kk_3796517297</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>01040802850</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>257878</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9422,17 +9422,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>kk_3794951359</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01066481842</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>257520</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9449,17 +9449,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>kk_3170564464</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01099188001</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>224948</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9469,51 +9469,51 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>304086</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9530,71 +9530,71 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>js0987</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>01052819790</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>110955</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>kk_2985598511</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>01086703302</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>218005</t>
+          <t>304113</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>kk_4840174486</t>
+          <t>kk_3220401027</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>01064087457</t>
+          <t>01037591063</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>304131</t>
+          <t>232602</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9604,24 +9604,24 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>EDM_0413</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>kk_4484370599</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>01052246899</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>284447</t>
+          <t>221630</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9638,98 +9638,98 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>kk_4839241951</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>01079146776</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>304090</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>289364</t>
+          <t>304126</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>kyong74</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01088245591</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>232010</t>
+          <t>22857</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -620,54 +620,54 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_3407332090</t>
+          <t>kig0268</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01073480423</t>
+          <t>01053928207</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>241393</t>
+          <t>301007</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kig0268</t>
+          <t>kk_3407332090</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01053928207</t>
+          <t>01073480423</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>301007</t>
+          <t>241393</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -701,54 +701,54 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_3178599665</t>
+          <t>kk_3500501777</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01089430429</t>
+          <t>01038347573</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>225280</t>
+          <t>245304</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_3500501777</t>
+          <t>kk_3178599665</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01038347573</t>
+          <t>01089430429</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>245304</t>
+          <t>225280</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -782,17 +782,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sagepcs</t>
+          <t>joohpark87</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01058583300</t>
+          <t>01062437622</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>201749</t>
+          <t>121373</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -802,24 +802,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>joohpark87</t>
+          <t>kk_4507190107</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01062437622</t>
+          <t>01091780704</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>121373</t>
+          <t>285496</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -829,61 +829,61 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kk_3243338539</t>
+          <t>sagepcs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01025098649</t>
+          <t>01058583300</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>234832</t>
+          <t>201749</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kk_4507190107</t>
+          <t>kk_3243338539</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01091780704</t>
+          <t>01025098649</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>285496</t>
+          <t>234832</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -917,17 +917,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_3794046073</t>
+          <t>hbnetsys</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01056918495</t>
+          <t>01052810852</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>257320</t>
+          <t>282445</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -937,78 +937,78 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>hbnetsys</t>
+          <t>kk_4772822345</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01052810852</t>
+          <t>01036338705</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>282445</t>
+          <t>301574</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_4772822345</t>
+          <t>kk_3794046073</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01036338705</t>
+          <t>01056918495</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>301574</t>
+          <t>257320</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>justicek73</t>
+          <t>cutebear88</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01033270931</t>
+          <t>01039942456</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>237394</t>
+          <t>212858</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1018,51 +1018,51 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>staylus11</t>
+          <t>justicek73</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01055097903</t>
+          <t>01033270931</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>200332</t>
+          <t>237394</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cutebear88</t>
+          <t>kk_4493450118</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01039942456</t>
+          <t>01077566800</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>212858</t>
+          <t>284909</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1072,34 +1072,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_4493450118</t>
+          <t>staylus11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01077566800</t>
+          <t>01055097903</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>284909</t>
+          <t>200332</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>namki9545</t>
+          <t>darius27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01073099545</t>
+          <t>01091911224</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>27441</t>
+          <t>292238</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_3338448571</t>
+          <t>kk_3692762833</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01050068417</t>
+          <t>01087630523</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>239011</t>
+          <t>250938</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1180,24 +1180,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>astro77</t>
+          <t>gbk888</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01091518663</t>
+          <t>01063271523</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>167514</t>
+          <t>264430</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1207,61 +1207,61 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_3959240760</t>
+          <t>pkcomon</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01035045875</t>
+          <t>01063208976</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>270320</t>
+          <t>198932</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gbk888</t>
+          <t>kk_2850432473</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01063271523</t>
+          <t>01026771240</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>264430</t>
+          <t>213403</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -1295,44 +1295,44 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pkcomon</t>
+          <t>kk_4291314607</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01063208976</t>
+          <t>01088119636</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>198932</t>
+          <t>275953</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_3692762833</t>
+          <t>kk_3338448571</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01087630523</t>
+          <t>01050068417</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>250938</t>
+          <t>239011</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1342,24 +1342,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4226246986</t>
+          <t>kk_3959240760</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01048263393</t>
+          <t>01035045875</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>273085</t>
+          <t>270320</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1369,24 +1369,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_2760596791</t>
+          <t>kk_4226246986</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01087827701</t>
+          <t>01048263393</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>208450</t>
+          <t>273085</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1396,51 +1396,51 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_2850432473</t>
+          <t>jung9916</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01026771240</t>
+          <t>01091576210</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>213403</t>
+          <t>171554</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_4291314607</t>
+          <t>namki9545</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01088119636</t>
+          <t>01073099545</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>275953</t>
+          <t>27441</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1450,213 +1450,213 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>darius27</t>
+          <t>astro77</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01091911224</t>
+          <t>01091518663</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>292238</t>
+          <t>167514</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>120212705670680427</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>jung9916</t>
+          <t>kk_2760596791</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01091576210</t>
+          <t>01087827701</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>171554</t>
+          <t>208450</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_2783594999</t>
+          <t>kk_3793101024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01095317357</t>
+          <t>01082844287</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>209807</t>
+          <t>257080</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_4828047673</t>
+          <t>leecs11124</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01087502319</t>
+          <t>01037870639</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>303388</t>
+          <t>260560</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EDM_0214</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_4743669054</t>
+          <t>kk_4201661917</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01036749627</t>
+          <t>01052228247</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>300361</t>
+          <t>271984</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4201661917</t>
+          <t>kk_4837990320</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01052228247</t>
+          <t>01024175652</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>271984</t>
+          <t>304030</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_2762251625</t>
+          <t>juhan3489</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01032085585</t>
+          <t>01037693092</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>208548</t>
+          <t>214043</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4838420487</t>
+          <t>kk_3795564177</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01050618241</t>
+          <t>01044552859</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>304051</t>
+          <t>257673</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1673,44 +1673,44 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>aram2016</t>
+          <t>kk_4743669054</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01071670785</t>
+          <t>01036749627</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>225250</t>
+          <t>300361</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_4509280340</t>
+          <t>djmin57</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01088521558</t>
+          <t>01034585986</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>285569</t>
+          <t>52890</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1720,78 +1720,78 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4746910410</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01047502488</t>
+          <t>01085815097</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>300629</t>
+          <t>303542</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4278011504</t>
+          <t>kk_3241814751</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01045289321</t>
+          <t>01048808215</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>275167</t>
+          <t>234712</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_4837990320</t>
+          <t>kk_2783594999</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01024175652</t>
+          <t>01095317357</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>304030</t>
+          <t>209807</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1801,51 +1801,51 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>juhan3489</t>
+          <t>kk_4278011504</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01037693092</t>
+          <t>01045289321</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>214043</t>
+          <t>275167</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4694268987</t>
+          <t>kk_4746910410</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01025088964</t>
+          <t>01047502488</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>295680</t>
+          <t>300629</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1855,331 +1855,331 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>leecs11124</t>
+          <t>kk_4838420487</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01037870639</t>
+          <t>01050618241</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>260560</t>
+          <t>304051</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>stonehinge</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01085815097</t>
+          <t>01027275105</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>303542</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>lms_ecom_0401_springhiking</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>djmin57</t>
+          <t>aram2016</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01034585986</t>
+          <t>01071670785</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>52890</t>
+          <t>225250</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_3793101024</t>
+          <t>kk_4790899014</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01082844287</t>
+          <t>01024708415</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>257080</t>
+          <t>302058</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>stonehinge</t>
+          <t>kk_4828047673</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01027275105</t>
+          <t>01087502319</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>303388</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>lms_ecom_0401_springhiking</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_3827025148</t>
+          <t>kk_3097460767</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01090399900</t>
+          <t>01048597145</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>263356</t>
+          <t>221400</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_3241814751</t>
+          <t>kk_2762251625</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01048808215</t>
+          <t>01032085585</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>234712</t>
+          <t>208548</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4790899014</t>
+          <t>kk_3827025148</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01024708415</t>
+          <t>01090399900</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>302058</t>
+          <t>263356</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_3097460767</t>
+          <t>kk_4509280340</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01048597145</t>
+          <t>01088521558</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>221400</t>
+          <t>285569</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_3795564177</t>
+          <t>kk_4694268987</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01044552859</t>
+          <t>01025088964</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>257673</t>
+          <t>295680</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_3186268807</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01055175130</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>230244</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4833493849</t>
+          <t>jcahn12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01083936762</t>
+          <t>01038358052</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>303728</t>
+          <t>59346</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
@@ -2213,17 +2213,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_3203549435</t>
+          <t>joocho629</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01033608209</t>
+          <t>01038056919</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>230719</t>
+          <t>162948</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2233,24 +2233,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0224</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4837763007</t>
+          <t>kk_3203549435</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01088993992</t>
+          <t>01033608209</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>304013</t>
+          <t>230719</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2260,132 +2260,132 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_3778874557</t>
+          <t>kk_3727979047</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01094017193</t>
+          <t>01079273404</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>256071</t>
+          <t>252685</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_3707105860</t>
+          <t>kk_4817738509</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01059290508</t>
+          <t>01085325672</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>251625</t>
+          <t>302840</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4285105163</t>
+          <t>kk_4614762502</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01083283220</t>
+          <t>01064155845</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>275559</t>
+          <t>290560</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4817738509</t>
+          <t>kk_3229351319</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01085325672</t>
+          <t>01090969959</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>302840</t>
+          <t>233446</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>joocho629</t>
+          <t>kk_3734181513</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01038056919</t>
+          <t>01066389021</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>162948</t>
+          <t>253177</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2395,24 +2395,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>EDM_0224</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>p7181</t>
+          <t>kk_3707105860</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01056288360</t>
+          <t>01059290508</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>250858</t>
+          <t>251625</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2422,78 +2422,78 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_3967220863</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01087902066</t>
+          <t>01083936762</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>270700</t>
+          <t>303728</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4614762502</t>
+          <t>klim202</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01064155845</t>
+          <t>01064368836</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>290560</t>
+          <t>168762</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>klim202</t>
+          <t>kk_3778874557</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01064368836</t>
+          <t>01094017193</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>168762</t>
+          <t>256071</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2503,24 +2503,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>cgkrry</t>
+          <t>kk_4299847976</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01085513271</t>
+          <t>01091384892</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>48578</t>
+          <t>276488</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2530,132 +2530,132 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_3866200904</t>
+          <t>p7181</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01062556776</t>
+          <t>01056288360</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>265988</t>
+          <t>250858</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>6941110100332</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ssbok0806</t>
+          <t>kk_3866200904</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01093267531</t>
+          <t>01062556776</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>223278</t>
+          <t>265988</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>abejung</t>
+          <t>kk_4285105163</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01023320007</t>
+          <t>01083283220</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>158025</t>
+          <t>275559</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_3186268807</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01055175130</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>230244</t>
+          <t>244619</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_3229351319</t>
+          <t>kk_3967220863</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01090969959</t>
+          <t>01087902066</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>233446</t>
+          <t>270700</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2665,24 +2665,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_3727979047</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01079273404</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>252685</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2692,24 +2692,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>jcahn12</t>
+          <t>kk_3290809343</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01038358052</t>
+          <t>01057206001</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>59346</t>
+          <t>237059</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2719,105 +2719,105 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_3734181513</t>
+          <t>kk_4793026063</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01066389021</t>
+          <t>01072703070</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>253177</t>
+          <t>302125</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_4837763007</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01088993992</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>304013</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_3290809343</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01057206001</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>237059</t>
+          <t>168147</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>ssbok0806</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01093267531</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>168147</t>
+          <t>223278</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2827,51 +2827,51 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4793026063</t>
+          <t>abejung</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01072703070</t>
+          <t>01023320007</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>302125</t>
+          <t>158025</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4299847976</t>
+          <t>cgkrry</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01091384892</t>
+          <t>01085513271</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>276488</t>
+          <t>48578</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2881,24 +2881,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>gilinim</t>
+          <t>junghyunpak</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01032351966</t>
+          <t>01028120688</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>302594</t>
+          <t>58618</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2908,51 +2908,51 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4508257846</t>
+          <t>sbstkd</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01092499867</t>
+          <t>01084506080</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>285541</t>
+          <t>137269</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4443559736</t>
+          <t>hansoi93</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01064021269</t>
+          <t>01072262346</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>282199</t>
+          <t>60217</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2962,24 +2962,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>EDM_0331</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>chunsadl</t>
+          <t>luvsena</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01087804011</t>
+          <t>01089625349</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>167610</t>
+          <t>172100</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2989,51 +2989,51 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ferix1999</t>
+          <t>gilinim</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01026339659</t>
+          <t>01032351966</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>191848</t>
+          <t>302594</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>tinykim</t>
+          <t>kk_4440711181</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01035630719</t>
+          <t>01063263543</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>65922</t>
+          <t>282110</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3043,132 +3043,132 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_3801427305</t>
+          <t>kk_4217088689</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01097820998</t>
+          <t>01077710204</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>259073</t>
+          <t>272648</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>godo2027</t>
+          <t>kk_4755147673</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01075835624</t>
+          <t>01062968675</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>179139</t>
+          <t>301054</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4288079130</t>
+          <t>kk_3898041727</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01056697298</t>
+          <t>01091030227</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>275750</t>
+          <t>267643</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>chelius</t>
+          <t>kmhjm</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01024880126</t>
+          <t>01095316235</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>300985</t>
+          <t>181953</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>optimal11</t>
+          <t>ko7417</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01083258827</t>
+          <t>01041821439</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>129148</t>
+          <t>21776</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3178,51 +3178,51 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>jinny6716</t>
+          <t>kk_4310987668</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01039376458</t>
+          <t>01027962045</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>95121</t>
+          <t>277132</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4839929131</t>
+          <t>scubaktk</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01044408612</t>
+          <t>01028951833</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>304116</t>
+          <t>51328</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3232,51 +3232,51 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4525960790</t>
+          <t>godo2027</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01084170327</t>
+          <t>01075835624</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>286541</t>
+          <t>179139</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_3795672557</t>
+          <t>kk_2975660270</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01091179346</t>
+          <t>01065565496</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>257697</t>
+          <t>217640</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3286,24 +3286,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4282126610</t>
+          <t>comic0828</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01037415807</t>
+          <t>01096390888</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>275374</t>
+          <t>140326</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3313,51 +3313,51 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4217088689</t>
+          <t>scp0103</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01077710204</t>
+          <t>01033083314</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>272648</t>
+          <t>214558</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>haein607</t>
+          <t>kk_3795672557</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01023369606</t>
+          <t>01091179346</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>151209</t>
+          <t>257697</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3374,17 +3374,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>hansoi93</t>
+          <t>kk_4443559736</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01072262346</t>
+          <t>01064021269</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>60217</t>
+          <t>282199</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3394,24 +3394,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0331</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>scp0103</t>
+          <t>kk_3901736373</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01033083314</t>
+          <t>01072562998</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>214558</t>
+          <t>267789</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3421,51 +3421,51 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_2975660270</t>
+          <t>kk_3943654079</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01065565496</t>
+          <t>01053762357</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>217640</t>
+          <t>269510</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_3246970011</t>
+          <t>delta12</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01080703392</t>
+          <t>01071339709</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>235053</t>
+          <t>192352</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3482,17 +3482,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>jeshurun76</t>
+          <t>kk_4508257846</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01051236012</t>
+          <t>01092499867</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>191849</t>
+          <t>285541</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3502,51 +3502,51 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4475486602</t>
+          <t>goppagi</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01041949661</t>
+          <t>01052632529</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>284059</t>
+          <t>179049</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kmhjm</t>
+          <t>kk_4634804186</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01095316235</t>
+          <t>01089506651</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>181953</t>
+          <t>292029</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3556,24 +3556,24 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>kk_4282126610</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01092690887</t>
+          <t>01037415807</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>303428</t>
+          <t>275374</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3590,44 +3590,44 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>wlcnstjs12</t>
+          <t>kbh2639</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01040240293</t>
+          <t>01026514411</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>149195</t>
+          <t>159679</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_3774156950</t>
+          <t>optimal11</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01041159966</t>
+          <t>01083258827</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>255778</t>
+          <t>129148</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3644,130 +3644,130 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3898041727</t>
+          <t>kk_3825294168</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01091030227</t>
+          <t>01076290208</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>267643</t>
+          <t>263146</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>sbstkd</t>
+          <t>kk_4839929131</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01084506080</t>
+          <t>01044408612</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>137269</t>
+          <t>304116</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>plus7431</t>
+          <t>kk_4610571768</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01084748664</t>
+          <t>01094092580</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>251388</t>
+          <t>290026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kbh2639</t>
+          <t>kk_3801427305</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01026514411</t>
+          <t>01097820998</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>159679</t>
+          <t>259073</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>goppagi</t>
+          <t>ferix1999</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01052632529</t>
+          <t>01026339659</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>179049</t>
+          <t>191848</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3779,44 +3779,44 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4755147673</t>
+          <t>kk_3774156950</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01062968675</t>
+          <t>01041159966</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>301054</t>
+          <t>255778</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>scubaktk</t>
+          <t>haein607</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01028951833</t>
+          <t>01023369606</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>51328</t>
+          <t>151209</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3826,159 +3826,159 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>luvsena</t>
+          <t>wlcnstjs12</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01089625349</t>
+          <t>01040240293</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>172100</t>
+          <t>149195</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4610571768</t>
+          <t>kk_4288079130</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01094092580</t>
+          <t>01056697298</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>290026</t>
+          <t>275750</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ko7417</t>
+          <t>kk_3718281230</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01041821439</t>
+          <t>01067711528</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>21776</t>
+          <t>252078</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_3718281230</t>
+          <t>jinny6716</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01067711528</t>
+          <t>01039376458</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>252078</t>
+          <t>95121</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_3456892694</t>
+          <t>kk_4838385004</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01057443264</t>
+          <t>01088158446</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>243269</t>
+          <t>304048</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>junghyunpak</t>
+          <t>chunsadl</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01028120688</t>
+          <t>01087804011</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>58618</t>
+          <t>167610</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3988,78 +3988,78 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4634804186</t>
+          <t>kk_4525960790</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01089506651</t>
+          <t>01084170327</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>292029</t>
+          <t>286541</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4838385004</t>
+          <t>kk_3246970011</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01088158446</t>
+          <t>01080703392</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>304048</t>
+          <t>235053</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>comic0828</t>
+          <t>kk_3456892694</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01096390888</t>
+          <t>01057443264</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>140326</t>
+          <t>243269</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4069,105 +4069,105 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_3825294168</t>
+          <t>jeshurun76</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01076290208</t>
+          <t>01051236012</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>263146</t>
+          <t>191849</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>delta12</t>
+          <t>plus7431</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01071339709</t>
+          <t>01084748664</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>192352</t>
+          <t>251388</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4310987668</t>
+          <t>tinykim</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01027962045</t>
+          <t>01035630719</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>277132</t>
+          <t>65922</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_3943654079</t>
+          <t>kk_4828776483</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01053762357</t>
+          <t>01092690887</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>269510</t>
+          <t>303428</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4177,51 +4177,51 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4440711181</t>
+          <t>kk_4475486602</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01063263543</t>
+          <t>01041949661</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>282110</t>
+          <t>284059</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_3901736373</t>
+          <t>chelius</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01072562998</t>
+          <t>01024880126</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>267789</t>
+          <t>300985</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4231,105 +4231,105 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>kk_3465759734</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01045550499</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>303885</t>
+          <t>243732</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_3694865986</t>
+          <t>hjh3127</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01083470708</t>
+          <t>01054261891</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>251070</t>
+          <t>52538</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_3631606950</t>
+          <t>kk_3776403631</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01063256163</t>
+          <t>01034755755</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>248164</t>
+          <t>255908</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>eccomi21</t>
+          <t>colorum</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01084717525</t>
+          <t>01054844416</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>143557</t>
+          <t>146276</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4339,24 +4339,24 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_3798545067</t>
+          <t>kk_4838514193</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01023751319</t>
+          <t>01028513978</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>258449</t>
+          <t>304057</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4366,78 +4366,78 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4530117802</t>
+          <t>kk_4835826103</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01094437239</t>
+          <t>01082133090</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>286792</t>
+          <t>303894</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4825242022</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01025208267</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>303235</t>
+          <t>304107</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_3776403631</t>
+          <t>kk_4672701053</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01034755755</t>
+          <t>01088807653</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>255908</t>
+          <t>294426</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4447,240 +4447,240 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>jth0122</t>
+          <t>kk_3766082784</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01088989856</t>
+          <t>01092342302</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>96490</t>
+          <t>255139</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4838635909</t>
+          <t>kk_3631606950</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01098131007</t>
+          <t>01063256163</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>304064</t>
+          <t>248164</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_3633964155</t>
+          <t>kslee9011</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01097743709</t>
+          <t>01031716463</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>248300</t>
+          <t>48237</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4835826103</t>
+          <t>kk_4835837819</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01082133090</t>
+          <t>01044119822</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>303894</t>
+          <t>303896</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>pkd2001</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01043345927</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>304098</t>
+          <t>169815</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>lynx246</t>
+          <t>kk_3694865986</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01041241323</t>
+          <t>01083470708</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>196113</t>
+          <t>251070</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_3913679442</t>
+          <t>kkemc11</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01085569215</t>
+          <t>01072822359</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>268330</t>
+          <t>224851</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4212123801</t>
+          <t>kk_3798545067</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01083862682</t>
+          <t>01023751319</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>272414</t>
+          <t>258449</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kimchhgood</t>
+          <t>kk_3601774804</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01092133961</t>
+          <t>01046513357</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>247059</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4690,51 +4690,51 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_4681484279</t>
+          <t>kk_3804201157</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01022642776</t>
+          <t>01055152547</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>294947</t>
+          <t>259728</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4720019874</t>
+          <t>myjjangga</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01052578634</t>
+          <t>01083364898</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>297465</t>
+          <t>87940</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4744,213 +4744,213 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>tomcurse02</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01022070282</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>304107</t>
+          <t>96444</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>jment1983</t>
+          <t>whtjdfo11</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01088991983</t>
+          <t>01075377523</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>271329</t>
+          <t>185516</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_3804201157</t>
+          <t>kk_4835267037</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01055152547</t>
+          <t>01047143494</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>259728</t>
+          <t>303847</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4839598883</t>
+          <t>kk_3913679442</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01032207906</t>
+          <t>01085569215</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>304105</t>
+          <t>268330</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4835267037</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01047143494</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>303847</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>287573</t>
+          <t>280163</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>tkfkdtmfjs79</t>
+          <t>kk_4840238333</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01044809033</t>
+          <t>01087443182</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>153239</t>
+          <t>304135</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_3775794718</t>
+          <t>kk_4464127061</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01085983536</t>
+          <t>01073655835</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>255860</t>
+          <t>283300</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4960,78 +4960,78 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_3766082784</t>
+          <t>kk_4720019874</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01092342302</t>
+          <t>01052578634</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>255139</t>
+          <t>297465</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_2999650964</t>
+          <t>kk_3793412568</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01073667501</t>
+          <t>01049200546</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>218535</t>
+          <t>257211</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>fimajun</t>
+          <t>ohey2003</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01035668051</t>
+          <t>01034151656</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>230171</t>
+          <t>116157</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5041,24 +5041,24 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_3601774804</t>
+          <t>kk_4825242022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01046513357</t>
+          <t>01025208267</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>247059</t>
+          <t>303235</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
@@ -5102,17 +5102,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_4840238333</t>
+          <t>csnoopy</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01087443182</t>
+          <t>01063730741</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>304135</t>
+          <t>110007</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5122,24 +5122,24 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_2989316682</t>
+          <t>kk_2999650964</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01037375641</t>
+          <t>01073667501</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>218263</t>
+          <t>218535</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5149,78 +5149,78 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>bizboard</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>csnoopy</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01063730741</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>110007</t>
+          <t>287573</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kk_4838748515</t>
+          <t>kk_3633964155</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01034435700</t>
+          <t>01097743709</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>304070</t>
+          <t>248300</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_4838514193</t>
+          <t>anirim</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01028513978</t>
+          <t>01026146239</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>304057</t>
+          <t>303897</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5230,51 +5230,51 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kk_4478716748</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01071630157</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>284194</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>colorum</t>
+          <t>kk_3775794718</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01054844416</t>
+          <t>01085983536</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>146276</t>
+          <t>255860</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
@@ -5318,103 +5318,103 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kk_3793412568</t>
+          <t>kk_4612713787</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01049200546</t>
+          <t>01095027601</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>257211</t>
+          <t>290278</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4819536073</t>
+          <t>lynx246</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01039113089</t>
+          <t>01041241323</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>302942</t>
+          <t>196113</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>kk_4838748515</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01034435700</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>164951</t>
+          <t>304070</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4672701053</t>
+          <t>jment1983</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01088807653</t>
+          <t>01088991983</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>294426</t>
+          <t>271329</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -5426,17 +5426,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>water4853</t>
+          <t>kk_4446020087</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01020542351</t>
+          <t>01089773053</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>178866</t>
+          <t>282273</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5446,105 +5446,105 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_4839598883</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01032207906</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>304105</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>soojst</t>
+          <t>kk_3258483317</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01097431003</t>
+          <t>01075584654</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>209447</t>
+          <t>235788</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>raneelim</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01051598929</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>72197</t>
+          <t>304098</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>kk_4344215691</t>
+          <t>water4853</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01020192399</t>
+          <t>01020542351</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>279044</t>
+          <t>178866</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5554,24 +5554,24 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>kk_3736097865</t>
+          <t>kimchhgood</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01089447248</t>
+          <t>01092133961</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>253356</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5581,24 +5581,24 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kslee9011</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01031716463</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>48237</t>
+          <t>303885</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5608,51 +5608,51 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>anirim</t>
+          <t>kk_4819536073</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01026146239</t>
+          <t>01039113089</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>303897</t>
+          <t>302942</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>kk_4222073058</t>
+          <t>kk_2989316682</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01046077586</t>
+          <t>01037375641</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>272870</t>
+          <t>218263</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5662,51 +5662,51 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>kk_3465759734</t>
+          <t>soojst</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01045550499</t>
+          <t>01097431003</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>243732</t>
+          <t>209447</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>kk_4464127061</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01073655835</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>283300</t>
+          <t>164951</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5723,44 +5723,44 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>kk_4446020087</t>
+          <t>kk_4478716748</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01089773053</t>
+          <t>01071630157</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>282273</t>
+          <t>284194</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>myjjangga</t>
+          <t>kk_3736097865</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01083364898</t>
+          <t>01089447248</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>87940</t>
+          <t>253356</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5770,24 +5770,24 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kkemc11</t>
+          <t>kk_4703414773</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01072822359</t>
+          <t>01093547510</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>224851</t>
+          <t>296108</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5797,24 +5797,24 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_4703414773</t>
+          <t>kk_4222073058</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01093547510</t>
+          <t>01046077586</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>296108</t>
+          <t>272870</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5824,24 +5824,24 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>tomcurse02</t>
+          <t>kk_4530117802</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01022070282</t>
+          <t>01094437239</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>96444</t>
+          <t>286792</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ohey2003</t>
+          <t>kk_4212123801</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01034151656</t>
+          <t>01083862682</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>116157</t>
+          <t>272414</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5878,24 +5878,24 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>kk_3258483317</t>
+          <t>kk_4344215691</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01075584654</t>
+          <t>01020192399</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>235788</t>
+          <t>279044</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5905,24 +5905,24 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>hjh3127</t>
+          <t>tkfkdtmfjs79</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01054261891</t>
+          <t>01044809033</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>52538</t>
+          <t>153239</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5932,24 +5932,24 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>whtjdfo11</t>
+          <t>fimajun</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01075377523</t>
+          <t>01035668051</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>185516</t>
+          <t>230171</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5959,24 +5959,24 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>pkd2001</t>
+          <t>eccomi21</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01043345927</t>
+          <t>01084717525</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>169815</t>
+          <t>143557</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5986,78 +5986,78 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>kk_4681484279</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01022642776</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>280163</t>
+          <t>294947</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>kk_4835837819</t>
+          <t>kk_4838635909</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01044119822</t>
+          <t>01098131007</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>303896</t>
+          <t>304064</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_4612713787</t>
+          <t>raneelim</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01095027601</t>
+          <t>01051598929</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>290278</t>
+          <t>72197</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6067,78 +6067,78 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>jth0122</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01088989856</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>96490</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>219525</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kk_3466706406</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01055441553</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>243779</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6155,17 +6155,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_4288273717</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01020746624</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>275762</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6182,17 +6182,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>kk_3501053454</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01093015628</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>270708</t>
+          <t>245323</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6202,51 +6202,51 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>kk_4839821563</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01027951809</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>304112</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>143826</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6256,105 +6256,105 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>kk_2950194486</t>
+          <t>kk_4357899204</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>01076104875</t>
+          <t>01082772838</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>216766</t>
+          <t>279564</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>seopme</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>01074122238</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>304125</t>
+          <t>270708</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>kk_4237700483</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01063041087</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>219525</t>
+          <t>273719</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>kyong74</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01088245591</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>279909</t>
+          <t>22857</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6371,98 +6371,98 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>kk_4840174486</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>01064087457</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>304131</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>136050</t>
+          <t>268974</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>304104</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>kk_4517851709</t>
+          <t>jung1481</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>01066445714</t>
+          <t>01024193371</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>286074</t>
+          <t>205735</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6479,98 +6479,98 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>fjsjhw</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>01050468291</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>192240</t>
+          <t>304100</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>292319</t>
+          <t>285491</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>kk_4839542021</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01089909663</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>304103</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6587,17 +6587,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>jung1481</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>01024193371</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>205735</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6614,44 +6614,44 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>kk_3134493871</t>
+          <t>kk_4840174486</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>01035918800</t>
+          <t>01064087457</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>222420</t>
+          <t>304131</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -6661,51 +6661,51 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>304124</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>kk_3796517297</t>
+          <t>kk_3134493871</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>01040802850</t>
+          <t>01035918800</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>257878</t>
+          <t>222420</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6715,24 +6715,24 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>304101</t>
+          <t>292319</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -6742,24 +6742,24 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>kk_3501053454</t>
+          <t>jsu2080</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>01093015628</t>
+          <t>01094582080</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>245323</t>
+          <t>275256</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -6769,24 +6769,24 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>jinoh</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>01024150539</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>270445</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6803,98 +6803,98 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>jeonhyel</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01077942894</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>285491</t>
+          <t>304102</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>kk_4839765445</t>
+          <t>kk_4840035519</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>01076118972</t>
+          <t>01086385010</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>304111</t>
+          <t>304121</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>kk_4212258541</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>01047138543</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>272420</t>
+          <t>304126</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6911,98 +6911,98 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>kk_3750120343</t>
+          <t>chlwoghk83</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>01092908890</t>
+          <t>01038851983</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>254168</t>
+          <t>145712</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>298138</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>kk_4838920250</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>01065688860</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>304074</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -7012,51 +7012,51 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>kk_4221652535</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01036858276</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>123130</t>
+          <t>272849</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>kk_3678962368</t>
+          <t>kk_3220401027</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>01041028567</t>
+          <t>01037591063</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>250374</t>
+          <t>232602</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -7066,78 +7066,78 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0413</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>186218</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>kk_4839283126</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>01024419045</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>304093</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>byun7707</t>
+          <t>kk_3794951359</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>01077391740</t>
+          <t>01066481842</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>161371</t>
+          <t>257520</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -7181,17 +7181,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>richjm</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01082909799</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>122482</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -7208,44 +7208,44 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>304129</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>kk_2985598511</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01086703302</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>218005</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -7262,17 +7262,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>kk_3796517297</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01040802850</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>257878</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -7289,17 +7289,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>kk_4727505000</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>01066573797</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>298110</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -7309,51 +7309,51 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>kk_4212157104</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01062437191</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>272417</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>maksim04</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01063557978</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>202013</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7370,152 +7370,152 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>kk_4357899204</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>01082772838</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>279564</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>kk_2985598511</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>01086703302</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>218005</t>
+          <t>227343</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>js0987</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01052819790</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>110955</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>kk_4840035519</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>01086385010</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>304121</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>kk_4484370599</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01052246899</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>284447</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -7532,44 +7532,44 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>140860</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>varam11</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01071373327</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>102004</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -7579,159 +7579,159 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0413</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>jeonhyel</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>01077942894</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>304102</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>kk_4670878863</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>01067207833</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>294326</t>
+          <t>68751</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>kk_2915134680</t>
+          <t>mooner82</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>01085224711</t>
+          <t>01037861045</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>215670</t>
+          <t>148696</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>kk_4212157104</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>01062437191</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>272417</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>219219</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7748,17 +7748,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>kk_4839027252</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01084518813</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>68751</t>
+          <t>304083</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -7768,105 +7768,105 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>219219</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ganjing78</t>
+          <t>kk_4839283126</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>01065121424</t>
+          <t>01024419045</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>78590</t>
+          <t>304093</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>kk_4839241951</t>
+          <t>kk_4727505000</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>01079146776</t>
+          <t>01066573797</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>304090</t>
+          <t>298110</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>kk_4237700483</t>
+          <t>isaackwak</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>01063041087</t>
+          <t>01090599860</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>273719</t>
+          <t>275913</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7883,98 +7883,98 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>304129</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>hhpp123</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01042621121</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>268974</t>
+          <t>294450</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>isaackwak</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>01090599860</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>275913</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>kk_4536846819</t>
+          <t>chaser1</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>01038223781</t>
+          <t>01038304145</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>287146</t>
+          <t>178090</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7991,17 +7991,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>kk_4680971786</t>
+          <t>he0218</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>01074443726</t>
+          <t>01049289998</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>294917</t>
+          <t>254710</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -8011,78 +8011,78 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>richjm</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>01082909799</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>122482</t>
+          <t>123130</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>162562</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8099,17 +8099,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>kk_3678962368</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01041028567</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>140860</t>
+          <t>250374</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8126,44 +8126,44 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>hhpp123</t>
+          <t>kk_3466706406</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>01042621121</t>
+          <t>01055441553</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>294450</t>
+          <t>243779</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8180,17 +8180,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>kk_4375333989</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>01091513985</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>280145</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8200,24 +8200,24 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>143826</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8227,240 +8227,240 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>304113</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>mooner82</t>
+          <t>kk_3750120343</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>01037861045</t>
+          <t>01092908890</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>148696</t>
+          <t>254168</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>kk_4212258541</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01047138543</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>272420</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>motamsi</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01090344665</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>96716</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>coverdn</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01086426866</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>304100</t>
+          <t>172406</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0413</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>js0987</t>
+          <t>kk_2950194486</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>01052819790</t>
+          <t>01076104875</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>110955</t>
+          <t>216766</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>kk_4839821563</t>
+          <t>kk_3170564464</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>01027951809</t>
+          <t>01099188001</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>304112</t>
+          <t>224948</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>kwon9493</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>01035589493</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>208245</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>172790</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8477,44 +8477,44 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>kk_4838947856</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>01094709458</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>304075</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>he0218</t>
+          <t>kk_2915134680</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>01049289998</t>
+          <t>01085224711</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>254710</t>
+          <t>215670</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8524,24 +8524,24 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>kk_3960572616</t>
+          <t>kk_4538201048</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>01072737379</t>
+          <t>01071790372</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>270384</t>
+          <t>287217</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8558,17 +8558,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>jsu2080</t>
+          <t>kk_3960572616</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>01094582080</t>
+          <t>01072737379</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>275256</t>
+          <t>270384</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8585,17 +8585,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>hodong1014</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01044530048</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>64397</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8605,24 +8605,24 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>chaser1</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>01038304145</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>178090</t>
+          <t>180321</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8666,44 +8666,44 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>kk_4536846819</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01038223781</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>287146</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8720,17 +8720,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>hodong1014</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>01044530048</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>64397</t>
+          <t>221630</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8747,17 +8747,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>kk_4680971786</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01074443726</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>294917</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8774,17 +8774,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>kk_4288273717</t>
+          <t>fjsjhw</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>01020746624</t>
+          <t>01050468291</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>275762</t>
+          <t>192240</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8794,24 +8794,24 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8828,71 +8828,71 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>174291</t>
+          <t>304109</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>kk_4538201048</t>
+          <t>kk_4839241951</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>01071790372</t>
+          <t>01079146776</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>287217</t>
+          <t>304090</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>varam11</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>01071373327</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>102004</t>
+          <t>136050</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8902,24 +8902,24 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>kk_4670878863</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01067207833</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>294326</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8936,17 +8936,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>227343</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8963,17 +8963,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>maksim04</t>
+          <t>kk_4517851709</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>01063557978</t>
+          <t>01066445714</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>202013</t>
+          <t>286074</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8990,17 +8990,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>180321</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9017,44 +9017,44 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>kk_4839027252</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>01084518813</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>304083</t>
+          <t>174291</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>coverdn</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>01086426866</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>172406</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9064,78 +9064,78 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>kk_4221652535</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>01036858276</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>272849</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>chlwoghk83</t>
+          <t>seopme</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>01038851983</t>
+          <t>01074122238</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>145712</t>
+          <t>304125</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9145,78 +9145,78 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>kk_4838920250</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01065688860</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>304074</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>motamsi</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>01090344665</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>96716</t>
+          <t>275998</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>kk_4839542021</t>
+          <t>kk_4838947856</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>01089909663</t>
+          <t>01094709458</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>304103</t>
+          <t>304075</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9226,24 +9226,24 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>jinoh</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01024150539</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>270445</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9260,71 +9260,71 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>kk_3380246984</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>01040750851</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>240492</t>
+          <t>304086</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>ganjing78</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01065121424</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>78590</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9341,44 +9341,44 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>kk_4484370599</t>
+          <t>kwon9493</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>01052246899</t>
+          <t>01035589493</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>284447</t>
+          <t>107077</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>229454</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -9395,17 +9395,17 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>kk_3380246984</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01040750851</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>240492</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9422,17 +9422,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>kk_3794951359</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>01066481842</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>257520</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9442,78 +9442,78 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>kk_3170564464</t>
+          <t>byun7707</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>01099188001</t>
+          <t>01077391740</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>224948</t>
+          <t>161371</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>304086</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>279909</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9530,17 +9530,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9550,78 +9550,78 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>229454</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>kk_3220401027</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>01037591063</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>232602</t>
+          <t>304101</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>221630</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9638,98 +9638,98 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>kk_4839765445</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01076118972</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>289364</t>
+          <t>304104</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>304126</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>kyong74</t>
+          <t>kk_4375333989</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>01088245591</t>
+          <t>01091513985</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>22857</t>
+          <t>280145</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -593,17 +593,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_3182623010</t>
+          <t>kig0268</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01094128645</t>
+          <t>01053928207</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>227908</t>
+          <t>301007</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -613,24 +613,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kig0268</t>
+          <t>kk_3182623010</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01053928207</t>
+          <t>01094128645</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>301007</t>
+          <t>227908</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -640,61 +640,61 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_3407332090</t>
+          <t>kk_3789625265</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01073480423</t>
+          <t>01029773942</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>241393</t>
+          <t>256664</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_3789625265</t>
+          <t>kk_3407332090</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01029773942</t>
+          <t>01073480423</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>256664</t>
+          <t>241393</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -782,27 +782,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>joohpark87</t>
+          <t>kk_3243338539</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01062437622</t>
+          <t>01025098649</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>121373</t>
+          <t>234832</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -863,27 +863,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kk_3243338539</t>
+          <t>joohpark87</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01025098649</t>
+          <t>01062437622</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>234832</t>
+          <t>121373</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -917,17 +917,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hbnetsys</t>
+          <t>kk_3794046073</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01052810852</t>
+          <t>01056918495</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>282445</t>
+          <t>257320</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_3794046073</t>
+          <t>hbnetsys</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01056918495</t>
+          <t>01052810852</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>257320</t>
+          <t>282445</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -991,24 +991,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cutebear88</t>
+          <t>justicek73</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01039942456</t>
+          <t>01033270931</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>212858</t>
+          <t>237394</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1018,24 +1018,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>justicek73</t>
+          <t>kk_4493450118</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01033270931</t>
+          <t>01077566800</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>237394</t>
+          <t>284909</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1052,17 +1052,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_4493450118</t>
+          <t>cutebear88</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01077566800</t>
+          <t>01039942456</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>284909</t>
+          <t>212858</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
         </is>
       </c>
     </row>
@@ -1106,44 +1106,44 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_3340113031</t>
+          <t>gbk888</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01098338138</t>
+          <t>01063271523</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>239100</t>
+          <t>264430</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>darius27</t>
+          <t>kk_4226246986</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01091911224</t>
+          <t>01048263393</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>292238</t>
+          <t>273085</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_3692762833</t>
+          <t>namki9545</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01087630523</t>
+          <t>01073099545</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>250938</t>
+          <t>27441</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1180,51 +1180,51 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gbk888</t>
+          <t>kk_2850432473</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01063271523</t>
+          <t>01026771240</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>264430</t>
+          <t>213403</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pkcomon</t>
+          <t>jung9916</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01063208976</t>
+          <t>01091576210</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>198932</t>
+          <t>171554</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1234,24 +1234,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_2850432473</t>
+          <t>kk_3959240760</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01026771240</t>
+          <t>01035045875</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>213403</t>
+          <t>270320</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1261,51 +1261,51 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_3628696638_2</t>
+          <t>darius27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01038262132</t>
+          <t>01091911224</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>302884</t>
+          <t>292238</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_4291314607</t>
+          <t>kk_2760596791</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01088119636</t>
+          <t>01087827701</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>275953</t>
+          <t>208450</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1315,51 +1315,51 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_3338448571</t>
+          <t>astro77</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01050068417</t>
+          <t>01091518663</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>239011</t>
+          <t>167514</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>120212705670680427</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_3959240760</t>
+          <t>kk_4291314607</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01035045875</t>
+          <t>01088119636</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>270320</t>
+          <t>275953</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1369,51 +1369,51 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_4226246986</t>
+          <t>kk_3628696638_2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01048263393</t>
+          <t>01038262132</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>273085</t>
+          <t>302884</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>jung9916</t>
+          <t>pkcomon</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01091576210</t>
+          <t>01063208976</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>171554</t>
+          <t>198932</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1423,24 +1423,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>namki9545</t>
+          <t>kk_3692762833</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01073099545</t>
+          <t>01087630523</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>27441</t>
+          <t>250938</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1450,51 +1450,51 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>astro77</t>
+          <t>kk_3340113031</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01091518663</t>
+          <t>01098338138</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>167514</t>
+          <t>239100</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_2760596791</t>
+          <t>kk_3338448571</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01087827701</t>
+          <t>01050068417</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>208450</t>
+          <t>239011</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1504,105 +1504,105 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_3793101024</t>
+          <t>kk_4790899014</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01082844287</t>
+          <t>01024708415</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>257080</t>
+          <t>302058</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>leecs11124</t>
+          <t>kk_4828047673</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01037870639</t>
+          <t>01087502319</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>260560</t>
+          <t>303388</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_4201661917</t>
+          <t>kk_3241814751</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01052228247</t>
+          <t>01048808215</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>271984</t>
+          <t>234712</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4837990320</t>
+          <t>kk_2783594999</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01024175652</t>
+          <t>01095317357</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>304030</t>
+          <t>209807</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1612,24 +1612,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>juhan3489</t>
+          <t>leecs11124</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01037693092</t>
+          <t>01037870639</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>214043</t>
+          <t>260560</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1639,24 +1639,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0214</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_3795564177</t>
+          <t>kk_4838420487</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01044552859</t>
+          <t>01050618241</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>257673</t>
+          <t>304051</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1673,233 +1673,233 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_4743669054</t>
+          <t>aram2016</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01036749627</t>
+          <t>01071670785</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>300361</t>
+          <t>225250</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>djmin57</t>
+          <t>kk_3795564177</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01034585986</t>
+          <t>01044552859</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>52890</t>
+          <t>257673</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_3097460767</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01085815097</t>
+          <t>01048597145</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>303542</t>
+          <t>221400</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_3241814751</t>
+          <t>kk_4694268987</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01048808215</t>
+          <t>01025088964</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>234712</t>
+          <t>295680</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_2783594999</t>
+          <t>stonehinge</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01095317357</t>
+          <t>01027275105</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>209807</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>lms_ecom_0401_springhiking</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4278011504</t>
+          <t>kk_4201661917</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01045289321</t>
+          <t>01052228247</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>275167</t>
+          <t>271984</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4746910410</t>
+          <t>kk_4837990320</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01047502488</t>
+          <t>01024175652</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>300629</t>
+          <t>304030</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4838420487</t>
+          <t>kk_3827025148</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01050618241</t>
+          <t>01090399900</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>304051</t>
+          <t>263356</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>stonehinge</t>
+          <t>kk_3793101024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01027275105</t>
+          <t>01082844287</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>257080</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1909,105 +1909,105 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>lms_ecom_0401_springhiking</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>aram2016</t>
+          <t>kk_4746910410</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01071670785</t>
+          <t>01047502488</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>225250</t>
+          <t>300629</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4790899014</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01024708415</t>
+          <t>01085815097</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>302058</t>
+          <t>303542</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_4828047673</t>
+          <t>djmin57</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01087502319</t>
+          <t>01034585986</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>303388</t>
+          <t>52890</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_3097460767</t>
+          <t>kk_4278011504</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01048597145</t>
+          <t>01045289321</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>221400</t>
+          <t>275167</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2017,78 +2017,78 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_2762251625</t>
+          <t>kk_4509280340</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01032085585</t>
+          <t>01088521558</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>208548</t>
+          <t>285569</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_3827025148</t>
+          <t>kk_4743669054</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01090399900</t>
+          <t>01036749627</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>263356</t>
+          <t>300361</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4509280340</t>
+          <t>juhan3489</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01088521558</t>
+          <t>01037693092</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>285569</t>
+          <t>214043</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2098,51 +2098,51 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4694268987</t>
+          <t>kk_2762251625</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01025088964</t>
+          <t>01032085585</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>295680</t>
+          <t>208548</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_3186268807</t>
+          <t>kk_4285105163</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01055175130</t>
+          <t>01083283220</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>230244</t>
+          <t>275559</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2152,105 +2152,105 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jcahn12</t>
+          <t>endruns</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01038358052</t>
+          <t>01020716852</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>59346</t>
+          <t>176346</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>endruns</t>
+          <t>abejung</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01020716852</t>
+          <t>01023320007</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>176346</t>
+          <t>158025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>joocho629</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01038056919</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>162948</t>
+          <t>244619</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>EDM_0224</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_3203549435</t>
+          <t>jcahn12</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01033608209</t>
+          <t>01038358052</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>230719</t>
+          <t>59346</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
@@ -2321,17 +2321,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4614762502</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01064155845</t>
+          <t>01083936762</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>290560</t>
+          <t>303728</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2348,44 +2348,44 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_3229351319</t>
+          <t>kk_3707105860</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01090969959</t>
+          <t>01059290508</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>233446</t>
+          <t>251625</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_3734181513</t>
+          <t>klim202</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01066389021</t>
+          <t>01064368836</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>253177</t>
+          <t>168762</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2395,24 +2395,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_3707105860</t>
+          <t>p7181</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01059290508</t>
+          <t>01056288360</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>251625</t>
+          <t>250858</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2422,51 +2422,51 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6941110100332</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4833493849</t>
+          <t>ssbok0806</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01083936762</t>
+          <t>01093267531</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>303728</t>
+          <t>223278</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>klim202</t>
+          <t>kk_3967220863</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01064368836</t>
+          <t>01087902066</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>168762</t>
+          <t>270700</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2476,24 +2476,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_3778874557</t>
+          <t>kk_3229351319</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01094017193</t>
+          <t>01090969959</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>256071</t>
+          <t>233446</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2503,159 +2503,159 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4299847976</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01091384892</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>276488</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>p7181</t>
+          <t>cgkrry</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01056288360</t>
+          <t>01085513271</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>250858</t>
+          <t>48578</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_3866200904</t>
+          <t>kk_4793026063</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01062556776</t>
+          <t>01072703070</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>265988</t>
+          <t>302125</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4285105163</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01083283220</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>275559</t>
+          <t>168147</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_3866200904</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01062556776</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>265988</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_3967220863</t>
+          <t>joocho629</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01087902066</t>
+          <t>01038056919</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>270700</t>
+          <t>162948</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2665,51 +2665,51 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0224</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_3734181513</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01066389021</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>253177</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_3290809343</t>
+          <t>kk_3186268807</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01057206001</t>
+          <t>01055175130</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>237059</t>
+          <t>230244</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2719,51 +2719,51 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_4793026063</t>
+          <t>kk_4837763007</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01072703070</t>
+          <t>01088993992</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>302125</t>
+          <t>304013</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4837763007</t>
+          <t>kk_3203549435</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01088993992</t>
+          <t>01033608209</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>304013</t>
+          <t>230719</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2773,105 +2773,105 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>kk_4299847976</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01091384892</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>168147</t>
+          <t>276488</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ssbok0806</t>
+          <t>kk_4614762502</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01093267531</t>
+          <t>01064155845</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>223278</t>
+          <t>290560</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>abejung</t>
+          <t>kk_3778874557</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01023320007</t>
+          <t>01094017193</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>158025</t>
+          <t>256071</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>cgkrry</t>
+          <t>kk_3290809343</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01085513271</t>
+          <t>01057206001</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>48578</t>
+          <t>237059</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2881,132 +2881,132 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>junghyunpak</t>
+          <t>kk_3825294168</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01028120688</t>
+          <t>01076290208</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>58618</t>
+          <t>263146</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>sbstkd</t>
+          <t>kk_4839929131</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01084506080</t>
+          <t>01044408612</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>137269</t>
+          <t>304116</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>hansoi93</t>
+          <t>kk_3943654079</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01072262346</t>
+          <t>01053762357</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>60217</t>
+          <t>269510</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>luvsena</t>
+          <t>kk_4755147673</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01089625349</t>
+          <t>01062968675</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>172100</t>
+          <t>301054</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>gilinim</t>
+          <t>junghyunpak</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01032351966</t>
+          <t>01028120688</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>302594</t>
+          <t>58618</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4440711181</t>
+          <t>kk_4610571768</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01063263543</t>
+          <t>01094092580</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>282110</t>
+          <t>290026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3043,105 +3043,105 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4217088689</t>
+          <t>kk_3901736373</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01077710204</t>
+          <t>01072562998</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>272648</t>
+          <t>267789</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4755147673</t>
+          <t>hansoi93</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01062968675</t>
+          <t>01072262346</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>301054</t>
+          <t>60217</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_3898041727</t>
+          <t>kk_4828776483</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01091030227</t>
+          <t>01092690887</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>267643</t>
+          <t>303428</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kmhjm</t>
+          <t>kk_4508257846</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01095316235</t>
+          <t>01092499867</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>181953</t>
+          <t>285541</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3151,88 +3151,88 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ko7417</t>
+          <t>kk_4525960790</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01041821439</t>
+          <t>01084170327</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>21776</t>
+          <t>286541</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4310987668</t>
+          <t>comic0828</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01027962045</t>
+          <t>01096390888</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>277132</t>
+          <t>140326</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>scubaktk</t>
+          <t>kk_4282126610</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01028951833</t>
+          <t>01037415807</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>51328</t>
+          <t>275374</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -3266,17 +3266,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_2975660270</t>
+          <t>haein607</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01065565496</t>
+          <t>01023369606</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>217640</t>
+          <t>151209</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3286,78 +3286,78 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>comic0828</t>
+          <t>jinny6716</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01096390888</t>
+          <t>01039376458</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>140326</t>
+          <t>95121</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>scp0103</t>
+          <t>kk_3898041727</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01033083314</t>
+          <t>01091030227</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>214558</t>
+          <t>267643</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_3795672557</t>
+          <t>scubaktk</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01091179346</t>
+          <t>01028951833</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>257697</t>
+          <t>51328</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3367,56 +3367,56 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4443559736</t>
+          <t>wlcnstjs12</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01064021269</t>
+          <t>01040240293</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>282199</t>
+          <t>149195</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>EDM_0331</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_3901736373</t>
+          <t>delta12</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01072562998</t>
+          <t>01071339709</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>267789</t>
+          <t>192352</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3428,44 +3428,44 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_3943654079</t>
+          <t>tinykim</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01053762357</t>
+          <t>01035630719</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>269510</t>
+          <t>65922</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>delta12</t>
+          <t>luvsena</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01071339709</t>
+          <t>01089625349</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>192352</t>
+          <t>172100</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3475,34 +3475,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4508257846</t>
+          <t>kk_4288079130</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01092499867</t>
+          <t>01056697298</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>285541</t>
+          <t>275750</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
     </row>
@@ -3563,17 +3563,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4282126610</t>
+          <t>kk_3456892694</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01037415807</t>
+          <t>01057443264</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>275374</t>
+          <t>243269</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3583,24 +3583,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kbh2639</t>
+          <t>kk_3774156950</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01026514411</t>
+          <t>01041159966</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>159679</t>
+          <t>255778</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3617,98 +3617,98 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>optimal11</t>
+          <t>kk_4310987668</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01083258827</t>
+          <t>01027962045</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>129148</t>
+          <t>277132</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3825294168</t>
+          <t>kk_4838385004</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01076290208</t>
+          <t>01088158446</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>263146</t>
+          <t>304048</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4839929131</t>
+          <t>sbstkd</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01044408612</t>
+          <t>01084506080</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>304116</t>
+          <t>137269</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4610571768</t>
+          <t>kk_2975660270</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01094092580</t>
+          <t>01065565496</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>290026</t>
+          <t>217640</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3725,71 +3725,71 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_3801427305</t>
+          <t>kbh2639</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01097820998</t>
+          <t>01026514411</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>259073</t>
+          <t>159679</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ferix1999</t>
+          <t>jeshurun76</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01026339659</t>
+          <t>01051236012</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>191848</t>
+          <t>191849</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_3774156950</t>
+          <t>kk_4440711181</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01041159966</t>
+          <t>01063263543</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>255778</t>
+          <t>282110</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3799,88 +3799,88 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>haein607</t>
+          <t>ferix1999</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01023369606</t>
+          <t>01026339659</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>151209</t>
+          <t>191848</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>wlcnstjs12</t>
+          <t>kmhjm</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01040240293</t>
+          <t>01095316235</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>149195</t>
+          <t>181953</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4288079130</t>
+          <t>kk_4443559736</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01056697298</t>
+          <t>01064021269</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>275750</t>
+          <t>282199</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>EDM_0331</t>
         </is>
       </c>
     </row>
@@ -3914,17 +3914,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>jinny6716</t>
+          <t>kk_3795672557</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01039376458</t>
+          <t>01091179346</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>95121</t>
+          <t>257697</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3934,78 +3934,78 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4838385004</t>
+          <t>optimal11</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01088158446</t>
+          <t>01083258827</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>304048</t>
+          <t>129148</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>chunsadl</t>
+          <t>kk_4475486602</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01087804011</t>
+          <t>01041949661</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>167610</t>
+          <t>284059</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4525960790</t>
+          <t>plus7431</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01084170327</t>
+          <t>01084748664</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>286541</t>
+          <t>251388</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4015,24 +4015,24 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_3246970011</t>
+          <t>kk_4217088689</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01080703392</t>
+          <t>01077710204</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>235053</t>
+          <t>272648</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4042,51 +4042,51 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_3456892694</t>
+          <t>chunsadl</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01057443264</t>
+          <t>01087804011</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>243269</t>
+          <t>167610</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>jeshurun76</t>
+          <t>kk_3246970011</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01051236012</t>
+          <t>01080703392</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>191849</t>
+          <t>235053</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4096,51 +4096,51 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>plus7431</t>
+          <t>ko7417</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01084748664</t>
+          <t>01041821439</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>251388</t>
+          <t>21776</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>tinykim</t>
+          <t>gilinim</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01035630719</t>
+          <t>01032351966</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>65922</t>
+          <t>302594</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4150,78 +4150,78 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>kk_3801427305</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01092690887</t>
+          <t>01097820998</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>303428</t>
+          <t>259073</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4475486602</t>
+          <t>chelius</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01041949661</t>
+          <t>01024880126</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>284059</t>
+          <t>300985</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>chelius</t>
+          <t>scp0103</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01024880126</t>
+          <t>01033083314</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>300985</t>
+          <t>214558</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4231,51 +4231,51 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_3465759734</t>
+          <t>jment1983</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01045550499</t>
+          <t>01088991983</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>243732</t>
+          <t>271329</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>hjh3127</t>
+          <t>colorum</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01054261891</t>
+          <t>01054844416</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>52538</t>
+          <t>146276</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4285,24 +4285,24 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_3776403631</t>
+          <t>kimchhgood</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01034755755</t>
+          <t>01092133961</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>255908</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4312,105 +4312,105 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>colorum</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01054844416</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>146276</t>
+          <t>303885</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_4838514193</t>
+          <t>kk_3793412568</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01028513978</t>
+          <t>01049200546</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>304057</t>
+          <t>257211</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4835826103</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01082133090</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>303894</t>
+          <t>164951</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kk_4838748515</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01034435700</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>304107</t>
+          <t>304070</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4420,24 +4420,24 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4672701053</t>
+          <t>kk_4612713787</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01088807653</t>
+          <t>01095027601</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>294426</t>
+          <t>290278</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4447,78 +4447,78 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_3766082784</t>
+          <t>kk_4222073058</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01092342302</t>
+          <t>01046077586</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>255139</t>
+          <t>272870</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_3631606950</t>
+          <t>kk_2999650964</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01063256163</t>
+          <t>01073667501</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>248164</t>
+          <t>218535</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>bizboard</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kslee9011</t>
+          <t>kk_3798545067</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01031716463</t>
+          <t>01023751319</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>48237</t>
+          <t>258449</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4528,24 +4528,24 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4835837819</t>
+          <t>kk_4672701053</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01044119822</t>
+          <t>01088807653</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>303896</t>
+          <t>294426</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4555,24 +4555,24 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>pkd2001</t>
+          <t>kkemc11</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01043345927</t>
+          <t>01072822359</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>169815</t>
+          <t>224851</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4582,51 +4582,51 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_3694865986</t>
+          <t>kk_4681484279</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01083470708</t>
+          <t>01022642776</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>251070</t>
+          <t>294947</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kkemc11</t>
+          <t>eccomi21</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01072822359</t>
+          <t>01084717525</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>224851</t>
+          <t>143557</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4636,51 +4636,51 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_3798545067</t>
+          <t>kk_4819536073</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01023751319</t>
+          <t>01039113089</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>258449</t>
+          <t>302942</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_3601774804</t>
+          <t>kk_4464127061</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01046513357</t>
+          <t>01073655835</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>247059</t>
+          <t>283300</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4690,24 +4690,24 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_3804201157</t>
+          <t>kk_3776403631</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01055152547</t>
+          <t>01034755755</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>259728</t>
+          <t>255908</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4724,17 +4724,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>myjjangga</t>
+          <t>kk_4212123801</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01083364898</t>
+          <t>01083862682</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>87940</t>
+          <t>272414</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4744,24 +4744,24 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tomcurse02</t>
+          <t>kk_4703414773</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01022070282</t>
+          <t>01093547510</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>96444</t>
+          <t>296108</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4771,186 +4771,186 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>whtjdfo11</t>
+          <t>kk_3766082784</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01075377523</t>
+          <t>01092342302</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>185516</t>
+          <t>255139</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_4835267037</t>
+          <t>water4853</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01047143494</t>
+          <t>01020542351</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>303847</t>
+          <t>178866</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_3913679442</t>
+          <t>lynx246</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01085569215</t>
+          <t>01041241323</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>268330</t>
+          <t>196113</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>whtjdfo11</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01075377523</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>185516</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>kk_3694865986</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01083470708</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>280163</t>
+          <t>251070</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kk_4840238333</t>
+          <t>myjjangga</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01087443182</t>
+          <t>01083364898</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>304135</t>
+          <t>87940</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_4464127061</t>
+          <t>kk_3775794718</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01073655835</t>
+          <t>01085983536</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>283300</t>
+          <t>255860</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4960,24 +4960,24 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_4720019874</t>
+          <t>kk_4838646680</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01052578634</t>
+          <t>01034311248</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>297465</t>
+          <t>304066</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4987,78 +4987,78 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>[pf]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_3793412568</t>
+          <t>kk_3804201157</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01049200546</t>
+          <t>01055152547</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>257211</t>
+          <t>259728</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ohey2003</t>
+          <t>kk_4839598883</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01034151656</t>
+          <t>01032207906</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>116157</t>
+          <t>304105</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_4825242022</t>
+          <t>kk_3633964155</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01025208267</t>
+          <t>01097743709</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>303235</t>
+          <t>248300</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5068,24 +5068,24 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_4838646680</t>
+          <t>tkfkdtmfjs79</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01034311248</t>
+          <t>01044809033</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>304066</t>
+          <t>153239</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5095,105 +5095,105 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>[pf]트래픽_유사+관심사</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>csnoopy</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01063730741</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>110007</t>
+          <t>287573</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_2999650964</t>
+          <t>kk_4838514193</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01073667501</t>
+          <t>01028513978</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>218535</t>
+          <t>304057</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>soojst</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01097431003</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>287573</t>
+          <t>209447</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kk_3633964155</t>
+          <t>kk_3736097865</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01097743709</t>
+          <t>01089447248</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>248300</t>
+          <t>253356</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5203,51 +5203,51 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>anirim</t>
+          <t>kk_3631606950</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01026146239</t>
+          <t>01063256163</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>303897</t>
+          <t>248164</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>ohey2003</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01034151656</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>116157</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5257,78 +5257,78 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_3775794718</t>
+          <t>anirim</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01085983536</t>
+          <t>01026146239</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>255860</t>
+          <t>303897</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kiraeo</t>
+          <t>kk_4835267037</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01085072563</t>
+          <t>01047143494</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>195029</t>
+          <t>303847</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kk_4612713787</t>
+          <t>kk_4446020087</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01095027601</t>
+          <t>01089773053</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>290278</t>
+          <t>282273</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5345,44 +5345,44 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>lynx246</t>
+          <t>raneelim</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01041241323</t>
+          <t>01051598929</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>196113</t>
+          <t>72197</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4838748515</t>
+          <t>kk_4840238333</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01034435700</t>
+          <t>01087443182</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>304070</t>
+          <t>304135</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5392,51 +5392,51 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>jment1983</t>
+          <t>kiraeo</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01088991983</t>
+          <t>01085072563</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>271329</t>
+          <t>195029</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_4446020087</t>
+          <t>kk_3465759734</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01089773053</t>
+          <t>01045550499</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>282273</t>
+          <t>243732</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5446,51 +5446,51 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_4839598883</t>
+          <t>pkd2001</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01032207906</t>
+          <t>01043345927</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>304105</t>
+          <t>169815</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_3258483317</t>
+          <t>jth0122</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01075584654</t>
+          <t>01088989856</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>235788</t>
+          <t>96490</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5500,78 +5500,78 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>kk_4838635909</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01098131007</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>304098</t>
+          <t>304064</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>water4853</t>
+          <t>kslee9011</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01020542351</t>
+          <t>01031716463</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>178866</t>
+          <t>48237</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>kimchhgood</t>
+          <t>tomcurse02</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01092133961</t>
+          <t>01022070282</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>96444</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5581,24 +5581,24 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>kk_4835826103</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01082133090</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>303885</t>
+          <t>303894</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5608,51 +5608,51 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kk_4819536073</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01039113089</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>302942</t>
+          <t>280163</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>kk_2989316682</t>
+          <t>kk_4825242022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01037375641</t>
+          <t>01025208267</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>218263</t>
+          <t>303235</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5662,51 +5662,51 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>soojst</t>
+          <t>kk_3601774804</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01097431003</t>
+          <t>01046513357</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>209447</t>
+          <t>247059</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>164951</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5716,51 +5716,51 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>kk_4478716748</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01071630157</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>284194</t>
+          <t>304098</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>kk_3736097865</t>
+          <t>kk_4835837819</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01089447248</t>
+          <t>01044119822</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>253356</t>
+          <t>303896</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5770,24 +5770,24 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kk_4703414773</t>
+          <t>kk_2989316682</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01093547510</t>
+          <t>01037375641</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>296108</t>
+          <t>218263</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5797,51 +5797,51 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_4222073058</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01046077586</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>272870</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kk_4530117802</t>
+          <t>kk_4720019874</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01094437239</t>
+          <t>01052578634</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>286792</t>
+          <t>297465</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>kk_4212123801</t>
+          <t>fimajun</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01083862682</t>
+          <t>01035668051</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>272414</t>
+          <t>230171</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5878,51 +5878,51 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>kk_4344215691</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01020192399</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>279044</t>
+          <t>304107</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>tkfkdtmfjs79</t>
+          <t>kk_4344215691</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01044809033</t>
+          <t>01020192399</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>153239</t>
+          <t>279044</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5932,24 +5932,24 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>fimajun</t>
+          <t>kk_4530117802</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01035668051</t>
+          <t>01094437239</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>230171</t>
+          <t>286792</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5959,159 +5959,159 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>eccomi21</t>
+          <t>csnoopy</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01084717525</t>
+          <t>01063730741</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>143557</t>
+          <t>110007</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>kk_4681484279</t>
+          <t>kk_3258483317</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01022642776</t>
+          <t>01075584654</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>294947</t>
+          <t>235788</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>kk_4838635909</t>
+          <t>hjh3127</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01098131007</t>
+          <t>01054261891</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>304064</t>
+          <t>52538</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>raneelim</t>
+          <t>kk_3913679442</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01051598929</t>
+          <t>01085569215</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>72197</t>
+          <t>268330</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>jth0122</t>
+          <t>kk_4478716748</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01088989856</t>
+          <t>01071630157</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>96490</t>
+          <t>284194</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>kk_4212258541</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01047138543</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>219525</t>
+          <t>272420</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6128,17 +6128,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>kk_4484370599</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01052246899</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>284447</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6155,44 +6155,44 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kk_4288273717</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01020746624</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>275762</t>
+          <t>268974</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kk_3501053454</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01093015628</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>245323</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6202,105 +6202,105 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>kk_4839821563</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>01027951809</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>304112</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>304100</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>kk_4357899204</t>
+          <t>kk_4680971786</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>01082772838</t>
+          <t>01074443726</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>279564</t>
+          <t>294917</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>270708</t>
+          <t>279909</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6317,17 +6317,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>kk_4237700483</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>01063041087</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>273719</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6344,98 +6344,98 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kyong74</t>
+          <t>kk_4839283126</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>01088245591</t>
+          <t>01024419045</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>22857</t>
+          <t>304093</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>172790</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>268974</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>162562</t>
+          <t>219525</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6452,17 +6452,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>jung1481</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>01024193371</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>205735</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6472,51 +6472,51 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>byun7707</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01077391740</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>304100</t>
+          <t>161371</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>285491</t>
+          <t>186218</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6526,51 +6526,51 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>kk_4839542021</t>
+          <t>kk_3134493871</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>01089909663</t>
+          <t>01035918800</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>304103</t>
+          <t>222420</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>varam11</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01071373327</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>102004</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6580,24 +6580,24 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0413</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>kk_3960572616</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01072737379</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>270384</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6614,98 +6614,98 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>ganjing78</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01065121424</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>78590</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>kk_4840174486</t>
+          <t>motamsi</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>01064087457</t>
+          <t>01090344665</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>304131</t>
+          <t>96716</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>kk_4838920250</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01065688860</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>304074</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>kk_3134493871</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>01035918800</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>222420</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6715,159 +6715,159 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>292319</t>
+          <t>143826</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>jsu2080</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>01094582080</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>275256</t>
+          <t>304113</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>275998</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>jeonhyel</t>
+          <t>kk_3220401027</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>01077942894</t>
+          <t>01037591063</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>304102</t>
+          <t>232602</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EDM_0413</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>kk_4840035519</t>
+          <t>kk_2915134680</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>01086385010</t>
+          <t>01085224711</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>304121</t>
+          <t>215670</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>304126</t>
+          <t>304109</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -6877,24 +6877,24 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>jinoh</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01024150539</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>270445</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6911,71 +6911,71 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>chlwoghk83</t>
+          <t>kk_4840198421</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>01038851983</t>
+          <t>01053706365</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>145712</t>
+          <t>304132</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>285491</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6992,44 +6992,44 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>isaackwak</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01090599860</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>275913</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>kk_4221652535</t>
+          <t>chlwoghk83</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>01036858276</t>
+          <t>01038851983</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>272849</t>
+          <t>145712</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -7039,24 +7039,24 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>kk_3220401027</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>01037591063</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>232602</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -7066,24 +7066,24 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -7100,17 +7100,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>227343</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -7120,24 +7120,24 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>kk_3794951359</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>01066481842</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>257520</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -7154,206 +7154,206 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>kk_4840198421</t>
+          <t>jung1481</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>01053706365</t>
+          <t>01024193371</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>304132</t>
+          <t>205735</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>richjm</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>01082909799</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>122482</t>
+          <t>68751</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>jeonhyel</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01077942894</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>304102</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>kk_2985598511</t>
+          <t>kk_3678962368</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>01086703302</t>
+          <t>01041028567</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>218005</t>
+          <t>250374</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>kk_3796517297</t>
+          <t>kk_4839542021</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>01040802850</t>
+          <t>01089909663</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>257878</t>
+          <t>304103</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>kk_4212157104</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>01062437191</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>272417</t>
+          <t>174291</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>maksim04</t>
+          <t>coverdn</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>01063557978</t>
+          <t>01086426866</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>202013</t>
+          <t>172406</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7363,24 +7363,24 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0413</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>289364</t>
+          <t>123130</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -7390,24 +7390,24 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>227343</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -7424,17 +7424,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>js0987</t>
+          <t>kk_4237700483</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>01052819790</t>
+          <t>01063041087</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>110955</t>
+          <t>273719</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -7451,206 +7451,206 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>304104</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>kk_4375333989</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01091513985</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>280145</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>kk_4484370599</t>
+          <t>js0987</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>01052246899</t>
+          <t>01052819790</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>284447</t>
+          <t>110955</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>richjm</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01082909799</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>140860</t>
+          <t>122482</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>varam11</t>
+          <t>kk_4212157104</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>01071373327</t>
+          <t>01062437191</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>102004</t>
+          <t>272417</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>kk_4727505000</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01066573797</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>68751</t>
+          <t>298110</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>mooner82</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>01037861045</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>148696</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7667,17 +7667,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>kk_4840174486</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01064087457</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>304131</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7687,51 +7687,51 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>304101</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>kk_3501053454</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01093015628</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>245323</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7741,34 +7741,34 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>kk_4839027252</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>01084518813</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>304083</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
@@ -7802,44 +7802,44 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>kk_4839283126</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>01024419045</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>304093</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>kk_4727505000</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>01066573797</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>298110</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7849,105 +7849,105 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>isaackwak</t>
+          <t>maksim04</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>01090599860</t>
+          <t>01063557978</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>275913</t>
+          <t>202013</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>304129</t>
+          <t>229454</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>hhpp123</t>
+          <t>kk_4839765445</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>01042621121</t>
+          <t>01076118972</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>294450</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>kk_4840035519</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01086385010</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>304121</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7957,24 +7957,24 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>chaser1</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>01038304145</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>178090</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7991,17 +7991,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>he0218</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>01049289998</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>254710</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -8011,78 +8011,78 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>123130</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>kk_3170564464</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01099188001</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>304124</t>
+          <t>224948</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8099,17 +8099,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>kk_3678962368</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>01041028567</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>250374</t>
+          <t>270708</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8126,98 +8126,98 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>180321</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>kk_3466706406</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>01055441553</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>243779</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>kk_4838947856</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01094709458</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>304075</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>143826</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8227,51 +8227,51 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_2950194486</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01076104875</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>216766</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>kk_3750120343</t>
+          <t>hodong1014</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>01092908890</t>
+          <t>01044530048</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>254168</t>
+          <t>64397</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8288,17 +8288,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>kk_4212258541</t>
+          <t>fjsjhw</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>01047138543</t>
+          <t>01050468291</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>272420</t>
+          <t>192240</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8308,51 +8308,51 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>motamsi</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>01090344665</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>96716</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>coverdn</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>01086426866</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>172406</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8362,24 +8362,24 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>kk_2950194486</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>01076104875</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>216766</t>
+          <t>221630</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8396,44 +8396,44 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>kk_3170564464</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>01099188001</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>224948</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8450,98 +8450,98 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>seopme</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01074122238</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>304125</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>kk_2915134680</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>01085224711</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>215670</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>kk_4538201048</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>01071790372</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>287217</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8558,17 +8558,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>kk_3960572616</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>01072737379</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>270384</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8585,17 +8585,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>hodong1014</t>
+          <t>kyong74</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>01044530048</t>
+          <t>01088245591</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>64397</t>
+          <t>22857</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8612,44 +8612,44 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>kk_4839241951</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01079146776</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>180321</t>
+          <t>304090</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>232010</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8659,24 +8659,24 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>kk_4536846819</t>
+          <t>hhpp123</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>01038223781</t>
+          <t>01042621121</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>287146</t>
+          <t>294450</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8693,44 +8693,44 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>221630</t>
+          <t>232010</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8740,51 +8740,51 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>kk_4680971786</t>
+          <t>kk_4221652535</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>01074443726</t>
+          <t>01036858276</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>294917</t>
+          <t>272849</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>fjsjhw</t>
+          <t>kk_3466706406</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>01050468291</t>
+          <t>01055441553</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>192240</t>
+          <t>243779</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8794,24 +8794,24 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8828,17 +8828,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8855,44 +8855,44 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>kk_4839241951</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>01079146776</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>304090</t>
+          <t>136050</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>136050</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8909,17 +8909,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>kk_4670878863</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>01067207833</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>294326</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8936,44 +8936,44 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>kk_2985598511</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01086703302</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>218005</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>kk_4517851709</t>
+          <t>kk_3796517297</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>01066445714</t>
+          <t>01040802850</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>286074</t>
+          <t>257878</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8990,17 +8990,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>140860</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9017,233 +9017,233 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>174291</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>kk_4357899204</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01082772838</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>279564</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>kk_4839027252</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01084518813</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>304083</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>298138</t>
+          <t>208245</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>seopme</t>
+          <t>kk_3794951359</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>01074122238</t>
+          <t>01066481842</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>304125</t>
+          <t>257520</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>kk_4838920250</t>
+          <t>jsu2080</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>01065688860</t>
+          <t>01094582080</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>304074</t>
+          <t>275256</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>304086</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>kk_4838947856</t>
+          <t>kk_4538201048</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>01094709458</t>
+          <t>01071790372</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>304075</t>
+          <t>287217</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>jinoh</t>
+          <t>chaser1</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>01024150539</t>
+          <t>01038304145</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>270445</t>
+          <t>178090</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9260,17 +9260,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>304086</t>
+          <t>304129</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -9280,51 +9280,51 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ganjing78</t>
+          <t>he0218</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>01065121424</t>
+          <t>01049289998</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>78590</t>
+          <t>254710</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9334,51 +9334,51 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>kwon9493</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>01035589493</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>292319</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -9388,24 +9388,24 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>kk_3380246984</t>
+          <t>kk_4517851709</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>01040750851</t>
+          <t>01066445714</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>240492</t>
+          <t>286074</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9422,17 +9422,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9442,24 +9442,24 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>byun7707</t>
+          <t>kk_3380246984</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>01077391740</t>
+          <t>01040750851</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>161371</t>
+          <t>240492</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9469,51 +9469,51 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>kk_4288273717</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01020746624</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>279909</t>
+          <t>275762</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9530,98 +9530,98 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>kwon9493</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01035589493</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>107077</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>kk_4839821563</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01027951809</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>229454</t>
+          <t>304112</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>304101</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>kk_4670878863</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01067207833</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>294326</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9638,98 +9638,98 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>kk_4839765445</t>
+          <t>kk_4536846819</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>01076118972</t>
+          <t>01038223781</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>304111</t>
+          <t>287146</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>mooner82</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01037861045</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>304104</t>
+          <t>148696</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>304126</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>kk_4375333989</t>
+          <t>kk_3750120343</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>01091513985</t>
+          <t>01092908890</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>280145</t>
+          <t>254168</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -593,17 +593,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kig0268</t>
+          <t>kk_3182623010</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01053928207</t>
+          <t>01094128645</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>301007</t>
+          <t>227908</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -613,142 +613,142 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_3182623010</t>
+          <t>kk_3407332090</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01094128645</t>
+          <t>01073480423</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>227908</t>
+          <t>241393</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_3789625265</t>
+          <t>kig0268</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01029773942</t>
+          <t>01053928207</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>256664</t>
+          <t>301007</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_3407332090</t>
+          <t>kk_3789625265</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01073480423</t>
+          <t>01029773942</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>241393</t>
+          <t>256664</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_3500501777</t>
+          <t>kk_3178599665</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01038347573</t>
+          <t>01089430429</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>245304</t>
+          <t>225280</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_3178599665</t>
+          <t>kk_3500501777</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01089430429</t>
+          <t>01038347573</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>225280</t>
+          <t>245304</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
@@ -782,44 +782,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kk_3243338539</t>
+          <t>kk_4507190107</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01025098649</t>
+          <t>01091780704</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>234832</t>
+          <t>285496</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kk_4507190107</t>
+          <t>joohpark87</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01091780704</t>
+          <t>01062437622</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>285496</t>
+          <t>121373</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -829,51 +829,51 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_TITANIUM</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sagepcs</t>
+          <t>kk_3243338539</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01058583300</t>
+          <t>01025098649</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>201749</t>
+          <t>234832</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>joohpark87</t>
+          <t>sagepcs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01062437622</t>
+          <t>01058583300</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>121373</t>
+          <t>201749</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -917,71 +917,71 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_3794046073</t>
+          <t>kk_4772822345</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01056918495</t>
+          <t>01036338705</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>257320</t>
+          <t>301574</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_4772822345</t>
+          <t>hbnetsys</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01036338705</t>
+          <t>01052810852</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>301574</t>
+          <t>282445</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hbnetsys</t>
+          <t>kk_3794046073</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01052810852</t>
+          <t>01056918495</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>282445</t>
+          <t>257320</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -991,51 +991,51 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>justicek73</t>
+          <t>staylus11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01033270931</t>
+          <t>01055097903</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>237394</t>
+          <t>200332</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4493450118</t>
+          <t>cutebear88</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01077566800</t>
+          <t>01039942456</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>284909</t>
+          <t>212858</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1045,24 +1045,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cutebear88</t>
+          <t>kk_4493450118</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01039942456</t>
+          <t>01077566800</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>212858</t>
+          <t>284909</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1072,78 +1072,78 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1201_WINTERDOWN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>staylus11</t>
+          <t>justicek73</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01055097903</t>
+          <t>01033270931</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>200332</t>
+          <t>237394</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gbk888</t>
+          <t>namki9545</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01063271523</t>
+          <t>01073099545</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>264430</t>
+          <t>27441</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4226246986</t>
+          <t>darius27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01048263393</t>
+          <t>01091911224</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>273085</t>
+          <t>292238</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>namki9545</t>
+          <t>kk_2760596791</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01073099545</t>
+          <t>01087827701</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>27441</t>
+          <t>208450</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1180,78 +1180,78 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_2850432473</t>
+          <t>gbk888</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01026771240</t>
+          <t>01063271523</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>213403</t>
+          <t>264430</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>jung9916</t>
+          <t>kk_3959240760</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01091576210</t>
+          <t>01035045875</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>171554</t>
+          <t>270320</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_3959240760</t>
+          <t>kk_4226246986</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01035045875</t>
+          <t>01048263393</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>270320</t>
+          <t>273085</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1261,24 +1261,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1119_WINTERFESTIVAL_TEASING</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>darius27</t>
+          <t>kk_4291314607</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01091911224</t>
+          <t>01088119636</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>292238</t>
+          <t>275953</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1295,44 +1295,44 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_2760596791</t>
+          <t>pkcomon</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01087827701</t>
+          <t>01063208976</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>208450</t>
+          <t>198932</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>astro77</t>
+          <t>kk_3628696638_2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01091518663</t>
+          <t>01038262132</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>167514</t>
+          <t>302884</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1342,88 +1342,88 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4291314607</t>
+          <t>astro77</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01088119636</t>
+          <t>01091518663</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>275953</t>
+          <t>167514</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>120212705670680427</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_3628696638_2</t>
+          <t>kk_3340113031</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01038262132</t>
+          <t>01098338138</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>302884</t>
+          <t>239100</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pkcomon</t>
+          <t>kk_3338448571</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01063208976</t>
+          <t>01050068417</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>198932</t>
+          <t>239011</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
@@ -1457,17 +1457,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_3340113031</t>
+          <t>kk_2850432473</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01098338138</t>
+          <t>01026771240</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>239100</t>
+          <t>213403</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1477,186 +1477,186 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_3338448571</t>
+          <t>jung9916</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01050068417</t>
+          <t>01091576210</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>239011</t>
+          <t>171554</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4790899014</t>
+          <t>kk_3827025148</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01024708415</t>
+          <t>01090399900</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>302058</t>
+          <t>263356</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_4828047673</t>
+          <t>kk_3793101024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01087502319</t>
+          <t>01082844287</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>303388</t>
+          <t>257080</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_3241814751</t>
+          <t>kk_4694268987</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01048808215</t>
+          <t>01025088964</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>234712</t>
+          <t>295680</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_2783594999</t>
+          <t>kk_4509280340</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01095317357</t>
+          <t>01088521558</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>209807</t>
+          <t>285569</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>leecs11124</t>
+          <t>aram2016</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01037870639</t>
+          <t>01071670785</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>260560</t>
+          <t>225250</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>EDM_0214</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4838420487</t>
+          <t>kk_4790899014</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01050618241</t>
+          <t>01024708415</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>304051</t>
+          <t>302058</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1666,105 +1666,105 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>aram2016</t>
+          <t>stonehinge</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01071670785</t>
+          <t>01027275105</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>225250</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>lms_ecom_0401_springhiking</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_3795564177</t>
+          <t>kk_4746910410</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01044552859</t>
+          <t>01047502488</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>257673</t>
+          <t>300629</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_3097460767</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01048597145</t>
+          <t>01085815097</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>221400</t>
+          <t>303542</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4694268987</t>
+          <t>kk_4201661917</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01025088964</t>
+          <t>01052228247</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>295680</t>
+          <t>271984</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1774,78 +1774,78 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>stonehinge</t>
+          <t>kk_3097460767</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01027275105</t>
+          <t>01048597145</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>221400</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>lms_ecom_0401_springhiking</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4201661917</t>
+          <t>kk_4837990320</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01052228247</t>
+          <t>01024175652</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>271984</t>
+          <t>304030</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4837990320</t>
+          <t>kk_2762251625</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01024175652</t>
+          <t>01032085585</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>304030</t>
+          <t>208548</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1855,24 +1855,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_3827025148</t>
+          <t>djmin57</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01090399900</t>
+          <t>01034585986</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>263356</t>
+          <t>52890</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1882,132 +1882,132 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_3793101024</t>
+          <t>kk_4828047673</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01082844287</t>
+          <t>01087502319</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>257080</t>
+          <t>303388</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4746910410</t>
+          <t>kk_3241814751</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01047502488</t>
+          <t>01048808215</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>300629</t>
+          <t>234712</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>juhan3489</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01085815097</t>
+          <t>01037693092</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>303542</t>
+          <t>214043</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>djmin57</t>
+          <t>kk_3795564177</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01034585986</t>
+          <t>01044552859</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>52890</t>
+          <t>257673</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4278011504</t>
+          <t>kk_4838420487</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01045289321</t>
+          <t>01050618241</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>275167</t>
+          <t>304051</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2017,115 +2017,115 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4509280340</t>
+          <t>kk_4743669054</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01088521558</t>
+          <t>01036749627</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>285569</t>
+          <t>300361</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4743669054</t>
+          <t>kk_2783594999</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01036749627</t>
+          <t>01095317357</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>300361</t>
+          <t>209807</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>juhan3489</t>
+          <t>kk_4278011504</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01037693092</t>
+          <t>01045289321</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>214043</t>
+          <t>275167</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_2762251625</t>
+          <t>leecs11124</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01032085585</t>
+          <t>01037870639</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>208548</t>
+          <t>260560</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EDM_0214</t>
         </is>
       </c>
     </row>
@@ -2159,206 +2159,206 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>endruns</t>
+          <t>kk_3290809343</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01020716852</t>
+          <t>01057206001</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>176346</t>
+          <t>237059</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>abejung</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01023320007</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>158025</t>
+          <t>244619</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>klim202</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01064368836</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>168762</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>jcahn12</t>
+          <t>kk_4817738509</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01038358052</t>
+          <t>01085325672</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>59346</t>
+          <t>302840</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_3727979047</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01079273404</t>
+          <t>01083936762</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>252685</t>
+          <t>303728</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4817738509</t>
+          <t>kk_3229351319</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01085325672</t>
+          <t>01090969959</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>302840</t>
+          <t>233446</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4833493849</t>
+          <t>jk571957</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01083936762</t>
+          <t>01080011083</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>303728</t>
+          <t>168147</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_3707105860</t>
+          <t>kk_4793026063</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01059290508</t>
+          <t>01072703070</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>251625</t>
+          <t>302125</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2375,17 +2375,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>klim202</t>
+          <t>cgkrry</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01064368836</t>
+          <t>01085513271</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>168762</t>
+          <t>48578</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2395,105 +2395,105 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>p7181</t>
+          <t>kk_4299847976</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01056288360</t>
+          <t>01091384892</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>250858</t>
+          <t>276488</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ssbok0806</t>
+          <t>kk_3186268807</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01093267531</t>
+          <t>01055175130</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>223278</t>
+          <t>230244</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_3967220863</t>
+          <t>p7181</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01087902066</t>
+          <t>01056288360</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>270700</t>
+          <t>250858</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6941110100332</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_3229351319</t>
+          <t>joocho629</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01090969959</t>
+          <t>01038056919</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>233446</t>
+          <t>162948</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2503,78 +2503,78 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0224</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_3866200904</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01062556776</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>265988</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>cgkrry</t>
+          <t>kk_4614762502</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01085513271</t>
+          <t>01064155845</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>48578</t>
+          <t>290560</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4793026063</t>
+          <t>endruns</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01072703070</t>
+          <t>01020716852</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>302125</t>
+          <t>176346</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2584,78 +2584,78 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>jk571957</t>
+          <t>kk_3967220863</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01080011083</t>
+          <t>01087902066</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>168147</t>
+          <t>270700</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_3866200904</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01062556776</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>265988</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>joocho629</t>
+          <t>kk_3778874557</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01038056919</t>
+          <t>01094017193</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>162948</t>
+          <t>256071</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>EDM_0224</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
@@ -2699,71 +2699,71 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_3186268807</t>
+          <t>kk_3707105860</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01055175130</t>
+          <t>01059290508</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>230244</t>
+          <t>251625</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_4837763007</t>
+          <t>abejung</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01088993992</t>
+          <t>01023320007</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>304013</t>
+          <t>158025</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_3203549435</t>
+          <t>kk_4837763007</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01033608209</t>
+          <t>01088993992</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>230719</t>
+          <t>304013</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2773,105 +2773,105 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4299847976</t>
+          <t>kk_3727979047</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01091384892</t>
+          <t>01079273404</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>276488</t>
+          <t>252685</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4614762502</t>
+          <t>jcahn12</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01064155845</t>
+          <t>01038358052</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>290560</t>
+          <t>59346</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_3778874557</t>
+          <t>ssbok0806</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01094017193</t>
+          <t>01093267531</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>256071</t>
+          <t>223278</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_3290809343</t>
+          <t>kk_3203549435</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01057206001</t>
+          <t>01033608209</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>237059</t>
+          <t>230719</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2881,132 +2881,132 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_3825294168</t>
+          <t>delta12</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01076290208</t>
+          <t>01071339709</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>263146</t>
+          <t>192352</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4839929131</t>
+          <t>kk_4755147673</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01044408612</t>
+          <t>01062968675</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>304116</t>
+          <t>301054</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_3943654079</t>
+          <t>kk_4217088689</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01053762357</t>
+          <t>01077710204</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>269510</t>
+          <t>272648</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4755147673</t>
+          <t>wlcnstjs12</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01062968675</t>
+          <t>01040240293</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>301054</t>
+          <t>149195</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>junghyunpak</t>
+          <t>optimal11</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01028120688</t>
+          <t>01083258827</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>58618</t>
+          <t>129148</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4610571768</t>
+          <t>scubaktk</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01094092580</t>
+          <t>01028951833</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>290026</t>
+          <t>51328</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3043,24 +3043,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_3901736373</t>
+          <t>chelius</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01072562998</t>
+          <t>01024880126</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>267789</t>
+          <t>300985</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3070,24 +3070,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>hansoi93</t>
+          <t>gilinim</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01072262346</t>
+          <t>01032351966</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>60217</t>
+          <t>302594</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3097,51 +3097,51 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>luvsena</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01092690887</t>
+          <t>01089625349</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>303428</t>
+          <t>172100</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4508257846</t>
+          <t>junghyunpak</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01092499867</t>
+          <t>01028120688</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>285541</t>
+          <t>58618</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3151,78 +3151,78 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4525960790</t>
+          <t>kk_4440711181</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01084170327</t>
+          <t>01063263543</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>286541</t>
+          <t>282110</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comic0828</t>
+          <t>kk_3898041727</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01096390888</t>
+          <t>01091030227</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>140326</t>
+          <t>267643</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4282126610</t>
+          <t>kk_4525960790</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01037415807</t>
+          <t>01084170327</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>275374</t>
+          <t>286541</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3232,132 +3232,132 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>godo2027</t>
+          <t>kk_3901736373</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01075835624</t>
+          <t>01072562998</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>179139</t>
+          <t>267789</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>haein607</t>
+          <t>kk_3456892694</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01023369606</t>
+          <t>01057443264</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>151209</t>
+          <t>243269</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>jinny6716</t>
+          <t>kk_4838385004</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01039376458</t>
+          <t>01088158446</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>95121</t>
+          <t>304048</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_3898041727</t>
+          <t>kk_3801427305</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01091030227</t>
+          <t>01097820998</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>267643</t>
+          <t>259073</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>scubaktk</t>
+          <t>kk_4634804186</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01028951833</t>
+          <t>01089506651</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>51328</t>
+          <t>292029</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3367,51 +3367,51 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>wlcnstjs12</t>
+          <t>plus7431</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01040240293</t>
+          <t>01084748664</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>149195</t>
+          <t>251388</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>delta12</t>
+          <t>kk_2975660270</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01071339709</t>
+          <t>01065565496</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>192352</t>
+          <t>217640</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3421,24 +3421,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>tinykim</t>
+          <t>ko7417</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01035630719</t>
+          <t>01041821439</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>65922</t>
+          <t>21776</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3448,24 +3448,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>luvsena</t>
+          <t>jinny6716</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01089625349</t>
+          <t>01039376458</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>172100</t>
+          <t>95121</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3475,213 +3475,213 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4288079130</t>
+          <t>tinykim</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01056697298</t>
+          <t>01035630719</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>275750</t>
+          <t>65922</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>goppagi</t>
+          <t>scp0103</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01052632529</t>
+          <t>01033083314</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>179049</t>
+          <t>214558</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_4634804186</t>
+          <t>kk_4475486602</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01089506651</t>
+          <t>01041949661</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>292029</t>
+          <t>284059</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_3456892694</t>
+          <t>kk_4508257846</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01057443264</t>
+          <t>01092499867</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>243269</t>
+          <t>285541</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_3774156950</t>
+          <t>kk_3825294168</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01041159966</t>
+          <t>01076290208</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>255778</t>
+          <t>263146</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4310987668</t>
+          <t>goppagi</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01027962045</t>
+          <t>01052632529</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>277132</t>
+          <t>179049</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4838385004</t>
+          <t>kk_4310987668</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01088158446</t>
+          <t>01027962045</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>304048</t>
+          <t>277132</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>sbstkd</t>
+          <t>kk_4288079130</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01084506080</t>
+          <t>01056697298</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>137269</t>
+          <t>275750</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3691,24 +3691,24 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_2975660270</t>
+          <t>kk_3246970011</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01065565496</t>
+          <t>01080703392</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>217640</t>
+          <t>235053</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3718,24 +3718,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kbh2639</t>
+          <t>kk_4443559736</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01026514411</t>
+          <t>01064021269</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>159679</t>
+          <t>282199</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3745,24 +3745,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>EDM_0331</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>jeshurun76</t>
+          <t>kbh2639</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01051236012</t>
+          <t>01026514411</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>191849</t>
+          <t>159679</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3772,24 +3772,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4440711181</t>
+          <t>kk_4839929131</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01063263543</t>
+          <t>01044408612</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>282110</t>
+          <t>304116</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3799,24 +3799,24 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ferix1999</t>
+          <t>sbstkd</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01026339659</t>
+          <t>01084506080</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>191848</t>
+          <t>137269</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3826,24 +3826,24 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kmhjm</t>
+          <t>hansoi93</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01095316235</t>
+          <t>01072262346</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>181953</t>
+          <t>60217</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3853,78 +3853,78 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4443559736</t>
+          <t>comic0828</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01064021269</t>
+          <t>01096390888</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>282199</t>
+          <t>140326</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>EDM_0331</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_3718281230</t>
+          <t>kk_3774156950</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01067711528</t>
+          <t>01041159966</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>252078</t>
+          <t>255778</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_3795672557</t>
+          <t>kk_4610571768</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01091179346</t>
+          <t>01094092580</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>257697</t>
+          <t>290026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3934,24 +3934,24 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>optimal11</t>
+          <t>kk_3795672557</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01083258827</t>
+          <t>01091179346</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>129148</t>
+          <t>257697</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3961,78 +3961,78 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4475486602</t>
+          <t>kk_4828776483</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01041949661</t>
+          <t>01092690887</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>284059</t>
+          <t>303428</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>plus7431</t>
+          <t>kk_3718281230</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01084748664</t>
+          <t>01067711528</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>251388</t>
+          <t>252078</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4217088689</t>
+          <t>kmhjm</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01077710204</t>
+          <t>01095316235</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>272648</t>
+          <t>181953</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4042,24 +4042,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>chunsadl</t>
+          <t>godo2027</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01087804011</t>
+          <t>01075835624</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>167610</t>
+          <t>179139</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4069,78 +4069,78 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_3246970011</t>
+          <t>ferix1999</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01080703392</t>
+          <t>01026339659</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>235053</t>
+          <t>191848</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ko7417</t>
+          <t>kk_3943654079</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01041821439</t>
+          <t>01053762357</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>21776</t>
+          <t>269510</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>gilinim</t>
+          <t>jeshurun76</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01032351966</t>
+          <t>01051236012</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>302594</t>
+          <t>191849</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4150,51 +4150,51 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_3801427305</t>
+          <t>haein607</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01097820998</t>
+          <t>01023369606</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>259073</t>
+          <t>151209</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>chelius</t>
+          <t>kk_4282126610</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01024880126</t>
+          <t>01037415807</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>300985</t>
+          <t>275374</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4211,71 +4211,71 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>scp0103</t>
+          <t>chunsadl</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01033083314</t>
+          <t>01087804011</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>214558</t>
+          <t>167610</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>jment1983</t>
+          <t>kimchhgood</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01088991983</t>
+          <t>01092133961</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>271329</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>colorum</t>
+          <t>kk_4720019874</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01054844416</t>
+          <t>01052578634</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>146276</t>
+          <t>297465</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4285,24 +4285,24 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kimchhgood</t>
+          <t>kk_4212123801</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01092133961</t>
+          <t>01083862682</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>272414</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4312,132 +4312,132 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>whtjdfo11</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01075377523</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>303885</t>
+          <t>185516</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_3793412568</t>
+          <t>kk_3776403631</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01049200546</t>
+          <t>01034755755</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>257211</t>
+          <t>255908</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>soojst</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01097431003</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>164951</t>
+          <t>209447</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4838748515</t>
+          <t>kk_3804201157</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01034435700</t>
+          <t>01055152547</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>304070</t>
+          <t>259728</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4612713787</t>
+          <t>kk_4344215691</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01095027601</t>
+          <t>01020192399</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>290278</t>
+          <t>279044</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4454,17 +4454,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_4222073058</t>
+          <t>kk_2989316682</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01046077586</t>
+          <t>01037375641</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>272870</t>
+          <t>218263</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4474,78 +4474,78 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_2999650964</t>
+          <t>kk_4681484279</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01073667501</t>
+          <t>01022642776</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>218535</t>
+          <t>294947</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_3798545067</t>
+          <t>kkemc11</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01023751319</t>
+          <t>01072822359</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>258449</t>
+          <t>224851</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4672701053</t>
+          <t>kk_4838646680</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01088807653</t>
+          <t>01034311248</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>294426</t>
+          <t>304066</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4555,24 +4555,24 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[pf]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kkemc11</t>
+          <t>kiraeo</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01072822359</t>
+          <t>01085072563</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>224851</t>
+          <t>195029</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4582,105 +4582,105 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4681484279</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01022642776</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>294947</t>
+          <t>287573</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>eccomi21</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01084717525</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>143557</t>
+          <t>304098</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4819536073</t>
+          <t>kk_3258483317</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01039113089</t>
+          <t>01075584654</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>302942</t>
+          <t>235788</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4464127061</t>
+          <t>water4853</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01073655835</t>
+          <t>01020542351</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>283300</t>
+          <t>178866</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4690,24 +4690,24 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_3776403631</t>
+          <t>myjjangga</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01034755755</t>
+          <t>01083364898</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>255908</t>
+          <t>87940</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4717,51 +4717,51 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4212123801</t>
+          <t>kk_3766082784</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01083862682</t>
+          <t>01092342302</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>272414</t>
+          <t>255139</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4703414773</t>
+          <t>raneelim</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01093547510</t>
+          <t>01051598929</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>296108</t>
+          <t>72197</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4771,24 +4771,24 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_3766082784</t>
+          <t>kk_3798545067</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01092342302</t>
+          <t>01023751319</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>255139</t>
+          <t>258449</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4805,71 +4805,71 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>water4853</t>
+          <t>kk_3793412568</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01020542351</t>
+          <t>01049200546</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>178866</t>
+          <t>257211</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>lynx246</t>
+          <t>fimajun</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01041241323</t>
+          <t>01035668051</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>196113</t>
+          <t>230171</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>whtjdfo11</t>
+          <t>pkd2001</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01075377523</t>
+          <t>01043345927</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>185516</t>
+          <t>169815</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4879,51 +4879,51 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_3694865986</t>
+          <t>kk_4835837819</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01083470708</t>
+          <t>01044119822</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>251070</t>
+          <t>303896</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>myjjangga</t>
+          <t>kk_4530117802</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01083364898</t>
+          <t>01094437239</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>87940</t>
+          <t>286792</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4933,24 +4933,24 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_3775794718</t>
+          <t>kk_4825242022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01085983536</t>
+          <t>01025208267</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>255860</t>
+          <t>303235</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4960,24 +4960,24 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_4838646680</t>
+          <t>ohey2003</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01034311248</t>
+          <t>01034151656</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>304066</t>
+          <t>116157</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4987,24 +4987,24 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>[pf]트래픽_유사+관심사</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_3804201157</t>
+          <t>kk_3633964155</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01055152547</t>
+          <t>01097743709</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>259728</t>
+          <t>248300</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5014,24 +5014,24 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_4839598883</t>
+          <t>csnoopy</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01032207906</t>
+          <t>01063730741</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>304105</t>
+          <t>110007</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5041,24 +5041,24 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_3633964155</t>
+          <t>tkfkdtmfjs79</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01097743709</t>
+          <t>01044809033</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>248300</t>
+          <t>153239</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5068,78 +5068,78 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>tkfkdtmfjs79</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01044809033</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>153239</t>
+          <t>304107</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4839598883</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01032207906</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>287573</t>
+          <t>304105</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_4838514193</t>
+          <t>kk_4838748515</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01028513978</t>
+          <t>01034435700</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>304057</t>
+          <t>304070</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5149,51 +5149,51 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>soojst</t>
+          <t>hjh3127</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01097431003</t>
+          <t>01054261891</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>209447</t>
+          <t>52538</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kk_3736097865</t>
+          <t>kk_4464127061</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01089447248</t>
+          <t>01073655835</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>253356</t>
+          <t>283300</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5203,78 +5203,78 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_3631606950</t>
+          <t>kk_4835826103</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01063256163</t>
+          <t>01082133090</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>248164</t>
+          <t>303894</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ohey2003</t>
+          <t>kk_4478716748</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01034151656</t>
+          <t>01071630157</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>116157</t>
+          <t>284194</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>anirim</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01026146239</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>303897</t>
+          <t>303885</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5284,51 +5284,51 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kk_4835267037</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01047143494</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>303847</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kk_4446020087</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01089773053</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>282273</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5338,78 +5338,78 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>raneelim</t>
+          <t>kk_3913679442</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01051598929</t>
+          <t>01085569215</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>72197</t>
+          <t>268330</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4840238333</t>
+          <t>kk_4222073058</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01087443182</t>
+          <t>01046077586</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>304135</t>
+          <t>272870</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kiraeo</t>
+          <t>jth0122</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01085072563</t>
+          <t>01088989856</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>195029</t>
+          <t>96490</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5419,88 +5419,88 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_3465759734</t>
+          <t>jment1983</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01045550499</t>
+          <t>01088991983</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>243732</t>
+          <t>271329</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>pkd2001</t>
+          <t>kk_3694865986</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01043345927</t>
+          <t>01083470708</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>169815</t>
+          <t>251070</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>jth0122</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01088989856</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>96490</t>
+          <t>280163</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
@@ -5534,44 +5534,44 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>kslee9011</t>
+          <t>kk_4819536073</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01031716463</t>
+          <t>01039113089</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>48237</t>
+          <t>302942</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>tomcurse02</t>
+          <t>kk_3601774804</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01022070282</t>
+          <t>01046513357</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>96444</t>
+          <t>247059</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5581,105 +5581,105 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kk_4835826103</t>
+          <t>eccomi21</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01082133090</t>
+          <t>01084717525</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>303894</t>
+          <t>143557</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>colorum</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01054844416</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>280163</t>
+          <t>146276</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>kk_4825242022</t>
+          <t>kk_4835267037</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01025208267</t>
+          <t>01047143494</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>303235</t>
+          <t>303847</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>kk_3601774804</t>
+          <t>kk_4446020087</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01046513357</t>
+          <t>01089773053</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>247059</t>
+          <t>282273</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5689,24 +5689,24 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_4672701053</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01088807653</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>294426</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5716,51 +5716,51 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>kslee9011</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01031716463</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>304098</t>
+          <t>48237</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>kk_4835837819</t>
+          <t>kk_4703414773</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01044119822</t>
+          <t>01093547510</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>303896</t>
+          <t>296108</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5770,24 +5770,24 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kk_2989316682</t>
+          <t>kk_4612713787</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01037375641</t>
+          <t>01095027601</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>218263</t>
+          <t>290278</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5797,51 +5797,51 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>kk_3465759734</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01045550499</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>243732</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kk_4720019874</t>
+          <t>kk_3775794718</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01052578634</t>
+          <t>01085983536</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>297465</t>
+          <t>255860</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5851,105 +5851,105 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>fimajun</t>
+          <t>anirim</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01035668051</t>
+          <t>01026146239</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>230171</t>
+          <t>303897</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>304107</t>
+          <t>164951</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>kk_4344215691</t>
+          <t>kk_4840238333</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01020192399</t>
+          <t>01087443182</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>279044</t>
+          <t>304135</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>kk_4530117802</t>
+          <t>tomcurse02</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01094437239</t>
+          <t>01022070282</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>286792</t>
+          <t>96444</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5959,24 +5959,24 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>csnoopy</t>
+          <t>kk_4838514193</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01063730741</t>
+          <t>01028513978</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>110007</t>
+          <t>304057</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5986,24 +5986,24 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>kk_3258483317</t>
+          <t>kk_3736097865</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01075584654</t>
+          <t>01089447248</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>235788</t>
+          <t>253356</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6013,51 +6013,51 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>hjh3127</t>
+          <t>lynx246</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01054261891</t>
+          <t>01041241323</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>52538</t>
+          <t>196113</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_3913679442</t>
+          <t>kk_3631606950</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01085569215</t>
+          <t>01063256163</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>268330</t>
+          <t>248164</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6074,44 +6074,44 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kk_4478716748</t>
+          <t>kk_2999650964</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01071630157</t>
+          <t>01073667501</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>284194</t>
+          <t>218535</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>bizboard</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kk_4212258541</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01047138543</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>272420</t>
+          <t>279909</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6128,17 +6128,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kk_4484370599</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01052246899</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>284447</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6155,44 +6155,44 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>268974</t>
+          <t>221630</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6209,71 +6209,71 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>seopme</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01074122238</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>304125</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>304100</t>
+          <t>186218</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>kk_4680971786</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>01074443726</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>294917</t>
+          <t>270708</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -6290,17 +6290,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>279909</t>
+          <t>180321</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6317,98 +6317,98 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>kk_4840035519</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01086385010</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>304121</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kk_4839283126</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>01024419045</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>304093</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>mooner82</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01037861045</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>148696</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>kk_4212258541</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01047138543</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>272420</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6425,17 +6425,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>kk_4517851709</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01066445714</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>219525</t>
+          <t>286074</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6452,17 +6452,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6472,24 +6472,24 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>byun7707</t>
+          <t>fjsjhw</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>01077391740</t>
+          <t>01050468291</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>161371</t>
+          <t>192240</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6499,78 +6499,78 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>174291</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>kk_3134493871</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>01035918800</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>222420</t>
+          <t>304100</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>varam11</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>01071373327</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>102004</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6580,24 +6580,24 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>kk_3960572616</t>
+          <t>hodong1014</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>01072737379</t>
+          <t>01044530048</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>270384</t>
+          <t>64397</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6614,17 +6614,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ganjing78</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>01065121424</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>78590</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6641,98 +6641,98 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>motamsi</t>
+          <t>kk_4838947856</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>01090344665</t>
+          <t>01094709458</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>96716</t>
+          <t>304075</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>kk_4838920250</t>
+          <t>kk_4840198421</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>01065688860</t>
+          <t>01053706365</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>304074</t>
+          <t>304132</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>maksim04</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01063557978</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>143826</t>
+          <t>202013</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -6742,105 +6742,105 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>275998</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>kyong74</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01088245591</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>22857</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>kk_3220401027</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>01037591063</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>232602</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>kk_2915134680</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>01085224711</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>215670</t>
+          <t>227343</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6850,34 +6850,34 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>kk_4357899204</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01082772838</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>279564</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -6911,152 +6911,152 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>kk_4840198421</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>01053706365</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>304132</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>285491</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>isaackwak</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>01090599860</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>275913</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>chlwoghk83</t>
+          <t>motamsi</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>01038851983</t>
+          <t>01090344665</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>145712</t>
+          <t>96716</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>kk_3501053454</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01093015628</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>245323</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -7066,24 +7066,24 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -7100,17 +7100,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>227343</t>
+          <t>140860</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -7127,125 +7127,125 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>68751</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>jung1481</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>01024193371</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>205735</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>kk_3960572616</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01072737379</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>68751</t>
+          <t>270384</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>jeonhyel</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>01077942894</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>304102</t>
+          <t>268974</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>kk_3678962368</t>
+          <t>jung1481</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>01041028567</t>
+          <t>01024193371</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>250374</t>
+          <t>205735</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -7262,17 +7262,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>kk_4839542021</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>01089909663</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>304103</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -7282,105 +7282,105 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>kk_4839542021</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01089909663</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>174291</t>
+          <t>304103</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>coverdn</t>
+          <t>kk_4838920250</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>01086426866</t>
+          <t>01065688860</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>172406</t>
+          <t>304074</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>EDM_0413</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>jsu2080</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01094582080</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>123130</t>
+          <t>275256</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -7390,24 +7390,24 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -7424,44 +7424,44 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>kk_4237700483</t>
+          <t>kk_3220401027</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>01063041087</t>
+          <t>01037591063</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>273719</t>
+          <t>232602</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EDM_0413</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>chlwoghk83</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01038851983</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>304104</t>
+          <t>145712</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -7471,24 +7471,24 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>kk_4375333989</t>
+          <t>kk_3794951359</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>01091513985</t>
+          <t>01066481842</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>280145</t>
+          <t>257520</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -7498,105 +7498,105 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>js0987</t>
+          <t>kk_3796517297</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>01052819790</t>
+          <t>01040802850</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>110955</t>
+          <t>257878</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>richjm</t>
+          <t>kk_4839765445</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>01082909799</t>
+          <t>01076118972</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>122482</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>kk_4212157104</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>01062437191</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>272417</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>172790</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -7613,17 +7613,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>kk_4727505000</t>
+          <t>kk_2950194486</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>01066573797</t>
+          <t>01076104875</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>298110</t>
+          <t>216766</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -7633,51 +7633,51 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>kk_4288273717</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01020746624</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>275762</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>kk_4840174486</t>
+          <t>kk_4536846819</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>01064087457</t>
+          <t>01038223781</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>304131</t>
+          <t>287146</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7687,24 +7687,24 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>304101</t>
+          <t>304109</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7721,17 +7721,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>kk_3501053454</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>01093015628</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>245323</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7741,78 +7741,78 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>kk_3170564464</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01099188001</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>224948</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>219219</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7829,17 +7829,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>ganjing78</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01065121424</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>78590</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7856,125 +7856,125 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>maksim04</t>
+          <t>js0987</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>01063557978</t>
+          <t>01052819790</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>202013</t>
+          <t>110955</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>229454</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>kk_4839765445</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>01076118972</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>304111</t>
+          <t>304086</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>kk_4840035519</t>
+          <t>richjm</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>01086385010</t>
+          <t>01082909799</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>304121</t>
+          <t>122482</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_3380246984</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01040750851</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>240492</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7991,17 +7991,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -8018,71 +8018,71 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_4212157104</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01062437191</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>298138</t>
+          <t>272417</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>kk_3170564464</t>
+          <t>kk_3134493871</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>01099188001</t>
+          <t>01035918800</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>224948</t>
+          <t>222420</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8092,24 +8092,24 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>kk_4670878863</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01067207833</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>270708</t>
+          <t>294326</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8126,17 +8126,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>180321</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -8153,71 +8153,71 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>kk_2985598511</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01086703302</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>218005</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>kk_4838947856</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>01094709458</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>304075</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8227,24 +8227,24 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>kk_2950194486</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>01076104875</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>216766</t>
+          <t>136050</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8261,17 +8261,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>hodong1014</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>01044530048</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>64397</t>
+          <t>143826</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8281,24 +8281,24 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>fjsjhw</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>01050468291</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>192240</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8308,24 +8308,24 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants1</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8342,44 +8342,44 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>kk_4839821563</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01027951809</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>304112</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>byun7707</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01077391740</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>221630</t>
+          <t>161371</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8389,24 +8389,24 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>289364</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8423,17 +8423,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>hhpp123</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01042621121</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>294450</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8450,44 +8450,44 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>seopme</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>01074122238</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>304125</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>kk_4221652535</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01036858276</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>272849</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -8497,51 +8497,51 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>jeonhyel</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01077942894</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>304102</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>285491</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8551,24 +8551,24 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>kk_3466706406</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01055441553</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>243779</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8585,17 +8585,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>kyong74</t>
+          <t>kk_4538201048</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>01088245591</t>
+          <t>01071790372</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>22857</t>
+          <t>287217</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8612,17 +8612,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>kk_4839241951</t>
+          <t>kk_4839283126</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>01079146776</t>
+          <t>01024419045</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>304090</t>
+          <t>304093</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8632,24 +8632,24 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>kk_4680971786</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01074443726</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>294917</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8666,17 +8666,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>hhpp123</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>01042621121</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>294450</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8693,98 +8693,98 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>304124</t>
+          <t>304126</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>232010</t>
+          <t>219219</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>kk_4221652535</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>01036858276</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>272849</t>
+          <t>123130</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>kk_3466706406</t>
+          <t>coverdn</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>01055441553</t>
+          <t>01086426866</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>243779</t>
+          <t>172406</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8794,24 +8794,24 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0413</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>he0218</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01049289998</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>254710</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8821,24 +8821,24 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8855,17 +8855,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>kk_4484370599</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01052246899</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>136050</t>
+          <t>284447</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8882,98 +8882,98 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>kk_4237700483</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01063041087</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>273719</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>isaackwak</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01090599860</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>275913</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>kk_2985598511</t>
+          <t>kk_4840174486</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>01086703302</t>
+          <t>01064087457</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>218005</t>
+          <t>304131</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>kk_3796517297</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>01040802850</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>257878</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8983,105 +8983,105 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>kk_4839027252</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01084518813</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>140860</t>
+          <t>304083</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>kk_4839241951</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01079146776</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>304090</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>kk_4357899204</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>01082772838</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>279564</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>kk_4839027252</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>01084518813</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>304083</t>
+          <t>292319</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -9091,24 +9091,24 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -9125,17 +9125,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>kk_3794951359</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>01066481842</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>257520</t>
+          <t>208245</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9152,71 +9152,71 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>jsu2080</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>01094582080</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>275256</t>
+          <t>304113</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>kk_4375333989</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01091513985</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>304086</t>
+          <t>280145</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>kk_4538201048</t>
+          <t>kk_4727505000</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>01071790372</t>
+          <t>01066573797</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>287217</t>
+          <t>298110</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9226,24 +9226,24 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>chaser1</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>01038304145</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>178090</t>
+          <t>232010</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9253,51 +9253,51 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>kk_2915134680</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01085224711</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>304129</t>
+          <t>215670</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -9314,17 +9314,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>he0218</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>01049289998</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>254710</t>
+          <t>219525</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9334,78 +9334,78 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>292319</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>304101</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>kk_4517851709</t>
+          <t>chaser1</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>01066445714</t>
+          <t>01038304145</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>286074</t>
+          <t>178090</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9422,17 +9422,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9449,44 +9449,44 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>kk_3380246984</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>01040750851</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>240492</t>
+          <t>304104</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>304129</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9503,98 +9503,98 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>kk_4288273717</t>
+          <t>kwon9493</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>01020746624</t>
+          <t>01035589493</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>275762</t>
+          <t>107077</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>kwon9493</t>
+          <t>kk_3750120343</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>01035589493</t>
+          <t>01092908890</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>254168</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>kk_4839821563</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>01027951809</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>304112</t>
+          <t>229454</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>varam11</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01071373327</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>162562</t>
+          <t>102004</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9604,24 +9604,24 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0413</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>kk_4670878863</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>01067207833</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>294326</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9638,17 +9638,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>kk_4536846819</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>01038223781</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>287146</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -9665,17 +9665,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>mooner82</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>01037861045</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>148696</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -9692,44 +9692,44 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>kk_3678962368</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01041028567</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>304126</t>
+          <t>250374</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>kk_3750120343</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>01092908890</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>254168</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -547,22 +547,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_4755812472</t>
+          <t>kk_4270962450</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01022651918</t>
+          <t>01065174170</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -575,22 +575,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_4270962450</t>
+          <t>kk_4755812472</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01065174170</t>
+          <t>01022651918</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -659,22 +659,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_4814460268</t>
+          <t>lscbo76</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01064733325</t>
+          <t>01025029158</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -687,22 +687,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lscbo76</t>
+          <t>kk_4814460268</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01025029158</t>
+          <t>01064733325</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -715,78 +715,78 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>wjdgus5106</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01092085106</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_3016906903</t>
+          <t>wjdgus5106</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01050555122</t>
+          <t>01092085106</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>kk_3016906903</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01050555122</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -967,12 +967,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -995,22 +995,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_4293591148</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01086489252</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1023,22 +1023,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>zollee77</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01064740702</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1051,22 +1051,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_3817523531</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01090061449</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1079,22 +1079,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>zollee77</t>
+          <t>kk_3817523531</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01064740702</t>
+          <t>01090061449</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1107,12 +1107,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>kk_4837475331</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01046487707</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1135,40 +1135,40 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>j31goyung</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01096791280</t>
+          <t>01049366682</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1178,25 +1178,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_4837475331</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01046487707</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1206,35 +1206,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1247,12 +1247,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4833864791</t>
+          <t>kk_4829109495</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01076696985</t>
+          <t>01096791280</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1262,25 +1262,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>j31goyung</t>
+          <t>kk_4279317974</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01049366682</t>
+          <t>01086395686</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1290,35 +1290,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1331,22 +1331,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_4833864791</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01076696985</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1359,12 +1359,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_4279317974</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01086395686</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>EDM_0314</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1387,40 +1387,40 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>kk_3881036278</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01071425586</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>phs76825</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01091406949</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1443,12 +1443,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_3881036278</t>
+          <t>kk_4792317163</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01071425586</t>
+          <t>01055819917</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1471,12 +1471,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>phs76825</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01091406949</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1486,35 +1486,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>kk_4822475920</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01073932582</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1527,22 +1527,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>kk_4827961097</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01046347894</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1555,22 +1555,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1583,12 +1583,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>s09635</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01090472784</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1611,12 +1611,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1639,12 +1639,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1654,35 +1654,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4839289649</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01041713878</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1695,12 +1695,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4792317163</t>
+          <t>gupabaljjang</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01055819917</t>
+          <t>01027797881</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1723,22 +1723,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_4827961097</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01046347894</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1751,22 +1751,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>kk_3672780564</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01089459294</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -1779,12 +1779,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>kk_2863319761</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01027753767</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1794,25 +1794,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>hhkim1018</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01054122583</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1822,63 +1822,63 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_2863319761</t>
+          <t>kk_4839289649</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01027753767</t>
+          <t>01041713878</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_3672780564</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01089459294</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1891,68 +1891,68 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>gupabaljjang</t>
+          <t>s09635</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01027797881</t>
+          <t>01090472784</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4822475920</t>
+          <t>hhkim1018</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01073932582</t>
+          <t>01054122583</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0329</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>chcjddl</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01086228198</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1962,25 +1962,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_2824348249</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01025435357</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2003,40 +2003,40 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>wjhj1400</t>
+          <t>kk_2954792291</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01064023952</t>
+          <t>01086049859</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kjchan69</t>
+          <t>kk_2824348249</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01063792010</t>
+          <t>01025435357</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2059,50 +2059,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>kk_3605280738</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01063779875</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>kk_4836613952</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01041344927</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2115,12 +2115,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4318643192</t>
+          <t>wjhj1400</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01062525049</t>
+          <t>01064023952</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2130,35 +2130,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4234864746</t>
+          <t>luxurykim11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01062301880</t>
+          <t>01093252716</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2171,12 +2171,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4826804167</t>
+          <t>kk_4326567662</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01022256801</t>
+          <t>01046049921</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2186,25 +2186,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>kk_4318643192</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01062525049</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2214,25 +2214,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_3605280738</t>
+          <t>kk_4826804167</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01063779875</t>
+          <t>01022256801</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2242,35 +2242,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2283,12 +2283,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4326567662</t>
+          <t>kk_4750697279</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01046049921</t>
+          <t>01086127388</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2298,53 +2298,53 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>6941110100332</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_2954792291</t>
+          <t>kk_4826150317</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01086049859</t>
+          <t>01050140463</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>chcjddl</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01086228198</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2354,91 +2354,91 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4826150317</t>
+          <t>kk_4234864746</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01050140463</t>
+          <t>01062301880</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4750697279</t>
+          <t>kjchan69</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01086127388</t>
+          <t>01063792010</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4836613952</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01041344927</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2451,22 +2451,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -2479,22 +2479,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>kk_4485686054</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01030613096</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2507,40 +2507,40 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>hot0941</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01033140941</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4815312274</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01050357610</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2550,91 +2550,91 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_4679052952</t>
+          <t>qssa2000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01053553195</t>
+          <t>01020284430</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>kk_4679052952</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01053553195</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4485686054</t>
+          <t>kk_4840338408</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01030613096</t>
+          <t>01054621177</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2647,12 +2647,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4840292707</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01085257253</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2675,22 +2675,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>hw00185</t>
+          <t>kk_2805794827</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01032596566</t>
+          <t>01098906270</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2703,50 +2703,50 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4837856932</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01042710870</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>hw00185</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01032596566</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2759,22 +2759,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_2805794827</t>
+          <t>kk_4840292707</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01098906270</t>
+          <t>01085257253</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2787,162 +2787,162 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mobis</t>
+          <t>hhgg6482</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01090422686</t>
+          <t>01052195642</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_3205887201</t>
+          <t>kk_4836691459</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01063328335</t>
+          <t>01072445075</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4838507875</t>
+          <t>mobis</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01041366853</t>
+          <t>01090422686</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_2860000961</t>
+          <t>kk_4837856932</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01086061074</t>
+          <t>01042710870</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -2955,22 +2955,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4535433913</t>
+          <t>kk_3205887201</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01071714088</t>
+          <t>01063328335</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -2983,78 +2983,78 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4836691459</t>
+          <t>kk_4838507875</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01072445075</t>
+          <t>01041366853</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>kk_2860000961</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01086061074</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3067,50 +3067,50 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4533637391</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01090803497</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>kk_4815312274</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01050357610</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3123,96 +3123,96 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4840338408</t>
+          <t>kk_4535433913</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01054621177</t>
+          <t>01071714088</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>qssa2000</t>
+          <t>kk_4533637391</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01020284430</t>
+          <t>01090803497</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>hot0941</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01033140941</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_3487131753</t>
+          <t>poketgyu</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01041080962</t>
+          <t>01085474650</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3235,12 +3235,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>bking1234</t>
+          <t>kk_4200407916</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01086427715</t>
+          <t>01032980786</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3256,19 +3256,19 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3291,78 +3291,78 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>halla1001</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01097612449</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_3181933743</t>
+          <t>eumban</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01024077112</t>
+          <t>01089805431</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT2</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -3375,12 +3375,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3390,25 +3390,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>kk_4840404521</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01032660272</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3424,85 +3424,85 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>nhs1024</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01035177054</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIRST_PURCHASE_COUPON</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4840404521</t>
+          <t>kk_3181933743</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01032660272</t>
+          <t>01024077112</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT2</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_3799202460</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01051162376</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -3515,12 +3515,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>akilris</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01076225525</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3536,47 +3536,47 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>hisgogo</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01054110956</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>jyyon101</t>
+          <t>kk_3721509519</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01050119990</t>
+          <t>01097118472</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3592,19 +3592,19 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3620,47 +3620,47 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>halla1001</t>
+          <t>kk_4439122782</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01097612449</t>
+          <t>01028252500</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>ellieee</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01098996425</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3683,50 +3683,50 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4305076317</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01082835869</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -3739,12 +3739,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4204337741</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01085530637</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3754,30 +3754,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>eumban</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01089805431</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3788,19 +3788,19 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3810,53 +3810,53 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4303227124</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01037747441</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_3721509519</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01097118472</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3872,85 +3872,85 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>mwnew5</t>
+          <t>kk_3799202460</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01091343604</t>
+          <t>01051162376</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>kk_4305076317</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01082835869</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>kk_3152552457</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01031327516</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -3991,40 +3991,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>cloud84</t>
+          <t>bking1234</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01094808884</t>
+          <t>01086427715</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>alswjd7015</t>
+          <t>jyyon101</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01039137015</t>
+          <t>01050119990</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4047,17 +4047,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4200407916</t>
+          <t>nhs1024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01032980786</t>
+          <t>01035177054</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4068,19 +4068,19 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>dpfmxkdl</t>
+          <t>kk_4703272205</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01023221625</t>
+          <t>01062682325</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4090,25 +4090,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>HIGH_INTENT_NUDGE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>poketgyu</t>
+          <t>kk_4204337741</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01085474650</t>
+          <t>01085530637</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4118,25 +4118,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4152,29 +4152,29 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CART_REMINDER</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ellieee</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01098996425</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -4187,12 +4187,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>dpfmxkdl</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01023221625</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4215,22 +4215,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -4243,40 +4243,40 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_3152552457</t>
+          <t>alswjd7015</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01031327516</t>
+          <t>01039137015</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>kk_3487131753</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01041080962</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4299,12 +4299,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4439122782</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01028252500</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4327,40 +4327,40 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>mwnew5</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01091343604</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FIRST_PURCHASE_COUPON</t>
+          <t>HIGH_INTENT_NUDGE</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>cloud84</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01094808884</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4376,7 +4376,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>CART_REMINDER</t>
         </is>
       </c>
     </row>
@@ -4411,12 +4411,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4439,12 +4439,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4467,12 +4467,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4703272205</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01062682325</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E145"/>
+  <dimension ref="A1:E166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,27 +512,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>wooyes</t>
+          <t>kk_4755812472</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01093487391</t>
+          <t>01022651918</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119323</t>
+          <t>301088</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -566,81 +566,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_4755812472</t>
+          <t>kk_3649011176</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01022651918</t>
+          <t>01029317964</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>301088</t>
+          <t>249089</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_3649011176</t>
+          <t>antonio34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01029317964</t>
+          <t>01090296238</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>249089</t>
+          <t>142917</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>antonio34</t>
+          <t>kk_4814460268</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01090296238</t>
+          <t>01064733325</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>142917</t>
+          <t>302718</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,54 +674,54 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_4814460268</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01064733325</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>302718</t>
+          <t>246466</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_3016906903</t>
+          <t>wjdgus5106</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01050555122</t>
+          <t>01092085106</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>219318</t>
+          <t>302833</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
@@ -755,71 +755,71 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>kk_3016906903</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01050555122</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>246466</t>
+          <t>219318</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wjdgus5106</t>
+          <t>kk_4483270795</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01092085106</t>
+          <t>01051728139</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>302833</t>
+          <t>284407</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>greom73</t>
+          <t>somsea</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01086372526</t>
+          <t>01028811570</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>135272</t>
+          <t>201115</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -829,24 +829,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0209_LIGHTBAG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>somsea</t>
+          <t>mezzo304</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01028811570</t>
+          <t>01032400300</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>201115</t>
+          <t>119647</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -856,51 +856,51 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EDM_0209_LIGHTBAG</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>goril04624</t>
+          <t>kk_3817523531</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01047651746</t>
+          <t>01090061449</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>304009</t>
+          <t>262416</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01098876431</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>303476</t>
+          <t>276079</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -910,159 +910,159 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mezzo304</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01032400300</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>119647</t>
+          <t>254356</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_3817523531</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01090061449</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>262416</t>
+          <t>233095</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>233095</t>
+          <t>139095</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>EDM_0314</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_4293591148</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01086489252</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>276079</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>254356</t>
+          <t>215822</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>zollee77</t>
+          <t>kk_4279317974</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01064740702</t>
+          <t>01086395686</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>285531</t>
+          <t>275222</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1072,24 +1072,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_4837475331</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01046487707</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>303989</t>
+          <t>70258</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4833864791</t>
+          <t>kk_4829109495</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01076696985</t>
+          <t>01096791280</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>303759</t>
+          <t>303456</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>kk_4837475331</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01046487707</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>70258</t>
+          <t>303989</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_4279317974</t>
+          <t>j31goyung</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01086395686</t>
+          <t>01049366682</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>275222</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1180,24 +1180,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>278629</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1214,98 +1214,98 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>j31goyung</t>
+          <t>kk_4833864791</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01049366682</t>
+          <t>01076696985</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>303759</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01096791280</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>303456</t>
+          <t>247134</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>phs76825</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01091406949</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>215822</t>
+          <t>190331</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>kk_4792317163</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01055819917</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>278629</t>
+          <t>302105</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1315,24 +1315,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_2863319761</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01027753767</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>139095</t>
+          <t>213584</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1342,132 +1342,132 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4822475920</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01073932582</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>303081</t>
+          <t>277256</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>kk_3881036278</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01071425586</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>210511</t>
+          <t>266935</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_2863319761</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01027753767</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>213584</t>
+          <t>210511</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_4827961097</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01046347894</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>303384</t>
+          <t>216543</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hhkim1018</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01054122583</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>13471</t>
+          <t>285056</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1477,51 +1477,51 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_3672780564</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01089459294</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>250138</t>
+          <t>174647</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_3881036278</t>
+          <t>gupabaljjang</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01071425586</t>
+          <t>01027797881</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>266935</t>
+          <t>132338</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1531,132 +1531,132 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_4839289649</t>
+          <t>hhkim1018</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01041713878</t>
+          <t>01054122583</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>304094</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>EDM_0329</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>kk_4826150317</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01050140463</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>303786</t>
+          <t>303288</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>277256</t>
+          <t>268665</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>kk_4827961097</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01046347894</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>285056</t>
+          <t>303384</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4792317163</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01055819917</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>302105</t>
+          <t>303786</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1666,132 +1666,132 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>247134</t>
+          <t>114522</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>s09635</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01090472784</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>256102</t>
+          <t>154450</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>phs76825</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01091406949</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>190331</t>
+          <t>303592</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>kk_2954792291</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01086049859</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>174647</t>
+          <t>216977</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>kk_4234864746</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01062301880</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>114522</t>
+          <t>273540</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1801,51 +1801,51 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>kk_4826804167</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01022256801</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>268665</t>
+          <t>303320</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>gupabaljjang</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01027797881</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>132338</t>
+          <t>281393</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1855,24 +1855,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>chcjddl</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01086228198</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>216543</t>
+          <t>198759</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1882,51 +1882,51 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>154450</t>
+          <t>157510</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>chcjddl</t>
+          <t>kk_4318643192</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01086228198</t>
+          <t>01062525049</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>198759</t>
+          <t>277689</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -1970,54 +1970,54 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_4750697279</t>
+          <t>kk_3605280738</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01086127388</t>
+          <t>01063779875</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>300871</t>
+          <t>247209</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>kk_4840537683</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01085206466</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>281393</t>
+          <t>304154</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>303592</t>
+          <t>221644</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2098,51 +2098,51 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>wjhj1400</t>
+          <t>hhgg6482</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01064023952</t>
+          <t>01052195642</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>217554</t>
+          <t>290916</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_3605280738</t>
+          <t>qssa2000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01063779875</t>
+          <t>01020284430</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>247209</t>
+          <t>202308</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2152,51 +2152,51 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4326567662</t>
+          <t>kk_2805794827</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01046049921</t>
+          <t>01098906270</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>278302</t>
+          <t>211460</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4836613952</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01041344927</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>303935</t>
+          <t>304092</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2213,422 +2213,422 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4318643192</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01062525049</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>277689</t>
+          <t>173433</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_2954792291</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01086049859</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>216977</t>
+          <t>304077</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4234864746</t>
+          <t>kk_4840510971</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01062301880</t>
+          <t>01083115500</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>273540</t>
+          <t>304153</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4826804167</t>
+          <t>kk_4837599586</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01022256801</t>
+          <t>01026751676</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>303320</t>
+          <t>304003</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4826150317</t>
+          <t>kk_4679052952</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01050140463</t>
+          <t>01053553195</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>303288</t>
+          <t>294798</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>157510</t>
+          <t>142777</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4836691459</t>
+          <t>hot0941</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01072445075</t>
+          <t>01033140941</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>303939</t>
+          <t>139060</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>kk_4840738116</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01041260767</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>173433</t>
+          <t>304164</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>221644</t>
+          <t>302814</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_2860000961</t>
+          <t>kk_4535433913</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01086061074</t>
+          <t>01071714088</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>213449</t>
+          <t>287044</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>kk_4837856932</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01042710870</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>300186</t>
+          <t>304021</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>miraekoss</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01020213203</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>304092</t>
+          <t>183703</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>275307</t>
+          <t>300186</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>120212705670680427</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4838507875</t>
+          <t>pppjs95</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01041366853</t>
+          <t>01040085813</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>304055</t>
+          <t>149718</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>304077</t>
+          <t>250768</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>qssa2000</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01020284430</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>202308</t>
+          <t>304186</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2638,51 +2638,51 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4533637391</t>
+          <t>kk_4841482998</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01090803497</t>
+          <t>01050082734</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>286955</t>
+          <t>304194</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4679052952</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01053553195</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>294798</t>
+          <t>275307</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2692,56 +2692,56 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>kk_3205887201</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01063328335</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>302814</t>
+          <t>231050</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_3205887201</t>
+          <t>mobis</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01063328335</t>
+          <t>01090422686</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>231050</t>
+          <t>123959</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2753,17 +2753,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4837856932</t>
+          <t>kk_4841179120</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01042710870</t>
+          <t>01068577665</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>304021</t>
+          <t>304188</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2773,51 +2773,51 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4840292707</t>
+          <t>kk_4840949436</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01085257253</t>
+          <t>01064495993</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>304142</t>
+          <t>304178</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>kk_4840338408</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01054621177</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>290916</t>
+          <t>304143</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -2861,17 +2861,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4485686054</t>
+          <t>kk_4841155697</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01030613096</t>
+          <t>01041762160</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>284508</t>
+          <t>304187</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2881,213 +2881,213 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_2805794827</t>
+          <t>kk_4838507875</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01098906270</t>
+          <t>01041366853</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>211460</t>
+          <t>304055</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>hw00185</t>
+          <t>kk_2860000961</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01032596566</t>
+          <t>01086061074</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>94067</t>
+          <t>213449</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4840338408</t>
+          <t>kk_4841564061</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01054621177</t>
+          <t>01088968580</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>304143</t>
+          <t>304198</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>hot0941</t>
+          <t>kk_4533637391</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01033140941</t>
+          <t>01090803497</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>139060</t>
+          <t>286955</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>142777</t>
+          <t>259616</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4535433913</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01071714088</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>287044</t>
+          <t>244625</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>kk_4840712470</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01054536562</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>259616</t>
+          <t>304162</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mobis</t>
+          <t>kk_4840857472</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01090422686</t>
+          <t>01040551807</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>123959</t>
+          <t>304172</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3097,186 +3097,186 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4204337741</t>
+          <t>cloud84</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01085530637</t>
+          <t>01094808884</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>272072</t>
+          <t>129205</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>EDM_0411</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4200407916</t>
+          <t>kk_4841836389</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01032980786</t>
+          <t>01045794096</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>271924</t>
+          <t>304208</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>271278</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>bking1234</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01086427715</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>257110</t>
+          <t>276681</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4303227124</t>
+          <t>alswjd7015</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01037747441</t>
+          <t>01039137015</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>276681</t>
+          <t>191971</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4703272205</t>
+          <t>bking1234</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01062682325</t>
+          <t>01086427715</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>296093</t>
+          <t>257110</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_3181933743</t>
+          <t>kk_4204337741</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01024077112</t>
+          <t>01085530637</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>227397</t>
+          <t>272072</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3286,51 +3286,51 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>104766</t>
+          <t>219288</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4439122782</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01028252500</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>282053</t>
+          <t>227380</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3347,17 +3347,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>cloud84</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01094808884</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>129205</t>
+          <t>250075</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3367,159 +3367,159 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>kk_4305076317</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01082835869</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>276795</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>304147</t>
+          <t>128947</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>kk_4841501713</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01042996002</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>271278</t>
+          <t>304195</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_4841778210</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01087814274</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>250768</t>
+          <t>304202</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>kk_3721509519</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01097118472</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>281590</t>
+          <t>252253</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>244062</t>
+          <t>126315</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3529,78 +3529,78 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>jyyon101</t>
+          <t>kk_4200407916</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01050119990</t>
+          <t>01032980786</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>216194</t>
+          <t>271924</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ellieee</t>
+          <t>kk_4840404521</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01098996425</t>
+          <t>01032660272</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>203688</t>
+          <t>304145</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>188067</t>
+          <t>134664</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3617,71 +3617,71 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>nhs1024</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01035177054</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>71200</t>
+          <t>304177</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>120212705670680427</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3487131753</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01041080962</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>244823</t>
+          <t>304205</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>kk_4841095079</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01050906999</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>219288</t>
+          <t>304183</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3691,51 +3691,51 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_3799202460</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01051162376</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>258560</t>
+          <t>244062</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>134664</t>
+          <t>240051</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3752,287 +3752,287 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>kk_3487131753</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01041080962</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>244823</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>kk_4840763633</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01048116274</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>265508</t>
+          <t>304165</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>240051</t>
+          <t>304193</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>dpfmxkdl</t>
+          <t>ellieee</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01023221625</t>
+          <t>01098996425</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>158745</t>
+          <t>203688</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>halla1001</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01097612449</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>174486</t>
+          <t>12594</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4840404521</t>
+          <t>kk_3181933743</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01032660272</t>
+          <t>01024077112</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>304145</t>
+          <t>227397</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>126315</t>
+          <t>304147</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>eumban</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01089805431</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>153760</t>
+          <t>271442</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>kk_4841861142</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01052528559</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>244625</t>
+          <t>304210</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>poketgyu</t>
+          <t>acp1011</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01085474650</t>
+          <t>01045809723</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>157236</t>
+          <t>67149</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>halla1001</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01097612449</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>266946</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4042,51 +4042,51 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_3721509519</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01097118472</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>252253</t>
+          <t>304190</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>eumban</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01089805431</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>271442</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4096,51 +4096,51 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_3152552457</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01031327516</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>223539</t>
+          <t>304174</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>kk_4568748102</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01054073523</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>217199</t>
+          <t>288185</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4150,132 +4150,132 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>227380</t>
+          <t>304158</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>250075</t>
+          <t>304168</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>217199</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>alswjd7015</t>
+          <t>kk_4841572668</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01039137015</t>
+          <t>01024164342</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>191971</t>
+          <t>304199</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>akilris</t>
+          <t>jyyon101</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01076225525</t>
+          <t>01050119990</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>266946</t>
+          <t>216194</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4285,61 +4285,628 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>mwnew5</t>
+          <t>nhs1024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01091343604</t>
+          <t>01035177054</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>263720</t>
+          <t>71200</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4305076317</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01082835869</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>276795</t>
+          <t>207211</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>kk_3858585698</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>01092163429</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>265508</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>KAKAO_alimtalk</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>dpfmxkdl</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>01023221625</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>158745</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Email_mkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>manong0821</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>01036923281</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>66211</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>LMS_ECOM_0410exclusive2</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>nikemkr</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>01032361592</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>145423</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>kk_4351409443</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>01050585646</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>279282</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>kk_4841140461</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>01088944649</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>304185</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>kk_3799202460</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>01051162376</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>258560</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>KAKAO_alimtalk</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>kk_3152552457</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>01031327516</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>223539</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>LMS_ECOM_0410exclusive2</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>kk_4840669442</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>01093940957</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>304160</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>jsb0425</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>01037883670</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>104766</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>kk_3837527580</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>01084311738</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>264113</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>LMS_ECOM_0410exclusive2</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>poketgyu</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>01085474650</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>157236</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>kk_4427490834</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>01034704205</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>281590</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>LMS_ECOM_0410exclusive2</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>jyseoul</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>01054813799</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>234558</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>kk_4840846776</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>01055961435</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>304170</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>[PF]전환_회원가입(유사)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>mwnew5</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>01091343604</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>263720</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>kk_4703272205</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>01062682325</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>296093</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>LMS_ECOM_0410exclusive2</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>hisgogo</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>01054110956</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>174486</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>nesto1</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>01056603953</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>125251</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>KAKAO_alimtalk</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>kk_4840872605</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>01063782216</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>304173</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>(organic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>kyoungs424</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>01041509204</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>153760</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E166"/>
+  <dimension ref="A1:E165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,54 +512,54 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kk_4755812472</t>
+          <t>kk_4270962450</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01022651918</t>
+          <t>01065174170</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>301088</t>
+          <t>274867</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_4270962450</t>
+          <t>kk_4755812472</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01065174170</t>
+          <t>01022651918</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>274867</t>
+          <t>301088</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -674,17 +674,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>josolha</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01052056266</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>246466</t>
+          <t>303793</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -694,115 +694,115 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>wjdgus5106</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01092085106</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>302833</t>
+          <t>246466</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>josolha</t>
+          <t>kk_3016906903</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01052056266</t>
+          <t>01050555122</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>303793</t>
+          <t>219318</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_3016906903</t>
+          <t>kk_4483270795</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01050555122</t>
+          <t>01051728139</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>219318</t>
+          <t>284407</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kk_4483270795</t>
+          <t>wjdgus5106</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01051728139</t>
+          <t>01092085106</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>284407</t>
+          <t>302833</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
@@ -890,17 +890,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_4293591148</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01086489252</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>276079</t>
+          <t>254356</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -910,105 +910,105 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>254356</t>
+          <t>139095</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EDM_0314</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>233095</t>
+          <t>276079</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>139095</t>
+          <t>233095</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_4279317974</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01086395686</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>275222</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1018,51 +1018,51 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>215822</t>
+          <t>70258</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_4279317974</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01086395686</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>275222</t>
+          <t>278629</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1072,24 +1072,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>70258</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1099,34 +1099,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>j31goyung</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01096791280</t>
+          <t>01049366682</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>303456</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -1160,54 +1160,54 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>j31goyung</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01049366682</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>215822</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>kk_4829109495</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01096791280</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>278629</t>
+          <t>303456</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
     </row>
@@ -1241,17 +1241,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>phs76825</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01091406949</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>247134</t>
+          <t>190331</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1268,17 +1268,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>phs76825</t>
+          <t>gupabaljjang</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01091406949</t>
+          <t>01027797881</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>190331</t>
+          <t>132338</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1288,24 +1288,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_4792317163</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01055819917</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>302105</t>
+          <t>174647</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
     </row>
@@ -1349,98 +1349,98 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>277256</t>
+          <t>247134</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_3881036278</t>
+          <t>kk_4826150317</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01071425586</t>
+          <t>01050140463</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>266935</t>
+          <t>303288</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>210511</t>
+          <t>303786</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>kk_4792317163</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01055819917</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>216543</t>
+          <t>302105</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1450,51 +1450,51 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>285056</t>
+          <t>114522</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>hhkim1018</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01054122583</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>174647</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1504,24 +1504,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>EDM_0329</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>gupabaljjang</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01027797881</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>132338</t>
+          <t>268665</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1531,51 +1531,51 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>hhkim1018</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01054122583</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>13471</t>
+          <t>277256</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_4826150317</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01050140463</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>303288</t>
+          <t>210511</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1585,78 +1585,78 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>kk_4827961097</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01046347894</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>268665</t>
+          <t>303384</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4827961097</t>
+          <t>kk_3881036278</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01046347894</t>
+          <t>01071425586</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>303384</t>
+          <t>266935</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>303786</t>
+          <t>285056</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1666,51 +1666,51 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>114522</t>
+          <t>216543</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>kk_2824348249</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01025435357</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>154450</t>
+          <t>212661</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1720,61 +1720,61 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>303592</t>
+          <t>281393</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_2954792291</t>
+          <t>kjchan69</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01086049859</t>
+          <t>01063792010</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>216977</t>
+          <t>256978</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
@@ -1808,17 +1808,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4826804167</t>
+          <t>kk_4840537683</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01022256801</t>
+          <t>01085206466</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>303320</t>
+          <t>304154</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1828,24 +1828,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>kk_3605280738</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01063779875</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>281393</t>
+          <t>247209</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1855,51 +1855,51 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>chcjddl</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01086228198</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>198759</t>
+          <t>303592</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>kk_4826804167</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01022256801</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>157510</t>
+          <t>303320</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1909,24 +1909,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4318643192</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01062525049</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>277689</t>
+          <t>154450</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1936,24 +1936,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kjchan69</t>
+          <t>kk_4318643192</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01063792010</t>
+          <t>01062525049</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>256978</t>
+          <t>277689</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1963,88 +1963,88 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_3605280738</t>
+          <t>kk_2954792291</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01063779875</t>
+          <t>01086049859</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>247209</t>
+          <t>216977</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4840537683</t>
+          <t>chcjddl</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01085206466</t>
+          <t>01086228198</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>304154</t>
+          <t>198759</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_2824348249</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01025435357</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>212661</t>
+          <t>157510</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>kk_3205887201</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01063328335</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>221644</t>
+          <t>231050</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2098,34 +2098,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>kk_4679052952</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01053553195</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>290916</t>
+          <t>294798</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -2159,17 +2159,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_2805794827</t>
+          <t>kk_4837856932</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01098906270</t>
+          <t>01042710870</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>211460</t>
+          <t>304021</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2179,83 +2179,83 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>pppjs95</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01040085813</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>304092</t>
+          <t>149718</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>kk_4533637391</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01090803497</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>173433</t>
+          <t>286955</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>304077</t>
+          <t>142777</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2267,44 +2267,44 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4840510971</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01083115500</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>304153</t>
+          <t>304092</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4837599586</t>
+          <t>kk_4841155697</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01026751676</t>
+          <t>01041762160</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>304003</t>
+          <t>304187</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2314,78 +2314,78 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4679052952</t>
+          <t>hhgg6482</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01053553195</t>
+          <t>01052195642</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>294798</t>
+          <t>290916</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>miraekoss</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01020213203</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>142777</t>
+          <t>183703</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>hot0941</t>
+          <t>kk_4815312274</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01033140941</t>
+          <t>01050357610</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>139060</t>
+          <t>302743</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2395,24 +2395,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4840738116</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01041260767</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>304164</t>
+          <t>304186</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2422,24 +2422,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>kk_4841179120</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01068577665</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>302814</t>
+          <t>304188</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2449,78 +2449,78 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4535433913</t>
+          <t>kk_2860000961</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01071714088</t>
+          <t>01086061074</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>287044</t>
+          <t>213449</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_4837856932</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01042710870</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>304021</t>
+          <t>250768</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>miraekoss</t>
+          <t>kk_2805794827</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01020213203</t>
+          <t>01098906270</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>211460</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2530,24 +2530,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>300186</t>
+          <t>221644</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2557,51 +2557,51 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>pppjs95</t>
+          <t>kk_4838507875</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01040085813</t>
+          <t>01041366853</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>149718</t>
+          <t>304055</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_4840510971</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01083115500</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>250768</t>
+          <t>304153</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2611,24 +2611,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4841152170</t>
+          <t>kk_4840338408</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01050200309</t>
+          <t>01054621177</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>304186</t>
+          <t>304143</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2645,71 +2645,71 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4841482998</t>
+          <t>mobis</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01050082734</t>
+          <t>01090422686</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>304194</t>
+          <t>123959</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>275307</t>
+          <t>259616</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_3205887201</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01063328335</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>231050</t>
+          <t>304077</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2719,78 +2719,78 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mobis</t>
+          <t>kk_4841482998</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01090422686</t>
+          <t>01050082734</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>123959</t>
+          <t>304194</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4841179120</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01068577665</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>304188</t>
+          <t>300186</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>120212705670680427</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4840949436</t>
+          <t>hot0941</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01064495993</t>
+          <t>01033140941</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>304178</t>
+          <t>139060</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2800,51 +2800,51 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4840338408</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01054621177</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>304143</t>
+          <t>275307</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4815312274</t>
+          <t>kk_4837599586</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01050357610</t>
+          <t>01026751676</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>302743</t>
+          <t>304003</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2854,24 +2854,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4841155697</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01041762160</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>304187</t>
+          <t>302814</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2881,105 +2881,105 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4838507875</t>
+          <t>kk_4840738116</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01041366853</t>
+          <t>01041260767</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>304055</t>
+          <t>304164</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_2860000961</t>
+          <t>kk_4841564061</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01086061074</t>
+          <t>01088968580</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>213449</t>
+          <t>304198</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4841564061</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01088968580</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>304198</t>
+          <t>173433</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4533637391</t>
+          <t>kk_4840949436</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01090803497</t>
+          <t>01064495993</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>286955</t>
+          <t>304178</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2989,240 +2989,240 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>kk_4535433913</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01071714088</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>259616</t>
+          <t>287044</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>poketgyu</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01085474650</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>244625</t>
+          <t>157236</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4840712470</t>
+          <t>dpfmxkdl</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01054536562</t>
+          <t>01023221625</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>304162</t>
+          <t>158745</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4840857472</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01040551807</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>304172</t>
+          <t>266946</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>cloud84</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01094808884</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>129205</t>
+          <t>304174</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>EDM_0411</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4841836389</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01045794096</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>304208</t>
+          <t>250075</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>ellieee</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01098996425</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>271278</t>
+          <t>203688</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4303227124</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01037747441</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>276681</t>
+          <t>240051</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>alswjd7015</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01039137015</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>191971</t>
+          <t>126315</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3232,51 +3232,51 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>bking1234</t>
+          <t>mwnew5</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01086427715</t>
+          <t>01091343604</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>257110</t>
+          <t>263720</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4204337741</t>
+          <t>kk_4703272205</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01085530637</t>
+          <t>01062682325</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>272072</t>
+          <t>296093</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3286,78 +3286,78 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>219288</t>
+          <t>244062</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>cloud84</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01094808884</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>227380</t>
+          <t>129205</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EDM_0411</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>250075</t>
+          <t>265508</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3367,132 +3367,132 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4305076317</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01082835869</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>276795</t>
+          <t>304177</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>120212705670680427</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>304147</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4841501713</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01042996002</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>304195</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4841778210</t>
+          <t>manong0821</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01087814274</t>
+          <t>01036923281</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>304202</t>
+          <t>66211</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_3721509519</t>
+          <t>kk_4841095079</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01097118472</t>
+          <t>01050906999</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>252253</t>
+          <t>304183</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3502,132 +3502,132 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>126315</t>
+          <t>271278</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_4200407916</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01032980786</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>271924</t>
+          <t>304168</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4840404521</t>
+          <t>nhs1024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01032660272</t>
+          <t>01035177054</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>304145</t>
+          <t>71200</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>134664</t>
+          <t>153760</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4840930255</t>
+          <t>kk_4841572668</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01092600071</t>
+          <t>01024164342</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>304177</t>
+          <t>304199</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3637,24 +3637,24 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>kk_3721509519</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01097118472</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>304205</t>
+          <t>252253</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3664,105 +3664,105 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4841095079</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01050906999</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>304183</t>
+          <t>227380</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>244062</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>240051</t>
+          <t>145423</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_3487131753</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01041080962</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>244823</t>
+          <t>304193</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3772,51 +3772,51 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4840763633</t>
+          <t>alswjd7015</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01048116274</t>
+          <t>01039137015</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>304165</t>
+          <t>191971</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_4841470777</t>
+          <t>kk_4841861142</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01067860344</t>
+          <t>01052528559</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>304193</t>
+          <t>304210</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3826,159 +3826,159 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ellieee</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01098996425</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>203688</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>halla1001</t>
+          <t>eumban</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01097612449</t>
+          <t>01089805431</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>271442</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_3181933743</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01024077112</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>227397</t>
+          <t>304205</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>304147</t>
+          <t>281590</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>eumban</t>
+          <t>kk_3487131753</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01089805431</t>
+          <t>01041080962</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>271442</t>
+          <t>244823</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4841861142</t>
+          <t>kk_4840404521</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01052528559</t>
+          <t>01032660272</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>304210</t>
+          <t>304145</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4022,17 +4022,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>akilris</t>
+          <t>halla1001</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01076225525</t>
+          <t>01097612449</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>266946</t>
+          <t>12594</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4042,132 +4042,132 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>217199</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>kk_4840763633</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01048116274</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>188067</t>
+          <t>304165</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4840913383</t>
+          <t>kk_3799202460</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01099887927</t>
+          <t>01051162376</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>304174</t>
+          <t>258560</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4568748102</t>
+          <t>kk_4840669442</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01054073523</t>
+          <t>01093940957</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>288185</t>
+          <t>304160</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4840658838</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01039292600</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>304158</t>
+          <t>219288</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4177,24 +4177,24 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4840817001</t>
+          <t>kk_4841836389</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01085963383</t>
+          <t>01045794096</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>304168</t>
+          <t>304208</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4211,152 +4211,152 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>217199</t>
+          <t>134664</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4841572668</t>
+          <t>kk_4200407916</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01024164342</t>
+          <t>01032980786</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>304199</t>
+          <t>271924</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>jyyon101</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01050119990</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>216194</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>nhs1024</t>
+          <t>kk_4841778210</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01035177054</t>
+          <t>01087814274</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>71200</t>
+          <t>304202</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>bking1234</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01086427715</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>257110</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>kk_4568748102</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01054073523</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>265508</t>
+          <t>288185</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4366,78 +4366,78 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>dpfmxkdl</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01023221625</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>158745</t>
+          <t>207211</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>manong0821</t>
+          <t>kk_4841501713</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01036923281</t>
+          <t>01042996002</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>66211</t>
+          <t>304195</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4840712470</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01054536562</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>145423</t>
+          <t>304162</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4447,51 +4447,51 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_4351409443</t>
+          <t>kk_4305076317</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01050585646</t>
+          <t>01082835869</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>279282</t>
+          <t>276795</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4841140461</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01088944649</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>304185</t>
+          <t>304190</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4508,125 +4508,125 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_3799202460</t>
+          <t>hisgogo</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01051162376</t>
+          <t>01054110956</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>258560</t>
+          <t>174486</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_3152552457</t>
+          <t>kk_4840857472</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01031327516</t>
+          <t>01040551807</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>223539</t>
+          <t>304172</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4840669442</t>
+          <t>kk_4840872605</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01093940957</t>
+          <t>01063782216</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>304160</t>
+          <t>304173</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_4351409443</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01050585646</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>104766</t>
+          <t>279282</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>kk_3181933743</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01024077112</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>227397</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4643,17 +4643,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>poketgyu</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01085474650</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>157236</t>
+          <t>128947</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4663,51 +4663,51 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>281590</t>
+          <t>304158</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>jyseoul</t>
+          <t>kk_4840846776</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01054813799</t>
+          <t>01055961435</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>234558</t>
+          <t>304170</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4717,51 +4717,51 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4840846776</t>
+          <t>kk_3152552457</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01055961435</t>
+          <t>01031327516</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>304170</t>
+          <t>223539</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>mwnew5</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01091343604</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>263720</t>
+          <t>276681</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4771,24 +4771,24 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4703272205</t>
+          <t>kk_4204337741</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01062682325</t>
+          <t>01085530637</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>296093</t>
+          <t>272072</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4798,78 +4798,78 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>jyyon101</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01050119990</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>174486</t>
+          <t>216194</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>kk_4841140461</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01088944649</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>304185</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4840872605</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01063782216</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>304173</t>
+          <t>244625</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4879,34 +4879,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(organic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>kyoungs424</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>01041509204</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>153760</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -620,17 +620,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_4814460268</t>
+          <t>lscbo76</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01064733325</t>
+          <t>01025029158</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>302718</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -640,24 +640,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lscbo76</t>
+          <t>kk_4814460268</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01025029158</t>
+          <t>01064733325</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>123029</t>
+          <t>302718</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -667,105 +667,105 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>josolha</t>
+          <t>wjdgus5106</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01052056266</t>
+          <t>01092085106</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>303793</t>
+          <t>302833</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>kk_3016906903</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01050555122</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>246466</t>
+          <t>219318</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_3016906903</t>
+          <t>kk_4483270795</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01050555122</t>
+          <t>01051728139</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>219318</t>
+          <t>284407</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_4483270795</t>
+          <t>josolha</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01051728139</t>
+          <t>01052056266</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>284407</t>
+          <t>303793</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -775,34 +775,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wjdgus5106</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01092085106</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>302833</t>
+          <t>246466</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -836,108 +836,108 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mezzo304</t>
+          <t>kk_3817523531</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01032400300</t>
+          <t>01090061449</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>119647</t>
+          <t>262416</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kk_3817523531</t>
+          <t>mezzo304</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01090061449</t>
+          <t>01032400300</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>262416</t>
+          <t>119647</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>254356</t>
+          <t>139095</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EDM_0314</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>139095</t>
+          <t>233095</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -971,27 +971,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>233095</t>
+          <t>254356</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>70258</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1045,51 +1045,51 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>kk_4833864791</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01076696985</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>278629</t>
+          <t>303759</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_4837475331</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01046487707</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>303989</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1099,51 +1099,51 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>j31goyung</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01049366682</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>215822</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4837475331</t>
+          <t>j31goyung</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01046487707</t>
+          <t>01049366682</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>303989</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>kk_4829109495</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01096791280</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>215822</t>
+          <t>303456</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1180,78 +1180,78 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01096791280</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>303456</t>
+          <t>70258</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4833864791</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01076696985</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>303759</t>
+          <t>278629</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>phs76825</t>
+          <t>hhkim1018</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01091406949</t>
+          <t>01054122583</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>190331</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1261,24 +1261,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0329</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gupabaljjang</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01027797881</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>132338</t>
+          <t>174647</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1288,24 +1288,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>kk_4792317163</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01055819917</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>174647</t>
+          <t>302105</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1315,51 +1315,51 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_2863319761</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01027753767</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>213584</t>
+          <t>114522</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>247134</t>
+          <t>303786</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1369,78 +1369,78 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_4826150317</t>
+          <t>kk_2863319761</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01050140463</t>
+          <t>01027753767</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>303288</t>
+          <t>213584</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>kk_4826150317</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01050140463</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>303786</t>
+          <t>303288</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_4792317163</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01055819917</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>302105</t>
+          <t>247134</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1450,51 +1450,51 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>114522</t>
+          <t>277256</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>hhkim1018</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01054122583</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>13471</t>
+          <t>268665</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1504,115 +1504,115 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>kk_4827961097</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01046347894</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>268665</t>
+          <t>303384</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>phs76825</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01091406949</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>277256</t>
+          <t>190331</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>210511</t>
+          <t>285056</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4827961097</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01046347894</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>303384</t>
+          <t>216543</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
@@ -1646,17 +1646,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>gupabaljjang</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01027797881</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>285056</t>
+          <t>132338</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1673,44 +1673,44 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>216543</t>
+          <t>210511</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_2824348249</t>
+          <t>kk_4318643192</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01025435357</t>
+          <t>01062525049</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>212661</t>
+          <t>277689</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1720,51 +1720,51 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>kk_2954792291</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01086049859</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>281393</t>
+          <t>216977</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kjchan69</t>
+          <t>chcjddl</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01063792010</t>
+          <t>01086228198</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>256978</t>
+          <t>198759</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1774,51 +1774,51 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_4234864746</t>
+          <t>kk_4826804167</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01062301880</t>
+          <t>01022256801</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>273540</t>
+          <t>303320</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4840537683</t>
+          <t>luxurykim11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01085206466</t>
+          <t>01093252716</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>304154</t>
+          <t>80194</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1828,78 +1828,78 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_3605280738</t>
+          <t>kk_4840537683</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01063779875</t>
+          <t>01085206466</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>247209</t>
+          <t>304154</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_2824348249</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01025435357</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>303592</t>
+          <t>212661</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_4826804167</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01022256801</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>303320</t>
+          <t>157510</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1909,24 +1909,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>154450</t>
+          <t>281393</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1936,78 +1936,78 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4318643192</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01062525049</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>277689</t>
+          <t>303592</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_2954792291</t>
+          <t>kjchan69</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01086049859</t>
+          <t>01063792010</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>216977</t>
+          <t>256978</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>chcjddl</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01086228198</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>198759</t>
+          <t>154450</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2017,110 +2017,110 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>kk_3605280738</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01063779875</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>157510</t>
+          <t>247209</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>kk_4234864746</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01062301880</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>80194</t>
+          <t>273540</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_3205887201</t>
+          <t>kk_4841179120</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01063328335</t>
+          <t>01068577665</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>231050</t>
+          <t>304188</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4679052952</t>
+          <t>kk_3205887201</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01053553195</t>
+          <t>01063328335</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>294798</t>
+          <t>231050</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2132,71 +2132,71 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>qssa2000</t>
+          <t>miraekoss</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01020284430</t>
+          <t>01020213203</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>202308</t>
+          <t>183703</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4837856932</t>
+          <t>kk_4841564061</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01042710870</t>
+          <t>01088968580</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>304021</t>
+          <t>304198</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>pppjs95</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01040085813</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>149718</t>
+          <t>304186</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2206,186 +2206,186 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4533637391</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01090803497</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>286955</t>
+          <t>304092</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>kk_4840338408</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01054621177</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>142777</t>
+          <t>304143</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>304092</t>
+          <t>221644</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4841155697</t>
+          <t>kk_4840510971</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01041762160</t>
+          <t>01083115500</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>304187</t>
+          <t>304153</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>kk_4815312274</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01050357610</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>290916</t>
+          <t>302743</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>miraekoss</t>
+          <t>kk_4840738116</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01020213203</t>
+          <t>01041260767</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>304164</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4815312274</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01050357610</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>302743</t>
+          <t>302814</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2395,24 +2395,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4841152170</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01050200309</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>304186</t>
+          <t>304077</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2422,375 +2422,375 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4841179120</t>
+          <t>kk_4841482998</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01068577665</t>
+          <t>01050082734</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>304188</t>
+          <t>304194</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_2860000961</t>
+          <t>hhgg6482</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01086061074</t>
+          <t>01052195642</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>213449</t>
+          <t>290916</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_4535433913</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01071714088</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>250768</t>
+          <t>287044</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_2805794827</t>
+          <t>pppjs95</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01098906270</t>
+          <t>01040085813</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>211460</t>
+          <t>149718</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>kk_4841155697</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01041762160</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>221644</t>
+          <t>304187</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4838507875</t>
+          <t>kk_4533637391</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01041366853</t>
+          <t>01090803497</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>304055</t>
+          <t>286955</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4840510971</t>
+          <t>hot0941</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01083115500</t>
+          <t>01033140941</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>304153</t>
+          <t>139060</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4840338408</t>
+          <t>kk_2860000961</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01054621177</t>
+          <t>01086061074</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>304143</t>
+          <t>213449</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>mobis</t>
+          <t>kk_4838507875</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01090422686</t>
+          <t>01041366853</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>123959</t>
+          <t>304055</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>259616</t>
+          <t>300186</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>120212705670680427</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>kk_4679052952</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01053553195</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>304077</t>
+          <t>294798</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_4841482998</t>
+          <t>kk_4837856932</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01050082734</t>
+          <t>01042710870</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>304194</t>
+          <t>304021</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>mobis</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01090422686</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>300186</t>
+          <t>123959</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>hot0941</t>
+          <t>kk_2805794827</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01033140941</t>
+          <t>01098906270</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>139060</t>
+          <t>211460</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2800,24 +2800,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>kk_4840949436</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01064495993</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>275307</t>
+          <t>304178</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2827,186 +2827,186 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4837599586</t>
+          <t>qssa2000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01026751676</t>
+          <t>01020284430</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>304003</t>
+          <t>202308</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>302814</t>
+          <t>173433</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4840738116</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01041260767</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>304164</t>
+          <t>259616</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4841564061</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01088968580</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>304198</t>
+          <t>275307</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>173433</t>
+          <t>250768</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4840949436</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01064495993</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>304178</t>
+          <t>142777</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4535433913</t>
+          <t>kk_4837599586</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01071714088</t>
+          <t>01026751676</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>287044</t>
+          <t>304003</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3016,78 +3016,78 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>poketgyu</t>
+          <t>kk_4840872605</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01085474650</t>
+          <t>01063782216</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>157236</t>
+          <t>304173</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>dpfmxkdl</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01023221625</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>158745</t>
+          <t>240051</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>akilris</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01076225525</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>266946</t>
+          <t>145423</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3097,24 +3097,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4840913383</t>
+          <t>jyyon101</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01099887927</t>
+          <t>01050119990</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>304174</t>
+          <t>216194</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3131,152 +3131,152 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>250075</t>
+          <t>304174</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ellieee</t>
+          <t>kk_4841778210</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01098996425</t>
+          <t>01087814274</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>203688</t>
+          <t>304202</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>240051</t>
+          <t>304158</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>126315</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>mwnew5</t>
+          <t>alswjd7015</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01091343604</t>
+          <t>01039137015</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>263720</t>
+          <t>191971</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4703272205</t>
+          <t>bking1234</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01062682325</t>
+          <t>01086427715</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>296093</t>
+          <t>257110</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3293,17 +3293,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>cloud84</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01094808884</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>244062</t>
+          <t>129205</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3313,186 +3313,186 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_0411</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>cloud84</t>
+          <t>kk_4840857472</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01094808884</t>
+          <t>01040551807</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>129205</t>
+          <t>304172</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>EDM_0411</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>kk_4841836389</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01045794096</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>265508</t>
+          <t>304208</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4840930255</t>
+          <t>kk_4200407916</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01092600071</t>
+          <t>01032980786</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>304177</t>
+          <t>271924</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>304147</t>
+          <t>126315</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>kk_4840712470</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01054536562</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>304162</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>manong0821</t>
+          <t>kk_4840763633</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01036923281</t>
+          <t>01048116274</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>66211</t>
+          <t>304165</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4841095079</t>
+          <t>kk_4351409443</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01050906999</t>
+          <t>01050585646</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>304183</t>
+          <t>279282</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3502,24 +3502,24 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>mwnew5</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01091343604</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>271278</t>
+          <t>263720</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
     </row>
@@ -3563,71 +3563,71 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>nhs1024</t>
+          <t>poketgyu</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01035177054</t>
+          <t>01085474650</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>71200</t>
+          <t>157236</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>hisgogo</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01054110956</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>153760</t>
+          <t>174486</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4841572668</t>
+          <t>kk_4840404521</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01024164342</t>
+          <t>01032660272</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>304199</t>
+          <t>304145</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3637,24 +3637,24 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3721509519</t>
+          <t>halla1001</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01097118472</t>
+          <t>01097612449</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>252253</t>
+          <t>12594</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3664,78 +3664,78 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>227380</t>
+          <t>153760</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_4841140461</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01088944649</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>104766</t>
+          <t>304185</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4841501713</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01042996002</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>145423</t>
+          <t>304195</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3745,24 +3745,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4841470777</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01067860344</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>304193</t>
+          <t>128947</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3772,24 +3772,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>alswjd7015</t>
+          <t>kk_3181933743</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01039137015</t>
+          <t>01024077112</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>191971</t>
+          <t>227397</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3799,132 +3799,132 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_4841861142</t>
+          <t>kk_4204337741</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01052528559</t>
+          <t>01085530637</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>304210</t>
+          <t>272072</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>kk_4841572668</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01024164342</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>188067</t>
+          <t>304199</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>eumban</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01089805431</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>271442</t>
+          <t>207211</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>kk_3799202460</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01051162376</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>304205</t>
+          <t>258560</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>kk_4703272205</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01062682325</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>281590</t>
+          <t>296093</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3941,17 +3941,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_3487131753</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01041080962</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>244823</t>
+          <t>304193</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4840404521</t>
+          <t>kk_3721509519</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01032660272</t>
+          <t>01097118472</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>304145</t>
+          <t>252253</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3988,51 +3988,51 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>acp1011</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01045809723</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>67149</t>
+          <t>250075</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>halla1001</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01097612449</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>304205</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4049,71 +4049,71 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>acp1011</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01045809723</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>217199</t>
+          <t>67149</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_4840763633</t>
+          <t>eumban</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01048116274</t>
+          <t>01089805431</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>304165</t>
+          <t>271442</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_3799202460</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01051162376</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>258560</t>
+          <t>265508</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4130,44 +4130,44 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4840669442</t>
+          <t>kk_3487131753</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01093940957</t>
+          <t>01041080962</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>304160</t>
+          <t>244823</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>219288</t>
+          <t>276681</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4177,78 +4177,78 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4841836389</t>
+          <t>kk_3152552457</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01045794096</t>
+          <t>01031327516</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>304208</t>
+          <t>223539</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>134664</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4200407916</t>
+          <t>kk_4305076317</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01032980786</t>
+          <t>01082835869</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>271924</t>
+          <t>276795</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4265,368 +4265,368 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>271278</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4841778210</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01087814274</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>304202</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>bking1234</t>
+          <t>kk_4840669442</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01086427715</t>
+          <t>01093940957</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>257110</t>
+          <t>304160</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_4568748102</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01054073523</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>288185</t>
+          <t>219288</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>kk_4841095079</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01050906999</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>304183</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4841501713</t>
+          <t>ellieee</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01042996002</t>
+          <t>01098996425</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>304195</t>
+          <t>203688</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4840712470</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01054536562</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>304162</t>
+          <t>244062</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_4305076317</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01082835869</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>276795</t>
+          <t>304147</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>304177</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>120212705670680427</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>174486</t>
+          <t>227380</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4840857472</t>
+          <t>nhs1024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01040551807</t>
+          <t>01035177054</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>304172</t>
+          <t>71200</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4840872605</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01063782216</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>304173</t>
+          <t>217199</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4351409443</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01050585646</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>279282</t>
+          <t>244625</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_3181933743</t>
+          <t>kk_4568748102</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01024077112</t>
+          <t>01054073523</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>227397</t>
+          <t>288185</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4636,105 +4636,105 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>281590</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4840658838</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01039292600</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>304158</t>
+          <t>134664</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_4840846776</t>
+          <t>manong0821</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01055961435</t>
+          <t>01036923281</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>304170</t>
+          <t>66211</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_3152552457</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01031327516</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>223539</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4751,17 +4751,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4303227124</t>
+          <t>kk_4841861142</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01037747441</t>
+          <t>01052528559</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>276681</t>
+          <t>304210</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4771,24 +4771,24 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4204337741</t>
+          <t>dpfmxkdl</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01085530637</t>
+          <t>01023221625</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>272072</t>
+          <t>158745</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4798,51 +4798,51 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>jyyon101</t>
+          <t>kk_4840846776</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01050119990</t>
+          <t>01055961435</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>216194</t>
+          <t>304170</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4841140461</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01088944649</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>304185</t>
+          <t>304190</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4859,27 +4859,27 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>244625</t>
+          <t>266946</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -566,54 +566,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_3649011176</t>
+          <t>antonio34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01029317964</t>
+          <t>01090296238</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>249089</t>
+          <t>142917</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>antonio34</t>
+          <t>kk_3649011176</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01090296238</t>
+          <t>01029317964</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>142917</t>
+          <t>249089</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
     </row>
@@ -674,17 +674,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_4483270795</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01051728139</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>284407</t>
+          <t>246466</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -694,115 +694,115 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>kk_3016906903</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01050555122</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>246466</t>
+          <t>219318</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>josolha</t>
+          <t>wjdgus5106</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01052056266</t>
+          <t>01092085106</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>303793</t>
+          <t>302833</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_3016906903</t>
+          <t>kk_4483270795</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01050555122</t>
+          <t>01051728139</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>219318</t>
+          <t>284407</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wjdgus5106</t>
+          <t>josolha</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01092085106</t>
+          <t>01052056266</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>302833</t>
+          <t>303793</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -890,44 +890,44 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>139095</t>
+          <t>233095</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_4293591148</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01086489252</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>276079</t>
+          <t>254356</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -937,78 +937,78 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>233095</t>
+          <t>276079</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>254356</t>
+          <t>139095</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EDM_0314</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>j31goyung</t>
+          <t>kk_4837475331</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01049366682</t>
+          <t>01046487707</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>303989</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1018,24 +1018,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4837475331</t>
+          <t>kk_4334202320</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01046487707</t>
+          <t>01087183625</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>303989</t>
+          <t>278629</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1045,105 +1045,105 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>215822</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_4833864791</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01076696985</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>303759</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>kk_4279317974</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01086395686</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>215822</t>
+          <t>275222</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4334202320</t>
+          <t>j31goyung</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01087183625</t>
+          <t>01049366682</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>278629</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -1187,17 +1187,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>kk_4833864791</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01096791280</t>
+          <t>01076696985</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>303456</t>
+          <t>303759</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1207,78 +1207,78 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4279317974</t>
+          <t>kk_4829109495</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01086395686</t>
+          <t>01096791280</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>275222</t>
+          <t>303456</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>247134</t>
+          <t>114522</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gupabaljjang</t>
+          <t>phs76825</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01027797881</t>
+          <t>01091406949</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>132338</t>
+          <t>190331</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1288,51 +1288,51 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>303786</t>
+          <t>210511</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>285056</t>
+          <t>216543</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1342,51 +1342,51 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>kk_4826150317</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01050140463</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>216543</t>
+          <t>303288</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_4792317163</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01055819917</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>302105</t>
+          <t>303786</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1396,24 +1396,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>gupabaljjang</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01027797881</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>268665</t>
+          <t>132338</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1423,24 +1423,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>kk_4827961097</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01046347894</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>114522</t>
+          <t>303384</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1450,24 +1450,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sammoon26</t>
+          <t>kk_4792317163</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01055552500</t>
+          <t>01055819917</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>174647</t>
+          <t>302105</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1477,24 +1477,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>hhkim1018</t>
+          <t>kk_2863319761</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01054122583</t>
+          <t>01027753767</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>13471</t>
+          <t>213584</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1504,51 +1504,51 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>EDM_0329</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>hhkim1018</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01054122583</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>210511</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>EDM_0329</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_3881036278</t>
+          <t>sammoon26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01071425586</t>
+          <t>01055552500</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>266935</t>
+          <t>174647</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1558,24 +1558,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_2863319761</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01027753767</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>213584</t>
+          <t>247134</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1585,78 +1585,78 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4826150317</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01050140463</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>303288</t>
+          <t>277256</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>277256</t>
+          <t>285056</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>phs76825</t>
+          <t>kk_3881036278</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01091406949</t>
+          <t>01071425586</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>190331</t>
+          <t>266935</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1666,78 +1666,78 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_4827961097</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01046347894</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>303384</t>
+          <t>268665</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_3605280738</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01063779875</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>247209</t>
+          <t>157510</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4234864746</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01062301880</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>273540</t>
+          <t>154450</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1747,105 +1747,105 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kjchan69</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01063792010</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>256978</t>
+          <t>303592</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>chcjddl</t>
+          <t>kk_4840537683</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01086228198</t>
+          <t>01085206466</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>198759</t>
+          <t>304154</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>luxurykim11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01093252716</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>154450</t>
+          <t>80194</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>kk_4826804167</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01022256801</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>157510</t>
+          <t>303320</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1855,132 +1855,132 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4840537683</t>
+          <t>kk_3605280738</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01085206466</t>
+          <t>01063779875</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>304154</t>
+          <t>247209</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>kk_4318643192</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01062525049</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>80194</t>
+          <t>277689</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>chcjddl</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01086228198</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>303592</t>
+          <t>198759</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4826804167</t>
+          <t>kjchan69</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01022256801</t>
+          <t>01063792010</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>303320</t>
+          <t>256978</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_4318643192</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01062525049</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>277689</t>
+          <t>281393</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
@@ -2024,71 +2024,71 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>kk_2954792291</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01086049859</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>281393</t>
+          <t>216977</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_2954792291</t>
+          <t>kk_4234864746</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01086049859</t>
+          <t>01062301880</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>216977</t>
+          <t>273540</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>miraekoss</t>
+          <t>kk_4533637391</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01020213203</t>
+          <t>01090803497</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>286955</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2105,22 +2105,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_3205887201</t>
+          <t>kk_4679052952</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01063328335</t>
+          <t>01053553195</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>231050</t>
+          <t>294798</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2132,17 +2132,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_2805794827</t>
+          <t>hot0941</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01098906270</t>
+          <t>01033140941</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>211460</t>
+          <t>139060</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2152,51 +2152,51 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>hot0941</t>
+          <t>kk_4840338408</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01033140941</t>
+          <t>01054621177</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>139060</t>
+          <t>304143</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4840949436</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01064495993</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>304178</t>
+          <t>302814</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2206,191 +2206,191 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>hhgg6482</t>
+          <t>kk_2860000961</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01052195642</t>
+          <t>01086061074</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>290916</t>
+          <t>213449</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4815312274</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01050357610</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>302743</t>
+          <t>173433</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4841482998</t>
+          <t>kk_3205887201</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01050082734</t>
+          <t>01063328335</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>304194</t>
+          <t>231050</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4679052952</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01053553195</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>294798</t>
+          <t>304186</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>kk_4841179120</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01068577665</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>300186</t>
+          <t>304188</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4840738116</t>
+          <t>kk_4837856932</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01041260767</t>
+          <t>01042710870</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>304164</t>
+          <t>304021</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4841152170</t>
+          <t>kk_4841155697</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01050200309</t>
+          <t>01041762160</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>304186</t>
+          <t>304187</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2402,44 +2402,44 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>miraekoss</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01020213203</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>173433</t>
+          <t>183703</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>qssa2000</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01020284430</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>202308</t>
+          <t>304077</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2449,24 +2449,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>221644</t>
+          <t>300186</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2476,78 +2476,78 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>120212705670680427</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_4837599586</t>
+          <t>pppjs95</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01026751676</t>
+          <t>01040085813</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>304003</t>
+          <t>149718</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>mobis</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01090422686</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>123959</t>
+          <t>142777</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4535433913</t>
+          <t>kk_4815312274</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01071714088</t>
+          <t>01050357610</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>287044</t>
+          <t>302743</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2557,83 +2557,83 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4281300201</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01044488385</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>275307</t>
+          <t>221644</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>qssa2000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01020284430</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>142777</t>
+          <t>202308</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>kk_4840949436</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01064495993</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>304092</t>
+          <t>304178</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2672,98 +2672,98 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_2860000961</t>
+          <t>kk_2805794827</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01086061074</t>
+          <t>01098906270</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>213449</t>
+          <t>211460</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4837856932</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01042710870</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>304021</t>
+          <t>304092</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>mobis</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01090422686</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>304077</t>
+          <t>123959</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>pppjs95</t>
+          <t>kk_3688266936</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01040085813</t>
+          <t>01031949749</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>149718</t>
+          <t>250768</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2773,186 +2773,186 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4841564061</t>
+          <t>kk_4281300201</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01088968580</t>
+          <t>01044488385</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>304198</t>
+          <t>275307</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>kk_4841482998</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01050082734</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>302814</t>
+          <t>304194</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4838507875</t>
+          <t>kk_4837599586</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01041366853</t>
+          <t>01026751676</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>304055</t>
+          <t>304003</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4841179120</t>
+          <t>kk_3803785598</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01068577665</t>
+          <t>01084494003</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>304188</t>
+          <t>259616</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4841155697</t>
+          <t>kk_4838507875</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01041762160</t>
+          <t>01041366853</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>304187</t>
+          <t>304055</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_4535433913</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01071714088</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>250768</t>
+          <t>287044</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MESSAGE_0325_TRAIL</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4840338408</t>
+          <t>hhgg6482</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01054621177</t>
+          <t>01052195642</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>304143</t>
+          <t>290916</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2962,105 +2962,105 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4533637391</t>
+          <t>kk_4841564061</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01090803497</t>
+          <t>01088968580</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>286955</t>
+          <t>304198</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_3803785598</t>
+          <t>kk_4840738116</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01084494003</t>
+          <t>01041260767</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>259616</t>
+          <t>304164</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>jyyon101</t>
+          <t>kk_4841095079</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01050119990</t>
+          <t>01050906999</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>216194</t>
+          <t>304183</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4841836389</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01045794096</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>145423</t>
+          <t>304208</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3070,132 +3070,132 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4204337741</t>
+          <t>kk_4840846776</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01085530637</t>
+          <t>01055961435</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>272072</t>
+          <t>304170</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4840846776</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01055961435</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>304170</t>
+          <t>281590</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mwnew5</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01091343604</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>263720</t>
+          <t>244625</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4351409443</t>
+          <t>kk_4305076317</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01050585646</t>
+          <t>01082835869</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>279282</t>
+          <t>276795</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>akilris</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01076225525</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>266946</t>
+          <t>304205</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3205,51 +3205,51 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4841836389</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01045794096</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>304208</t>
+          <t>265508</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4841095079</t>
+          <t>acp1011</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01050906999</t>
+          <t>01045809723</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>304183</t>
+          <t>67149</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3259,24 +3259,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4840930255</t>
+          <t>kk_4841778210</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01092600071</t>
+          <t>01087814274</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>304177</t>
+          <t>304202</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3286,24 +3286,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>281590</t>
+          <t>153760</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3313,51 +3313,51 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4840763633</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01048116274</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>304165</t>
+          <t>304177</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>120212705670680427</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>217199</t>
+          <t>250075</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3367,186 +3367,186 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>dpfmxkdl</t>
+          <t>halla1001</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01023221625</t>
+          <t>01097612449</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>158745</t>
+          <t>12594</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>alswjd7015</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01039137015</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>191971</t>
+          <t>276681</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>bking1234</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01086427715</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>257110</t>
+          <t>304147</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>manong0821</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01036923281</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>66211</t>
+          <t>266946</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>nhs1024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01035177054</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>71200</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4303227124</t>
+          <t>kk_4200407916</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01037747441</t>
+          <t>01032980786</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>276681</t>
+          <t>271924</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_4841861142</t>
+          <t>kk_3487131753</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01052528559</t>
+          <t>01041080962</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>304210</t>
+          <t>244823</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3556,213 +3556,213 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4200407916</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01032980786</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>271924</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>poketgyu</t>
+          <t>kk_4840763633</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01085474650</t>
+          <t>01048116274</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>157236</t>
+          <t>304165</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>bking1234</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01086427715</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>219288</t>
+          <t>257110</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>244625</t>
+          <t>227380</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>304190</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>kk_4841140461</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01088944649</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>126315</t>
+          <t>304185</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>174486</t>
+          <t>126315</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>kk_3721509519</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01097118472</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>304205</t>
+          <t>252253</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3772,24 +3772,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4703272205</t>
+          <t>kk_4568748102</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01062682325</t>
+          <t>01054073523</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>296093</t>
+          <t>288185</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3799,51 +3799,51 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_4305076317</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01082835869</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>276795</t>
+          <t>145423</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>ellieee</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01098996425</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>250075</t>
+          <t>203688</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3853,24 +3853,24 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4840872605</t>
+          <t>hisgogo</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01063782216</t>
+          <t>01054110956</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>304173</t>
+          <t>174486</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3880,240 +3880,240 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_3152552457</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01031327516</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>223539</t>
+          <t>271278</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>kk_3152552457</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01031327516</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>134664</t>
+          <t>223539</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4840404521</t>
+          <t>kk_4204337741</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01032660272</t>
+          <t>01085530637</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>304145</t>
+          <t>272072</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4840817001</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01085963383</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>304168</t>
+          <t>240051</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>cloud84</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01094808884</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>240051</t>
+          <t>129205</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EDM_0411</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>eumban</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01089805431</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>271442</t>
+          <t>304193</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>acp1011</t>
+          <t>jyyon101</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01045809723</t>
+          <t>01050119990</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>67149</t>
+          <t>216194</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>cloud84</t>
+          <t>kk_4841501713</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01094808884</t>
+          <t>01042996002</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>129205</t>
+          <t>304195</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>EDM_0411</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4841778210</t>
+          <t>kk_4841572668</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01087814274</t>
+          <t>01024164342</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>304202</t>
+          <t>304199</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4130,71 +4130,71 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>227380</t>
+          <t>304158</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>kk_4840404521</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01032660272</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>304145</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>dpfmxkdl</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01023221625</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>244062</t>
+          <t>158745</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4204,24 +4204,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>271278</t>
+          <t>304168</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4231,24 +4231,24 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_3181933743</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01024077112</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>227397</t>
+          <t>217199</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4258,51 +4258,51 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_4841572668</t>
+          <t>kk_4840872605</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01024164342</t>
+          <t>01063782216</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>304199</t>
+          <t>304173</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>kk_3799202460</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01051162376</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>265508</t>
+          <t>258560</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4319,81 +4319,81 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_3487131753</t>
+          <t>eumban</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01041080962</t>
+          <t>01089805431</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>244823</t>
+          <t>271442</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ellieee</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01098996425</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>203688</t>
+          <t>219288</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>188067</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -4427,27 +4427,27 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>nhs1024</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01035177054</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>71200</t>
+          <t>134664</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -4481,152 +4481,152 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4841140461</t>
+          <t>kk_4840712470</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01088944649</t>
+          <t>01054536562</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>304185</t>
+          <t>304162</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_4841470777</t>
+          <t>kk_4840669442</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01067860344</t>
+          <t>01093940957</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>304193</t>
+          <t>304160</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>halla1001</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01097612449</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4840658838</t>
+          <t>kk_3181933743</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01039292600</t>
+          <t>01024077112</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>304158</t>
+          <t>227397</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4568748102</t>
+          <t>poketgyu</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01054073523</t>
+          <t>01085474650</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>288185</t>
+          <t>157236</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_3721509519</t>
+          <t>kk_4351409443</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01097118472</t>
+          <t>01050585646</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>252253</t>
+          <t>279282</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4636,132 +4636,132 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_4703272205</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01062682325</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>104766</t>
+          <t>296093</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>244062</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>153760</t>
+          <t>128947</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4841501713</t>
+          <t>manong0821</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01042996002</t>
+          <t>01036923281</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>304195</t>
+          <t>66211</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4840712470</t>
+          <t>mwnew5</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01054536562</t>
+          <t>01091343604</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>304162</t>
+          <t>263720</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4771,24 +4771,24 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>alswjd7015</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01039137015</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>191971</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4805,17 +4805,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_3799202460</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01051162376</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>258560</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4825,61 +4825,61 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>304147</t>
+          <t>207211</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4840669442</t>
+          <t>kk_4841861142</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01093940957</t>
+          <t>01052528559</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>304160</t>
+          <t>304210</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -1592,17 +1592,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_3496076178</t>
+          <t>kk_4837307904</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01045599838</t>
+          <t>01053415247</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>245165</t>
+          <t>303974</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1612,24 +1612,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4837307904</t>
+          <t>kk_3496076178</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01053415247</t>
+          <t>01045599838</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>303974</t>
+          <t>245165</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -2321,17 +2321,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_3637355234</t>
+          <t>bobo10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01025659242</t>
+          <t>01085251319</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>248511</t>
+          <t>222481</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2348,17 +2348,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>bobo10</t>
+          <t>kk_3637355234</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01085251319</t>
+          <t>01025659242</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>222481</t>
+          <t>248511</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2672,17 +2672,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kjyun3070</t>
+          <t>kk_4843392227</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01025037487</t>
+          <t>01031802445</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>304246</t>
+          <t>304306</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2699,17 +2699,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4843392227</t>
+          <t>kjyun3070</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01031802445</t>
+          <t>01025037487</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>304306</t>
+          <t>304246</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2780,17 +2780,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>jghglg</t>
+          <t>kk_4843461412</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01077584718</t>
+          <t>01026434270</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>205536</t>
+          <t>304316</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2800,24 +2800,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4843461412</t>
+          <t>jghglg</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01026434270</t>
+          <t>01077584718</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>304316</t>
+          <t>205536</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -3023,71 +3023,71 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4825081949</t>
+          <t>kk_4760874675</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01089579189</t>
+          <t>01092960558</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>303226</t>
+          <t>301263</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4760874675</t>
+          <t>kk_4825081949</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01092960558</t>
+          <t>01089579189</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>301263</t>
+          <t>303226</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4842184373</t>
+          <t>kk_4843149504</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01031320092</t>
+          <t>01056900629</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>304221</t>
+          <t>304280</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3097,24 +3097,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4843149504</t>
+          <t>kk_4842184373</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01056900629</t>
+          <t>01031320092</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>304280</t>
+          <t>304221</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -3293,54 +3293,54 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_3879655601</t>
+          <t>kk_4842694517</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01066650864</t>
+          <t>01033999168</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>266863</t>
+          <t>304242</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4842694517</t>
+          <t>kk_3879655601</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01033999168</t>
+          <t>01066650864</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>304242</t>
+          <t>266863</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
     </row>
@@ -3374,17 +3374,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>holstein</t>
+          <t>kk_4842703404</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01050502500</t>
+          <t>01027721118</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>304244</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3401,71 +3401,71 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4842703404</t>
+          <t>kk_3595551743</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01027721118</t>
+          <t>01025839326</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>304244</t>
+          <t>246836</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_3595551743</t>
+          <t>holstein</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01025839326</t>
+          <t>01050502500</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>246836</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>syosyol</t>
+          <t>khj426</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01064885418</t>
+          <t>01041416347</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>253938</t>
+          <t>20208</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3482,17 +3482,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>khj426</t>
+          <t>syosyol</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01041416347</t>
+          <t>01064885418</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>253938</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3617,81 +3617,81 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_3725118384</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01035977118</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>252440</t>
+          <t>268974</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>268974</t>
+          <t>304113</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_3725118384</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01035977118</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>252440</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -3725,17 +3725,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_4841965432</t>
+          <t>kk_4842910098</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01032510712</t>
+          <t>01091798172</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>304213</t>
+          <t>304259</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3752,17 +3752,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4842910098</t>
+          <t>blblhh</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01091798172</t>
+          <t>01033446769</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>304259</t>
+          <t>304297</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3806,17 +3806,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>blblhh</t>
+          <t>khkim6620</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01033446769</t>
+          <t>01076876567</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>304297</t>
+          <t>105445</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3833,17 +3833,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>khkim6620</t>
+          <t>kk_4841965432</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01076876567</t>
+          <t>01032510712</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>105445</t>
+          <t>304213</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3860,17 +3860,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4842710536</t>
+          <t>kk_4842135174</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01036878125</t>
+          <t>01072426633</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>304245</t>
+          <t>304218</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3887,17 +3887,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4842135174</t>
+          <t>kk_4842710536</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01072426633</t>
+          <t>01036878125</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>304218</t>
+          <t>304245</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3941,162 +3941,162 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>mhck94148967</t>
+          <t>kk_4522711623</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01037291432</t>
+          <t>01089870313</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>265260</t>
+          <t>286306</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4842422203</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01031681399</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>304232</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4434329905</t>
+          <t>kk_4842422203</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01071724035</t>
+          <t>01031681399</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>281922</t>
+          <t>304232</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4522711623</t>
+          <t>kk_4842950188</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01089870313</t>
+          <t>01054340750</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>286306</t>
+          <t>304262</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_4842950188</t>
+          <t>kk_4434329905</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01054340750</t>
+          <t>01071724035</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>304262</t>
+          <t>281922</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>mhck94148967</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01037291432</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>265260</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
     </row>
@@ -4130,17 +4130,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>dongheon20</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01052298928</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>155362</t>
+          <t>133308</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4157,71 +4157,71 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>ohsm0065</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01056170065</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>283897</t>
+          <t>74567</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ohsm0065</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01056170065</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>250755</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>dongheon20</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01052298928</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>242799</t>
+          <t>155362</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4238,17 +4238,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>250755</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4292,17 +4292,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>nohya2</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01020112033</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>247427</t>
+          <t>242799</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4346,17 +4346,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>nohya2</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01020112033</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>247427</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -1565,17 +1565,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_2929531599</t>
+          <t>kk_4837307904</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01052235006</t>
+          <t>01053415247</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>216036</t>
+          <t>303974</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1585,24 +1585,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4837307904</t>
+          <t>kk_3496076178</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01053415247</t>
+          <t>01045599838</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>303974</t>
+          <t>245165</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1612,61 +1612,61 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4842275089</t>
+          <t>kk_2929531599</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01033934089</t>
+          <t>01052235006</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>304226</t>
+          <t>216036</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_3496076178</t>
+          <t>kk_4842275089</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01045599838</t>
+          <t>01033934089</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>245165</t>
+          <t>304226</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -1808,17 +1808,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4843002291</t>
+          <t>kk_4842224344</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01024118610</t>
+          <t>01071616299</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>304268</t>
+          <t>304222</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1835,17 +1835,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4842224344</t>
+          <t>kk_4843002291</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01071616299</t>
+          <t>01024118610</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>304222</t>
+          <t>304268</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3077,17 +3077,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4843149504</t>
+          <t>kk_4842184373</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01056900629</t>
+          <t>01031320092</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>304280</t>
+          <t>304221</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3097,24 +3097,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4842184373</t>
+          <t>kk_4843149504</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01031320092</t>
+          <t>01056900629</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>304221</t>
+          <t>304280</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
@@ -3320,71 +3320,71 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4842694517</t>
+          <t>kk_3879655601</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01033999168</t>
+          <t>01066650864</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>304242</t>
+          <t>266863</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_3879655601</t>
+          <t>kk_4842694517</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01066650864</t>
+          <t>01033999168</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>266863</t>
+          <t>304242</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4842703404</t>
+          <t>holstein</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01027721118</t>
+          <t>01050502500</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>304244</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3401,54 +3401,54 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>holstein</t>
+          <t>kk_3595551743</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01050502500</t>
+          <t>01025839326</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>246836</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_3595551743</t>
+          <t>kk_4842703404</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01025839326</t>
+          <t>01027721118</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>246836</t>
+          <t>304244</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -3617,98 +3617,98 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>kk_3725118384</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01035977118</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>268974</t>
+          <t>252440</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3725118384</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01035977118</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>252440</t>
+          <t>304113</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>268974</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kona143</t>
+          <t>kk_4842999655</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01021001916</t>
+          <t>01080258508</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>304260</t>
+          <t>304267</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3779,17 +3779,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4842999655</t>
+          <t>kona143</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01080258508</t>
+          <t>01021001916</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>304267</t>
+          <t>304260</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3968,71 +3968,71 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4842422203</t>
+          <t>mhck94148967</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01031681399</t>
+          <t>01037291432</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>304232</t>
+          <t>265260</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>mhck94148967</t>
+          <t>kk_4434329905</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01037291432</t>
+          <t>01071724035</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>265260</t>
+          <t>281922</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4434329905</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01071724035</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>281922</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4049,27 +4049,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_4842422203</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01031681399</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>304232</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -4130,17 +4130,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>dongheon20</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01052298928</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>155362</t>
+          <t>133308</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4157,71 +4157,71 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>kk_4247630261</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01091437323</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>283897</t>
+          <t>274140</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>nohya2</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01020112033</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>247427</t>
+          <t>250755</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ohsm0065</t>
+          <t>dongheon20</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01056170065</t>
+          <t>01052298928</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>155362</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4238,44 +4238,44 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>nohya2</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01020112033</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>250755</t>
+          <t>247427</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>242799</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4292,81 +4292,81 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>242799</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4247630261</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01091437323</t>
+          <t>01095004289</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>274140</t>
+          <t>209015</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_2768989214</t>
+          <t>ohsm0065</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01095004289</t>
+          <t>01056170065</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>209015</t>
+          <t>74567</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -1565,44 +1565,44 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_4837307904</t>
+          <t>kk_4842275089</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01053415247</t>
+          <t>01033934089</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>303974</t>
+          <t>304226</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_3496076178</t>
+          <t>kk_4837307904</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01045599838</t>
+          <t>01053415247</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>245165</t>
+          <t>303974</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
@@ -1646,27 +1646,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4842275089</t>
+          <t>kk_3496076178</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01033934089</t>
+          <t>01045599838</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>304226</t>
+          <t>245165</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -2672,17 +2672,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kjyun3070</t>
+          <t>kk_4843392227</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01025037487</t>
+          <t>01031802445</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>304246</t>
+          <t>304306</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2699,17 +2699,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4843392227</t>
+          <t>kjyun3070</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01031802445</t>
+          <t>01025037487</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>304306</t>
+          <t>304246</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3023,71 +3023,71 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4825081949</t>
+          <t>kk_4760874675</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01089579189</t>
+          <t>01092960558</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>303226</t>
+          <t>301263</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4760874675</t>
+          <t>kk_4825081949</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01092960558</t>
+          <t>01089579189</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>301263</t>
+          <t>303226</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4842184373</t>
+          <t>kk_4843149504</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01031320092</t>
+          <t>01056900629</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>304221</t>
+          <t>304280</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3097,24 +3097,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4843149504</t>
+          <t>kk_4842184373</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01056900629</t>
+          <t>01031320092</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>304280</t>
+          <t>304221</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -3293,17 +3293,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4842881382</t>
+          <t>kk_4842694517</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01033848857</t>
+          <t>01033999168</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>304256</t>
+          <t>304242</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3320,71 +3320,71 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_3879655601</t>
+          <t>kk_4842881382</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01066650864</t>
+          <t>01033848857</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>266863</t>
+          <t>304256</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4842694517</t>
+          <t>kk_3879655601</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01033999168</t>
+          <t>01066650864</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>304242</t>
+          <t>266863</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>holstein</t>
+          <t>kk_4842703404</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01050502500</t>
+          <t>01027721118</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>304244</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3428,17 +3428,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4842703404</t>
+          <t>holstein</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01027721118</t>
+          <t>01050502500</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>304244</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3536,17 +3536,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_4479679945</t>
+          <t>jangshin711</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01091309005</t>
+          <t>01062415654</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>284232</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3563,17 +3563,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>jangshin711</t>
+          <t>kk_4479679945</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01062415654</t>
+          <t>01091309005</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>78392</t>
+          <t>284232</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3617,54 +3617,54 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_3725118384</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01035977118</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>252440</t>
+          <t>304113</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_3725118384</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01035977118</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>252440</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -3698,17 +3698,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4842999655</t>
+          <t>kona143</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01080258508</t>
+          <t>01021001916</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>304267</t>
+          <t>304260</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3752,17 +3752,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>blblhh</t>
+          <t>kk_4842910098</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01033446769</t>
+          <t>01091798172</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>304297</t>
+          <t>304259</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3779,17 +3779,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kona143</t>
+          <t>kk_4842999655</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01021001916</t>
+          <t>01080258508</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>304260</t>
+          <t>304267</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3806,17 +3806,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_4842910098</t>
+          <t>kk_4841965432</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01091798172</t>
+          <t>01032510712</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>304259</t>
+          <t>304213</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3833,17 +3833,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_4841965432</t>
+          <t>blblhh</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01032510712</t>
+          <t>01033446769</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>304213</t>
+          <t>304297</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3860,17 +3860,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4842135174</t>
+          <t>kk_4842710536</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01072426633</t>
+          <t>01036878125</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>304218</t>
+          <t>304245</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3887,17 +3887,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4842710536</t>
+          <t>kk_4842135174</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01036878125</t>
+          <t>01072426633</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>304245</t>
+          <t>304218</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3941,162 +3941,162 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4522711623</t>
+          <t>kk_4842950188</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01089870313</t>
+          <t>01054340750</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>286306</t>
+          <t>304262</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>mhck94148967</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01037291432</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>265260</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4434329905</t>
+          <t>mhck94148967</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01071724035</t>
+          <t>01037291432</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>281922</t>
+          <t>265260</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_4522711623</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01089870313</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>286306</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_4842422203</t>
+          <t>kk_4434329905</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01031681399</t>
+          <t>01071724035</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>304232</t>
+          <t>281922</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_4842950188</t>
+          <t>kk_4842422203</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01054340750</t>
+          <t>01031681399</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>304262</t>
+          <t>304232</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -4130,17 +4130,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_4247630261</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01091437323</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>274140</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4157,71 +4157,71 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4247630261</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01091437323</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>274140</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>250755</t>
+          <t>242799</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>dongheon20</t>
+          <t>nohya2</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01052298928</t>
+          <t>01020112033</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>155362</t>
+          <t>247427</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4238,17 +4238,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>nohya2</t>
+          <t>dongheon20</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01020112033</t>
+          <t>01052298928</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>247427</t>
+          <t>155362</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4265,17 +4265,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>242799</t>
+          <t>133308</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4292,17 +4292,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01095004289</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>283897</t>
+          <t>209015</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4319,17 +4319,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_2768989214</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01095004289</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>209015</t>
+          <t>250755</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -1565,71 +1565,71 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_4842275089</t>
+          <t>kk_2929531599</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01033934089</t>
+          <t>01052235006</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>304226</t>
+          <t>216036</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4837307904</t>
+          <t>kk_4842275089</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01053415247</t>
+          <t>01033934089</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>303974</t>
+          <t>304226</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_2929531599</t>
+          <t>kk_3496076178</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01052235006</t>
+          <t>01045599838</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>216036</t>
+          <t>245165</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1639,24 +1639,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_3496076178</t>
+          <t>kk_4837307904</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01045599838</t>
+          <t>01053415247</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>245165</t>
+          <t>303974</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
@@ -1808,17 +1808,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4842224344</t>
+          <t>kk_4843002291</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01071616299</t>
+          <t>01024118610</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>304222</t>
+          <t>304268</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1835,17 +1835,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4843002291</t>
+          <t>kk_4842224344</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01024118610</t>
+          <t>01071616299</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>304268</t>
+          <t>304222</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2672,17 +2672,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4843392227</t>
+          <t>kjyun3070</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01031802445</t>
+          <t>01025037487</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>304306</t>
+          <t>304246</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2699,17 +2699,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kjyun3070</t>
+          <t>kk_4843392227</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01025037487</t>
+          <t>01031802445</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>304246</t>
+          <t>304306</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2780,17 +2780,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>jghglg</t>
+          <t>kk_4843461412</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01077584718</t>
+          <t>01026434270</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>205536</t>
+          <t>304316</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2800,24 +2800,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4843461412</t>
+          <t>jghglg</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01026434270</t>
+          <t>01077584718</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>304316</t>
+          <t>205536</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -3374,17 +3374,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4842703404</t>
+          <t>holstein</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01027721118</t>
+          <t>01050502500</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>304244</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3428,17 +3428,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>holstein</t>
+          <t>kk_4842703404</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01050502500</t>
+          <t>01027721118</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>304244</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3455,17 +3455,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>khj426</t>
+          <t>syosyol</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01041416347</t>
+          <t>01064885418</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>253938</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3482,17 +3482,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>syosyol</t>
+          <t>khj426</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01064885418</t>
+          <t>01041416347</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>253938</t>
+          <t>20208</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3617,98 +3617,98 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_3930861019</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01089437783</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>268974</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3725118384</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01035977118</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>252440</t>
+          <t>304113</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>kk_3725118384</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01035977118</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>268974</t>
+          <t>252440</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kona143</t>
+          <t>kk_4841965432</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01021001916</t>
+          <t>01032510712</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>304260</t>
+          <t>304213</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3725,17 +3725,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>khkim6620</t>
+          <t>kona143</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01076876567</t>
+          <t>01021001916</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>105445</t>
+          <t>304260</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3752,17 +3752,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4842910098</t>
+          <t>kk_4842999655</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01091798172</t>
+          <t>01080258508</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>304259</t>
+          <t>304267</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3779,17 +3779,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4842999655</t>
+          <t>blblhh</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01080258508</t>
+          <t>01033446769</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>304267</t>
+          <t>304297</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3806,17 +3806,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_4841965432</t>
+          <t>khkim6620</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01032510712</t>
+          <t>01076876567</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>304213</t>
+          <t>105445</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3833,17 +3833,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>blblhh</t>
+          <t>kk_4842910098</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01033446769</t>
+          <t>01091798172</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>304297</t>
+          <t>304259</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3860,17 +3860,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4842710536</t>
+          <t>kk_4842135174</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01036878125</t>
+          <t>01072426633</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>304245</t>
+          <t>304218</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3887,17 +3887,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4842135174</t>
+          <t>kk_4842710536</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01072426633</t>
+          <t>01036878125</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>304218</t>
+          <t>304245</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3941,108 +3941,108 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4842950188</t>
+          <t>kk_4522711623</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01054340750</t>
+          <t>01089870313</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>304262</t>
+          <t>286306</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_4842422203</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01031681399</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>304232</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>mhck94148967</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01037291432</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>265260</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4522711623</t>
+          <t>kk_4842950188</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01089870313</t>
+          <t>01054340750</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>286306</t>
+          <t>304262</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
     </row>
@@ -4076,27 +4076,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_4842422203</t>
+          <t>mhck94148967</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01031681399</t>
+          <t>01037291432</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>304232</t>
+          <t>265260</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
     </row>
@@ -4130,17 +4130,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4247630261</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01091437323</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>274140</t>
+          <t>133308</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4157,71 +4157,71 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>nohya2</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01020112033</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>283897</t>
+          <t>247427</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>242799</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>nohya2</t>
+          <t>dongheon20</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01020112033</t>
+          <t>01052298928</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>247427</t>
+          <t>155362</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4238,17 +4238,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>dongheon20</t>
+          <t>ohsm0065</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01052298928</t>
+          <t>01056170065</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>155362</t>
+          <t>74567</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4265,17 +4265,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>242799</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4292,44 +4292,44 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_2768989214</t>
+          <t>kk_4247630261</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01095004289</t>
+          <t>01091437323</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>209015</t>
+          <t>274140</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01095004289</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>250755</t>
+          <t>209015</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4346,27 +4346,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ohsm0065</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01056170065</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>250755</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,17 +458,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>sty31933</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01059637276</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>304077</t>
+          <t>302965</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -478,78 +478,78 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kk_3817523531</t>
+          <t>kk_3941872291</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01090061449</t>
+          <t>01062546290</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>262416</t>
+          <t>269400</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kk_4270962450</t>
+          <t>aronsk</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01065174170</t>
+          <t>01028043855</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>274867</t>
+          <t>303150</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_3297935659</t>
+          <t>columbia25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01090281747</t>
+          <t>01072741705</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>237556</t>
+          <t>292353</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -559,191 +559,191 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>pmax</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_4819571980</t>
+          <t>kk_4512211992</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01032678993</t>
+          <t>01040855407</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>302943</t>
+          <t>285712</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_FridnsTalk_CartSale</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_4826165723</t>
+          <t>eccomi21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01063388703</t>
+          <t>01084717525</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>303291</t>
+          <t>143557</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_2766947879</t>
+          <t>kk_4279317974</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01040508131</t>
+          <t>01086395686</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>208880</t>
+          <t>275222</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_3672780564</t>
+          <t>kk_3186268807</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01089459294</t>
+          <t>01055175130</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>250138</t>
+          <t>230244</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>vijkk48</t>
+          <t>kk_3337408762</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01049214164</t>
+          <t>01095768922</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>251486</t>
+          <t>238953</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>kk_2929531599</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01052235006</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>173433</t>
+          <t>216036</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_4833693850</t>
+          <t>kk_4806290091</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01038159698</t>
+          <t>01042848444</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>303742</t>
+          <t>302466</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,152 +755,152 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>jung9916</t>
+          <t>kk_3186253524</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01091576210</t>
+          <t>01020132166</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>171554</t>
+          <t>230229</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>EDM_0406</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kk_4819859269</t>
+          <t>seopme</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01033625849</t>
+          <t>01074122238</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>302958</t>
+          <t>304125</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kk_3382857459</t>
+          <t>kk_3672780564</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01057126210</t>
+          <t>01089459294</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>240590</t>
+          <t>250138</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>jalove3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01090657762</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>302814</t>
+          <t>168971</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ryu501</t>
+          <t>ryukw0604</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01067262528</t>
+          <t>01037512203</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>145916</t>
+          <t>131147</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_4224863579</t>
+          <t>kk_3803973742</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01045995157</t>
+          <t>01062581642</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>273002</t>
+          <t>259682</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -910,105 +910,105 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0209_EGGIPOUTCH</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_4842375919</t>
+          <t>sas159</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01054212093</t>
+          <t>01041922755</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>304229</t>
+          <t>188959</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_4842492680</t>
+          <t>kk_3182623010</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01024861808</t>
+          <t>01094128645</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>304237</t>
+          <t>227908</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kimmk12</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01092235669</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>76270</t>
+          <t>276079</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_4841960111</t>
+          <t>pak652</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01033587128</t>
+          <t>01022458173</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>304212</t>
+          <t>280384</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1025,17 +1025,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4842257901</t>
+          <t>kk_4846905948</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01099969825</t>
+          <t>01099121650</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>304225</t>
+          <t>304473</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1052,17 +1052,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_4201661917</t>
+          <t>kk_3672642114</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01052228247</t>
+          <t>01093597232</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>271984</t>
+          <t>250133</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1072,213 +1072,213 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_4817183511</t>
+          <t>kk_4846613084</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01038475953</t>
+          <t>01079413983</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>302817</t>
+          <t>304453</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>greom73</t>
+          <t>sangdori76</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01086372526</t>
+          <t>01088651421</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>135272</t>
+          <t>248370</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>s09635</t>
+          <t>gywjd8404</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01090472784</t>
+          <t>01048642364</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>256102</t>
+          <t>131135</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_3693928814</t>
+          <t>seonghyeon20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01026763178</t>
+          <t>01088283643</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>251031</t>
+          <t>204875</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4842951523</t>
+          <t>kk_4845099354</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01051558480</t>
+          <t>01030334936</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>304263</t>
+          <t>304390</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_3139519743</t>
+          <t>kk_3795703816</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01063851075</t>
+          <t>01040850174</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>222754</t>
+          <t>257699</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4826503124</t>
+          <t>dpfmxkdl</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01042004564</t>
+          <t>01023221625</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>303307</t>
+          <t>158745</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_3529523763</t>
+          <t>kk_3955959787</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01085373147</t>
+          <t>01087702143</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>246265</t>
+          <t>270178</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1288,24 +1288,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>whdxo30</t>
+          <t>kk_4845411058</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01098421448</t>
+          <t>01032450700</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>96502</t>
+          <t>304413</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1322,44 +1322,44 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>stopzero</t>
+          <t>doremige</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01090058585</t>
+          <t>01083505612</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>279138</t>
+          <t>304450</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sunlight97</t>
+          <t>kk_4846153585</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01098067107</t>
+          <t>01071602706</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>168443</t>
+          <t>304439</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1376,71 +1376,71 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>kk_3745509137</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01094130627</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>154450</t>
+          <t>253905</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_4842694508</t>
+          <t>w14721</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01032274987</t>
+          <t>01091085401</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>304241</t>
+          <t>262190</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_4841152170</t>
+          <t>kk_3798348150</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01050200309</t>
+          <t>01020250324</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>304186</t>
+          <t>258390</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1450,294 +1450,294 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>nmstway</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01093823995</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>304092</t>
+          <t>304455</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_2997012029</t>
+          <t>kk_4846007316</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01028601556</t>
+          <t>01028293928</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>218408</t>
+          <t>304431</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_3328286087</t>
+          <t>kk_4845228879</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01098090201</t>
+          <t>01084451479</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>238558</t>
+          <t>304399</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_WINTERSEASONOFF3RD</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_4837286516</t>
+          <t>kk_4846796027</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01092741887</t>
+          <t>01052779751</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>303973</t>
+          <t>304467</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_2929531599</t>
+          <t>kk_4846778806</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01052235006</t>
+          <t>01040473668</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>216036</t>
+          <t>304466</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4842275089</t>
+          <t>hy1453</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01033934089</t>
+          <t>01064627675</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>304226</t>
+          <t>226545</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_3496076178</t>
+          <t>kk_4846234119</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01045599838</t>
+          <t>01049167784</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>245165</t>
+          <t>304442</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4837307904</t>
+          <t>kk_4845121902</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01053415247</t>
+          <t>01063826114</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>303974</t>
+          <t>304394</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>hisooyong</t>
+          <t>kk_3338448571</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01026866117</t>
+          <t>01050068417</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>172752</t>
+          <t>239011</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>newbbaccom</t>
+          <t>charismasm74</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01025776082</t>
+          <t>01093438775</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>304300</t>
+          <t>303650</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4842756928</t>
+          <t>kk_3821281618</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01067660130</t>
+          <t>01088952813</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>304248</t>
+          <t>262770</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1754,125 +1754,125 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4835462666</t>
+          <t>kk_4846078636</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01025263630</t>
+          <t>01099000411</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>303860</t>
+          <t>304434</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_4843482023</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01030727029</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>304320</t>
+          <t>244625</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4843002291</t>
+          <t>cseeun</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01024118610</t>
+          <t>01052533925</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>304268</t>
+          <t>171213</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4842224344</t>
+          <t>kk_3846547859</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01071616299</t>
+          <t>01055056387</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>304222</t>
+          <t>264802</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4842831681</t>
+          <t>sughg</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01033574114</t>
+          <t>01066321444</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>304254</t>
+          <t>189932</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1889,98 +1889,98 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_4843239939</t>
+          <t>kk_2804147495</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01025351587</t>
+          <t>01046206130</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>304291</t>
+          <t>211367</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bubhak</t>
+          <t>ektlrksek</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01030100699</t>
+          <t>01092231103</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>yeoks73</t>
+          <t>kk_4520177358</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01062816207</t>
+          <t>01039211233</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>79643</t>
+          <t>286186</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>hero8548</t>
+          <t>tjsgksrlf123</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01092748548</t>
+          <t>01033775889</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>222771</t>
+          <t>51662</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1990,51 +1990,51 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>EDM_0126_bestreview</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>kk_2706830356</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01020264590</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>80194</t>
+          <t>303409</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>EDM_0402</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4712682242</t>
+          <t>kkhgreen</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01089596094</t>
+          <t>01092780969</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>296794</t>
+          <t>256221</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2044,213 +2044,213 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4746257748</t>
+          <t>boxyogo</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01047829639</t>
+          <t>01047175275</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>300549</t>
+          <t>294173</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>eastehdwk</t>
+          <t>kk_4845508185</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01084434416</t>
+          <t>01082736745</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>178991</t>
+          <t>304415</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4842927888</t>
+          <t>kk_4843461412</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01038403700</t>
+          <t>01026434270</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>304261</t>
+          <t>304316</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_3630958119</t>
+          <t>jsy90</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01077413527</t>
+          <t>01055153689</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>248123</t>
+          <t>304378</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>vtjddn</t>
+          <t>kk_4846360933</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01041346668</t>
+          <t>01037341293</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>295481</t>
+          <t>304445</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4842405217</t>
+          <t>frankseo</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01040880701</t>
+          <t>01073890799</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>304231</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kojn3718</t>
+          <t>kk_4846296264</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01090473718</t>
+          <t>01057718259</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>107248</t>
+          <t>304444</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4840930255</t>
+          <t>anirim</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01092600071</t>
+          <t>01026146239</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>304177</t>
+          <t>303897</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2260,132 +2260,132 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4653613871</t>
+          <t>jjunghaha</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01087303425</t>
+          <t>01053895722</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>293200</t>
+          <t>17630</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4841470777</t>
+          <t>kk_4845257177</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01067860344</t>
+          <t>01034081789</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>304193</t>
+          <t>304403</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>bobo10</t>
+          <t>kk_4846754659</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01085251319</t>
+          <t>01091349747</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>222481</t>
+          <t>304463</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_3637355234</t>
+          <t>kk_4502849451</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01025659242</t>
+          <t>01057550515</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>248511</t>
+          <t>285306</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4843491166</t>
+          <t>kk_2860000961</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01044880321</t>
+          <t>01086061074</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>304321</t>
+          <t>213449</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2395,321 +2395,321 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>teenglory</t>
+          <t>kk_4804517522</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01028236541</t>
+          <t>01027141942</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>113555</t>
+          <t>302419</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4483270795</t>
+          <t>kk_4845481797</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01051728139</t>
+          <t>01056670020</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>284407</t>
+          <t>304414</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_3736097865</t>
+          <t>santastic</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01089447248</t>
+          <t>01064117065</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>253356</t>
+          <t>304410</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_4660543031</t>
+          <t>kk_4845889920</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01065173006</t>
+          <t>01041965899</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>293617</t>
+          <t>304430</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4820300458</t>
+          <t>kk_4842910098</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01059188956</t>
+          <t>01091798172</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>302984</t>
+          <t>304259</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_3809928726</t>
+          <t>kk_4750424051</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01079193871</t>
+          <t>01064958365</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>261086</t>
+          <t>300863</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>260210_Konos</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_3457131246</t>
+          <t>kk_4837400672</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01050362153</t>
+          <t>01093667007</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>243280</t>
+          <t>303984</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ohey2003</t>
+          <t>kk_4845023359</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01034151656</t>
+          <t>01020760617</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>116157</t>
+          <t>304387</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>ljsjsy</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01089846463</t>
+          <t>01047759562</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>303618</t>
+          <t>292623</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4750697279</t>
+          <t>kk_4504731355</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01086127388</t>
+          <t>01030391478</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>300871</t>
+          <t>285364</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>EDM_0209_LIGHTBAG</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kjyun3070</t>
+          <t>yong9021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01025037487</t>
+          <t>01091453429</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>304246</t>
+          <t>178559</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4843392227</t>
+          <t>kk_2881959901</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01031802445</t>
+          <t>01065516593</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>304306</t>
+          <t>214614</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2726,44 +2726,44 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_3433423317</t>
+          <t>aijene</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01075326556</t>
+          <t>01024942984</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>242341</t>
+          <t>43582</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4819009863</t>
+          <t>kk_4837577772</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01033396228</t>
+          <t>01084837878</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>302911</t>
+          <t>303999</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2773,105 +2773,105 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4843461412</t>
+          <t>kk_4845276986</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01026434270</t>
+          <t>01099470418</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>304316</t>
+          <t>304404</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>jghglg</t>
+          <t>smapumki</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01077584718</t>
+          <t>01091110988</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>205536</t>
+          <t>51742</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>khj2155</t>
+          <t>kk_4845728411</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01067617228</t>
+          <t>01041347851</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>280072</t>
+          <t>304427</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4842460884</t>
+          <t>kk_4845555835</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01066121103</t>
+          <t>01032274369</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>304235</t>
+          <t>304418</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2888,44 +2888,44 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_3438127132</t>
+          <t>kk_4006977661</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01042465894</t>
+          <t>01027938030</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>242550</t>
+          <t>271755</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>b1ue7</t>
+          <t>kk_4715265153</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01088937612</t>
+          <t>01077714623</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>218185</t>
+          <t>297043</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2935,186 +2935,186 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kiwi3023</t>
+          <t>dohyunahn</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01075047415</t>
+          <t>01038817179</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>106702</t>
+          <t>304469</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_3392285660</t>
+          <t>kk_2794135395</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01097678768</t>
+          <t>01094224624</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>240993</t>
+          <t>210420</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>6941110100332</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4826150317</t>
+          <t>tandjh</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01050140463</t>
+          <t>01030676796</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>303288</t>
+          <t>59328</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4760874675</t>
+          <t>abckk3390</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01092960558</t>
+          <t>01062023390</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>301263</t>
+          <t>71493</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4825081949</t>
+          <t>kk_2800477789</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01089579189</t>
+          <t>01035177105</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>303226</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4843149504</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01056900629</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>304280</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4842184373</t>
+          <t>kang481127</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01031320092</t>
+          <t>01053764012</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>304221</t>
+          <t>304276</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3131,98 +3131,98 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4840174486</t>
+          <t>aumteail</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01064087457</t>
+          <t>01065702230</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>304131</t>
+          <t>261499</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_3688266936</t>
+          <t>kk_3623213220</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01031949749</t>
+          <t>01065959020</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>250768</t>
+          <t>247746</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_3821943032</t>
+          <t>abril80</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01040419162</t>
+          <t>01032942835</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>262827</t>
+          <t>192610</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_4846749411</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01039056708</t>
+          <t>01031226749</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>303497</t>
+          <t>304462</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3239,44 +3239,44 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>swd71</t>
+          <t>kk_4846692829</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01071953545</t>
+          <t>01023649887</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>122866</t>
+          <t>304457</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4842227811</t>
+          <t>kk_4846761310</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01053115045</t>
+          <t>01091189951</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>304223</t>
+          <t>304464</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3293,44 +3293,44 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4842694517</t>
+          <t>kk_4651201605</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01033999168</t>
+          <t>01045489411</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>304242</t>
+          <t>293053</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4842881382</t>
+          <t>willper</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01033848857</t>
+          <t>01085343440</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>304256</t>
+          <t>304408</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3347,44 +3347,44 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_3879655601</t>
+          <t>kk_3788170304</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01066650864</t>
+          <t>01071502244</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>266863</t>
+          <t>256604</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>holstein</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01050502500</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3401,44 +3401,44 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_3595551743</t>
+          <t>wodl8077</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01025839326</t>
+          <t>01097558077</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>246836</t>
+          <t>144037</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4842703404</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01027721118</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>304244</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3455,17 +3455,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>syosyol</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01064885418</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>253938</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3482,98 +3482,98 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>khj426</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01041416347</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4443220093</t>
+          <t>chpuss74</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01050391223</t>
+          <t>01035361091</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>282189</t>
+          <t>154462</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>jangshin711</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01062415654</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>78392</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4479679945</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01091309005</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>284232</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3590,17 +3590,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_3522681591</t>
+          <t>kk_4469973568</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01042232282</t>
+          <t>01087158602</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>245991</t>
+          <t>283741</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3610,24 +3610,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_3930861019</t>
+          <t>kk_3343508579</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01089437783</t>
+          <t>01062563328</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>268974</t>
+          <t>239234</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3637,78 +3637,78 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_3210379887</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01024748405</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>231651</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_3725118384</t>
+          <t>rkdguddyd21</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01035977118</t>
+          <t>01089751458</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>252440</t>
+          <t>304465</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4841965432</t>
+          <t>twinswoo</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01032510712</t>
+          <t>01056545433</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>304213</t>
+          <t>208155</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3725,17 +3725,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kona143</t>
+          <t>swonh77</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01021001916</t>
+          <t>01083828396</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>304260</t>
+          <t>295604</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3746,681 +3746,6 @@
       <c r="E123" t="inlineStr">
         <is>
           <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>kk_4842999655</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>01080258508</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>304267</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>blblhh</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>01033446769</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>304297</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>khkim6620</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>01076876567</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>105445</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>kk_4842910098</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>01091798172</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>304259</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>kk_4842135174</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>01072426633</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>304218</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>kk_4842710536</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>01036878125</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>304245</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>kk_4843247304</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>01091358534</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>304292</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>kk_4522711623</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>01089870313</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>286306</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>kk_4842422203</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>01031681399</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>304232</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>kk_4843439707</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>01022248653</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>304310</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>kk_4842950188</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>01054340750</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>304262</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Organic Traffic</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Organic Traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>kk_4434329905</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>01071724035</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>281922</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>mhck94148967</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>01037291432</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>265260</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Awareness</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>melodyhj</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>01040480010</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>273180</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Official SNS</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>(referral)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>xuswldls</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>01027349414</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>133308</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>nohya2</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>01020112033</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>247427</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>kk_4472536591</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>01037057526</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>283897</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>dongheon20</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>01052298928</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>155362</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>ohsm0065</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>01056170065</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>74567</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>kk_3444865211</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>01021964871</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>242799</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>kk_4247630261</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>01091437323</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>274140</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>kk_2768989214</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>01095004289</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>209015</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>kk_3688034999</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>01025408262</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>250755</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>kk_4481598577</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>01082947677</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>284316</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>jaeyouri</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>01099842856</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>90901</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>etc</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -1430,54 +1430,54 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_3798348150</t>
+          <t>nmstway</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01020250324</t>
+          <t>01093823995</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>258390</t>
+          <t>304455</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nmstway</t>
+          <t>kk_3798348150</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01093823995</t>
+          <t>01020250324</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>304455</t>
+          <t>258390</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -1538,17 +1538,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_4846796027</t>
+          <t>kk_4846778806</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01052779751</t>
+          <t>01040473668</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>304467</t>
+          <t>304466</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1565,17 +1565,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_4846778806</t>
+          <t>kk_4846796027</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01040473668</t>
+          <t>01052779751</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>304466</t>
+          <t>304467</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2510,27 +2510,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4842910098</t>
+          <t>kk_4837400672</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01091798172</t>
+          <t>01093667007</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>304259</t>
+          <t>303984</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -2564,27 +2564,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4837400672</t>
+          <t>kk_4842910098</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01093667007</t>
+          <t>01091798172</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>303984</t>
+          <t>304259</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
@@ -2726,54 +2726,54 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>aijene</t>
+          <t>kk_4837577772</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01024942984</t>
+          <t>01084837878</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>43582</t>
+          <t>303999</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4837577772</t>
+          <t>aijene</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01084837878</t>
+          <t>01024942984</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>303999</t>
+          <t>43582</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -2915,54 +2915,54 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4715265153</t>
+          <t>dohyunahn</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01077714623</t>
+          <t>01038817179</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>297043</t>
+          <t>304469</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>dohyunahn</t>
+          <t>kk_4715265153</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01038817179</t>
+          <t>01077714623</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>304469</t>
+          <t>297043</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -3104,81 +3104,81 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kang481127</t>
+          <t>kk_3623213220</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01053764012</t>
+          <t>01065959020</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>304276</t>
+          <t>247746</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>aumteail</t>
+          <t>kang481127</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01065702230</t>
+          <t>01053764012</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>261499</t>
+          <t>304276</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_3623213220</t>
+          <t>aumteail</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01065959020</t>
+          <t>01065702230</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>247746</t>
+          <t>261499</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -3266,71 +3266,71 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4846761310</t>
+          <t>kk_4651201605</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01091189951</t>
+          <t>01045489411</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>304464</t>
+          <t>293053</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4651201605</t>
+          <t>willper</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01045489411</t>
+          <t>01085343440</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>293053</t>
+          <t>304408</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>willper</t>
+          <t>kk_4846761310</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01085343440</t>
+          <t>01091189951</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>304464</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3374,54 +3374,54 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>wodl8077</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01097558077</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>144037</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -3455,17 +3455,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>chpuss74</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01035361091</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>154462</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3482,44 +3482,44 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>wodl8077</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01097558077</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>144037</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>chpuss74</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01035361091</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>154462</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3536,27 +3536,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -3590,27 +3590,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4469973568</t>
+          <t>kk_3210379887</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01087158602</t>
+          <t>01024748405</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>283741</t>
+          <t>231651</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -3644,44 +3644,44 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3210379887</t>
+          <t>kk_4469973568</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01024748405</t>
+          <t>01087158602</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>231651</t>
+          <t>283741</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>rkdguddyd21</t>
+          <t>swonh77</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01089751458</t>
+          <t>01083828396</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>304465</t>
+          <t>295604</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3698,17 +3698,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>twinswoo</t>
+          <t>rkdguddyd21</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01056545433</t>
+          <t>01089751458</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>208155</t>
+          <t>304465</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3725,17 +3725,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>swonh77</t>
+          <t>twinswoo</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01083828396</t>
+          <t>01056545433</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>295604</t>
+          <t>208155</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -2294,17 +2294,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4845257177</t>
+          <t>kk_4846754659</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01034081789</t>
+          <t>01091349747</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>304403</t>
+          <t>304463</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2321,17 +2321,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4846754659</t>
+          <t>kk_4845257177</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01091349747</t>
+          <t>01034081789</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>304463</t>
+          <t>304403</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2510,71 +2510,71 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4837400672</t>
+          <t>kk_4750424051</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01093667007</t>
+          <t>01064958365</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>303984</t>
+          <t>300863</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>260210_Konos</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4750424051</t>
+          <t>kk_4842910098</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01064958365</t>
+          <t>01091798172</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>300863</t>
+          <t>304259</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>260210_Konos</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4842910098</t>
+          <t>kk_4845023359</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01091798172</t>
+          <t>01020760617</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>304259</t>
+          <t>304387</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2584,34 +2584,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4845023359</t>
+          <t>kk_4837400672</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01020760617</t>
+          <t>01093667007</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>304387</t>
+          <t>303984</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -2672,108 +2672,108 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>yong9021</t>
+          <t>kk_2881959901</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01091453429</t>
+          <t>01065516593</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>178559</t>
+          <t>214614</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_2881959901</t>
+          <t>yong9021</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01065516593</t>
+          <t>01091453429</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>214614</t>
+          <t>178559</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_4837577772</t>
+          <t>aijene</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01084837878</t>
+          <t>01024942984</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>303999</t>
+          <t>43582</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>aijene</t>
+          <t>kk_4837577772</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01024942984</t>
+          <t>01084837878</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>43582</t>
+          <t>303999</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
@@ -2888,71 +2888,71 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4006977661</t>
+          <t>dohyunahn</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01027938030</t>
+          <t>01038817179</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>271755</t>
+          <t>304469</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>dohyunahn</t>
+          <t>kk_4715265153</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01038817179</t>
+          <t>01077714623</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>304469</t>
+          <t>297043</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4715265153</t>
+          <t>kk_4006977661</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01077714623</t>
+          <t>01027938030</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>297043</t>
+          <t>271755</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3104,125 +3104,125 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_3623213220</t>
+          <t>kang481127</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01065959020</t>
+          <t>01053764012</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>247746</t>
+          <t>304276</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kang481127</t>
+          <t>aumteail</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01053764012</t>
+          <t>01065702230</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>304276</t>
+          <t>261499</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>aumteail</t>
+          <t>abril80</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01065702230</t>
+          <t>01032942835</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>261499</t>
+          <t>192610</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>abril80</t>
+          <t>kk_3623213220</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01032942835</t>
+          <t>01065959020</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>192610</t>
+          <t>247746</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4846749411</t>
+          <t>kk_4846692829</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01031226749</t>
+          <t>01023649887</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>304462</t>
+          <t>304457</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3239,17 +3239,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4846692829</t>
+          <t>kk_4846749411</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01023649887</t>
+          <t>01031226749</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>304457</t>
+          <t>304462</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3266,71 +3266,71 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4651201605</t>
+          <t>kk_3788170304</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01045489411</t>
+          <t>01071502244</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>293053</t>
+          <t>256604</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>willper</t>
+          <t>kk_4651201605</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01085343440</t>
+          <t>01045489411</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>293053</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4846761310</t>
+          <t>willper</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01091189951</t>
+          <t>01085343440</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>304464</t>
+          <t>304408</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3347,17 +3347,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_3788170304</t>
+          <t>kk_4846761310</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01071502244</t>
+          <t>01091189951</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256604</t>
+          <t>304464</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3367,24 +3367,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3401,71 +3401,71 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_3183517395</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01082019936</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>228501</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>chpuss74</t>
+          <t>wodl8077</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01035361091</t>
+          <t>01097558077</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>154462</t>
+          <t>144037</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3475,24 +3475,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>wodl8077</t>
+          <t>chpuss74</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01097558077</t>
+          <t>01035361091</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>144037</t>
+          <t>154462</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3502,24 +3502,24 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3536,17 +3536,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3563,17 +3563,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3590,81 +3590,81 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_3210379887</t>
+          <t>kk_3343508579</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01024748405</t>
+          <t>01062563328</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>231651</t>
+          <t>239234</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_3343508579</t>
+          <t>kk_4469973568</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01062563328</t>
+          <t>01087158602</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>239234</t>
+          <t>283741</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4469973568</t>
+          <t>kk_3210379887</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01087158602</t>
+          <t>01024748405</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>283741</t>
+          <t>231651</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -3698,17 +3698,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>rkdguddyd21</t>
+          <t>twinswoo</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01089751458</t>
+          <t>01056545433</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>304465</t>
+          <t>208155</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3725,17 +3725,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>twinswoo</t>
+          <t>rkdguddyd21</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01056545433</t>
+          <t>01089751458</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>208155</t>
+          <t>304465</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -674,54 +674,54 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_3337408762</t>
+          <t>kk_2929531599</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01095768922</t>
+          <t>01052235006</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>238953</t>
+          <t>216036</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_2929531599</t>
+          <t>kk_3337408762</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01052235006</t>
+          <t>01095768922</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>216036</t>
+          <t>238953</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -755,54 +755,54 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_3186253524</t>
+          <t>seopme</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01020132166</t>
+          <t>01074122238</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>230229</t>
+          <t>304125</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EDM_0406</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>seopme</t>
+          <t>kk_3186253524</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01074122238</t>
+          <t>01020132166</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>304125</t>
+          <t>230229</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0406</t>
         </is>
       </c>
     </row>
@@ -1052,54 +1052,54 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_3672642114</t>
+          <t>kk_4846613084</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01093597232</t>
+          <t>01079413983</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>250133</t>
+          <t>304453</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_4846613084</t>
+          <t>kk_3672642114</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01079413983</t>
+          <t>01093597232</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>304453</t>
+          <t>250133</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
@@ -1214,17 +1214,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_3795703816</t>
+          <t>kk_3955959787</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01040850174</t>
+          <t>01087702143</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>257699</t>
+          <t>270178</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1234,24 +1234,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dpfmxkdl</t>
+          <t>kk_3795703816</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01023221625</t>
+          <t>01040850174</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>158745</t>
+          <t>257699</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1261,51 +1261,51 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_3955959787</t>
+          <t>kk_3745509137</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01087702143</t>
+          <t>01094130627</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>270178</t>
+          <t>253905</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_4845411058</t>
+          <t>doremige</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01032450700</t>
+          <t>01083505612</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>304413</t>
+          <t>304450</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1322,17 +1322,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>doremige</t>
+          <t>kk_4845411058</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01083505612</t>
+          <t>01032450700</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>304450</t>
+          <t>304413</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1376,135 +1376,135 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_3745509137</t>
+          <t>kk_4846007316</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01094130627</t>
+          <t>01028293928</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>253905</t>
+          <t>304431</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>w14721</t>
+          <t>hy1453</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01091085401</t>
+          <t>01064627675</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>262190</t>
+          <t>226545</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>nmstway</t>
+          <t>dpfmxkdl</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01093823995</t>
+          <t>01023221625</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>304455</t>
+          <t>158745</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_3798348150</t>
+          <t>kk_4846796027</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01020250324</t>
+          <t>01052779751</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>258390</t>
+          <t>304467</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4846007316</t>
+          <t>w14721</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01028293928</t>
+          <t>01091085401</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>304431</t>
+          <t>262190</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -1538,44 +1538,44 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_4846778806</t>
+          <t>kk_3798348150</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01040473668</t>
+          <t>01020250324</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>304466</t>
+          <t>258390</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_4846796027</t>
+          <t>nmstway</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01052779751</t>
+          <t>01093823995</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>304467</t>
+          <t>304455</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1592,44 +1592,44 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>hy1453</t>
+          <t>kk_4846234119</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01064627675</t>
+          <t>01049167784</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>226545</t>
+          <t>304442</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4846234119</t>
+          <t>kk_4846778806</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01049167784</t>
+          <t>01040473668</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>304442</t>
+          <t>304466</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1646,44 +1646,44 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4845121902</t>
+          <t>kk_3338448571</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01063826114</t>
+          <t>01050068417</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>304394</t>
+          <t>239011</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_3338448571</t>
+          <t>charismasm74</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01050068417</t>
+          <t>01093438775</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>239011</t>
+          <t>303650</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1693,186 +1693,186 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>charismasm74</t>
+          <t>kk_4845121902</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01093438775</t>
+          <t>01063826114</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>303650</t>
+          <t>304394</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_3821281618</t>
+          <t>kk_3846547859</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01088952813</t>
+          <t>01055056387</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>262770</t>
+          <t>264802</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4846078636</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01099000411</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>304434</t>
+          <t>244625</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>kk_3821281618</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01088952813</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>244625</t>
+          <t>262770</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cseeun</t>
+          <t>kk_2804147495</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01052533925</t>
+          <t>01046206130</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>171213</t>
+          <t>211367</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_3846547859</t>
+          <t>sughg</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01055056387</t>
+          <t>01066321444</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>264802</t>
+          <t>189932</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sughg</t>
+          <t>kk_4846078636</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01066321444</t>
+          <t>01099000411</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>189932</t>
+          <t>304434</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1889,17 +1889,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_2804147495</t>
+          <t>ektlrksek</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01046206130</t>
+          <t>01092231103</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>211367</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1916,44 +1916,44 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ektlrksek</t>
+          <t>cseeun</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01092231103</t>
+          <t>01052533925</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>171213</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4520177358</t>
+          <t>boxyogo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01039211233</t>
+          <t>01047175275</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>286186</t>
+          <t>294173</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1963,51 +1963,51 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>tjsgksrlf123</t>
+          <t>kk_4845508185</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01033775889</t>
+          <t>01082736745</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>51662</t>
+          <t>304415</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>EDM_0126_bestreview</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_2706830356</t>
+          <t>tjsgksrlf123</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01020264590</t>
+          <t>01033775889</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>303409</t>
+          <t>51662</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>EDM_0402</t>
+          <t>EDM_0126_bestreview</t>
         </is>
       </c>
     </row>
@@ -2051,17 +2051,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>boxyogo</t>
+          <t>kk_4846360933</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01047175275</t>
+          <t>01037341293</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>294173</t>
+          <t>304445</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2071,34 +2071,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4845508185</t>
+          <t>frankseo</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01082736745</t>
+          <t>01073890799</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>304415</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -2132,71 +2132,71 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>jsy90</t>
+          <t>kk_4846754659</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01055153689</t>
+          <t>01091349747</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>304378</t>
+          <t>304463</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4846360933</t>
+          <t>kk_4845257177</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01037341293</t>
+          <t>01034081789</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>304445</t>
+          <t>304403</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>frankseo</t>
+          <t>kk_4846296264</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01073890799</t>
+          <t>01057718259</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>10630</t>
+          <t>304444</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2206,24 +2206,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4846296264</t>
+          <t>anirim</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01057718259</t>
+          <t>01026146239</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>304444</t>
+          <t>303897</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2233,105 +2233,105 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>anirim</t>
+          <t>kk_4845481797</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01026146239</t>
+          <t>01056670020</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>303897</t>
+          <t>304414</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>jjunghaha</t>
+          <t>ljsjsy</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01053895722</t>
+          <t>01047759562</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>17630</t>
+          <t>292623</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4846754659</t>
+          <t>kk_4502849451</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01091349747</t>
+          <t>01057550515</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>304463</t>
+          <t>285306</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4845257177</t>
+          <t>santastic</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01034081789</t>
+          <t>01064117065</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>304403</t>
+          <t>304410</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2348,17 +2348,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4502849451</t>
+          <t>yong9021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01057550515</t>
+          <t>01091453429</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>285306</t>
+          <t>178559</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2368,51 +2368,51 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_2860000961</t>
+          <t>kk_4845728411</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01086061074</t>
+          <t>01041347851</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>213449</t>
+          <t>304427</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4804517522</t>
+          <t>kk_4842910098</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01027141942</t>
+          <t>01091798172</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>302419</t>
+          <t>304259</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2422,132 +2422,132 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4845481797</t>
+          <t>jsy90</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01056670020</t>
+          <t>01055153689</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>304414</t>
+          <t>304378</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410pants2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>santastic</t>
+          <t>kk_4006977661</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01064117065</t>
+          <t>01027938030</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>304410</t>
+          <t>271755</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_4845889920</t>
+          <t>kk_3623213220</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01041965899</t>
+          <t>01065959020</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>304430</t>
+          <t>247746</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4750424051</t>
+          <t>kk_3788170304</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01064958365</t>
+          <t>01071502244</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>300863</t>
+          <t>256604</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>260210_Konos</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4842910098</t>
+          <t>kk_4837577772</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01091798172</t>
+          <t>01084837878</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>304259</t>
+          <t>303999</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
@@ -2591,98 +2591,98 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4837400672</t>
+          <t>kk_4520177358</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01093667007</t>
+          <t>01039211233</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>303984</t>
+          <t>286186</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ljsjsy</t>
+          <t>jjunghaha</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01047759562</t>
+          <t>01053895722</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>292623</t>
+          <t>17630</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4504731355</t>
+          <t>kk_4804517522</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01030391478</t>
+          <t>01027141942</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>285364</t>
+          <t>302419</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>EDM_0209_LIGHTBAG</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_2881959901</t>
+          <t>kk_4845889920</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01065516593</t>
+          <t>01041965899</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>214614</t>
+          <t>304430</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2699,152 +2699,152 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>yong9021</t>
+          <t>kk_4750424051</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01091453429</t>
+          <t>01064958365</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>178559</t>
+          <t>300863</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>260210_Konos</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>aijene</t>
+          <t>kk_4845276986</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01024942984</t>
+          <t>01099470418</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>43582</t>
+          <t>304404</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4837577772</t>
+          <t>smapumki</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01084837878</t>
+          <t>01091110988</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>303999</t>
+          <t>51742</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4845276986</t>
+          <t>kk_4504731355</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01099470418</t>
+          <t>01030391478</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>304404</t>
+          <t>285364</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EDM_0209_LIGHTBAG</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>smapumki</t>
+          <t>kk_2794135395</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01091110988</t>
+          <t>01094224624</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>51742</t>
+          <t>210420</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6941110100332</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4845728411</t>
+          <t>abril80</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01041347851</t>
+          <t>01032942835</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>304427</t>
+          <t>192610</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2861,17 +2861,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4845555835</t>
+          <t>kang481127</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01032274369</t>
+          <t>01053764012</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>304418</t>
+          <t>304276</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2888,179 +2888,179 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>dohyunahn</t>
+          <t>wodl8077</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01038817179</t>
+          <t>01097558077</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>304469</t>
+          <t>144037</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4715265153</t>
+          <t>kk_3210379887</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01077714623</t>
+          <t>01024748405</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>297043</t>
+          <t>231651</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4006977661</t>
+          <t>kk_4469973568</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01027938030</t>
+          <t>01087158602</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>271755</t>
+          <t>283741</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_2794135395</t>
+          <t>swonh77</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01094224624</t>
+          <t>01083828396</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>210420</t>
+          <t>295604</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>tandjh</t>
+          <t>kk_4715265153</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01030676796</t>
+          <t>01077714623</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>59328</t>
+          <t>297043</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>abckk3390</t>
+          <t>twinswoo</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01062023390</t>
+          <t>01056545433</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>71493</t>
+          <t>208155</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_2800477789</t>
+          <t>kk_2706830356</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01035177105</t>
+          <t>01020264590</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>211095</t>
+          <t>303409</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3070,24 +3070,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0402</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_2860000961</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01086061074</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>213449</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3097,159 +3097,159 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kang481127</t>
+          <t>kk_4837400672</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01053764012</t>
+          <t>01093667007</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>304276</t>
+          <t>303984</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>aumteail</t>
+          <t>kk_2881959901</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01065702230</t>
+          <t>01065516593</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>261499</t>
+          <t>214614</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>abril80</t>
+          <t>aijene</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01032942835</t>
+          <t>01024942984</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>192610</t>
+          <t>43582</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_3623213220</t>
+          <t>kk_4845555835</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01065959020</t>
+          <t>01032274369</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>247746</t>
+          <t>304418</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4846692829</t>
+          <t>dohyunahn</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01023649887</t>
+          <t>01038817179</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>304457</t>
+          <t>304469</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4846749411</t>
+          <t>tandjh</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01031226749</t>
+          <t>01030676796</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>304462</t>
+          <t>59328</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3266,152 +3266,152 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_3788170304</t>
+          <t>abckk3390</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01071502244</t>
+          <t>01062023390</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>256604</t>
+          <t>71493</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4651201605</t>
+          <t>kk_2800477789</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01045489411</t>
+          <t>01035177105</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>293053</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>willper</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01085343440</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4846761310</t>
+          <t>aumteail</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01091189951</t>
+          <t>01065702230</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>304464</t>
+          <t>261499</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>kk_4846749411</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01031226749</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>304462</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>kk_4846692829</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01023649887</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>304457</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3428,44 +3428,44 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>willper</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01085343440</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>304408</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>wodl8077</t>
+          <t>kk_4846761310</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01097558077</t>
+          <t>01091189951</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>144037</t>
+          <t>304464</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3475,34 +3475,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>chpuss74</t>
+          <t>kk_4651201605</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01035361091</t>
+          <t>01045489411</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>154462</t>
+          <t>293053</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -3536,27 +3536,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -3590,17 +3590,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_3343508579</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01062563328</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>239234</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3617,44 +3617,44 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4469973568</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01087158602</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>283741</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_3210379887</t>
+          <t>chpuss74</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01024748405</t>
+          <t>01035361091</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>231651</t>
+          <t>154462</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3671,17 +3671,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>swonh77</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01083828396</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>295604</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3698,27 +3698,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>twinswoo</t>
+          <t>kk_3343508579</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01056545433</t>
+          <t>01062563328</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>208155</t>
+          <t>239234</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -2834,17 +2834,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>abril80</t>
+          <t>kang481127</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01032942835</t>
+          <t>01053764012</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>192610</t>
+          <t>304276</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2861,17 +2861,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kang481127</t>
+          <t>abril80</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01053764012</t>
+          <t>01032942835</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>304276</t>
+          <t>192610</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3293,54 +3293,54 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_2800477789</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01035177105</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>211095</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_2800477789</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01035177105</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -3509,17 +3509,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_3183517395</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01082019936</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>228501</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3536,44 +3536,44 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3617,27 +3617,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -3671,17 +3671,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -2834,17 +2834,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kang481127</t>
+          <t>abril80</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01053764012</t>
+          <t>01032942835</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>304276</t>
+          <t>192610</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2861,17 +2861,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>abril80</t>
+          <t>kang481127</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01032942835</t>
+          <t>01053764012</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>192610</t>
+          <t>304276</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3293,54 +3293,54 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_2800477789</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01035177105</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_2800477789</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01035177105</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>211095</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -3428,27 +3428,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>willper</t>
+          <t>kk_4651201605</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01085343440</t>
+          <t>01045489411</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>293053</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -3482,44 +3482,44 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4651201605</t>
+          <t>willper</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01045489411</t>
+          <t>01085343440</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>293053</t>
+          <t>304408</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3536,17 +3536,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3563,125 +3563,125 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>chpuss74</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01035361091</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>154462</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_3183517395</t>
+          <t>chpuss74</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01082019936</t>
+          <t>01035361091</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>228501</t>
+          <t>154462</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -3455,17 +3455,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4846761310</t>
+          <t>willper</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01091189951</t>
+          <t>01085343440</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>304464</t>
+          <t>304408</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3482,17 +3482,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>willper</t>
+          <t>kk_4846761310</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01085343440</t>
+          <t>01091189951</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>304464</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3509,44 +3509,44 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3563,27 +3563,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -3617,54 +3617,54 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_3183517395</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01082019936</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>228501</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_non_buyer.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -728,17 +728,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_4806290091</t>
+          <t>seopme</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01042848444</t>
+          <t>01074122238</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>302466</t>
+          <t>304125</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -748,132 +748,132 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>seopme</t>
+          <t>kk_3186253524</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01074122238</t>
+          <t>01020132166</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>304125</t>
+          <t>230229</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0406</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kk_3186253524</t>
+          <t>kk_3672780564</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01020132166</t>
+          <t>01089459294</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>230229</t>
+          <t>250138</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EDM_0406</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kk_3672780564</t>
+          <t>jalove3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01089459294</t>
+          <t>01090657762</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>250138</t>
+          <t>168971</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>jalove3</t>
+          <t>ryukw0604</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01090657762</t>
+          <t>01037512203</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>168971</t>
+          <t>131147</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ryukw0604</t>
+          <t>kk_3803973742</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01037512203</t>
+          <t>01062581642</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>131147</t>
+          <t>259682</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -883,24 +883,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_3803973742</t>
+          <t>sas159</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01062581642</t>
+          <t>01041922755</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>259682</t>
+          <t>188959</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -917,17 +917,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sas159</t>
+          <t>kk_3182623010</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01041922755</t>
+          <t>01094128645</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>188959</t>
+          <t>227908</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -937,51 +937,51 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_3182623010</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01094128645</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>227908</t>
+          <t>276079</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_4293591148</t>
+          <t>pak652</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01086489252</t>
+          <t>01022458173</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>276079</t>
+          <t>280384</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -998,98 +998,98 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pak652</t>
+          <t>kk_4846905948</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01022458173</t>
+          <t>01099121650</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>280384</t>
+          <t>304473</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4846905948</t>
+          <t>kk_3672642114</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01099121650</t>
+          <t>01093597232</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>304473</t>
+          <t>250133</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_4846613084</t>
+          <t>sangdori76</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01079413983</t>
+          <t>01088651421</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>304453</t>
+          <t>248370</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_3672642114</t>
+          <t>gywjd8404</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01093597232</t>
+          <t>01048642364</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>250133</t>
+          <t>131135</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sangdori76</t>
+          <t>seonghyeon20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01088651421</t>
+          <t>01088283643</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>248370</t>
+          <t>204875</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1126,78 +1126,78 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gywjd8404</t>
+          <t>kk_3795703816</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01048642364</t>
+          <t>01040850174</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>131135</t>
+          <t>257699</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>seonghyeon20</t>
+          <t>kk_3745509137</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01088283643</t>
+          <t>01094130627</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>204875</t>
+          <t>253905</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4845099354</t>
+          <t>kk_4845411058</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01030334936</t>
+          <t>01032450700</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>304390</t>
+          <t>304413</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1214,17 +1214,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_3955959787</t>
+          <t>kk_4846153585</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01087702143</t>
+          <t>01071602706</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>270178</t>
+          <t>304439</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1234,132 +1234,132 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_3795703816</t>
+          <t>kk_4846007316</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01040850174</t>
+          <t>01028293928</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>257699</t>
+          <t>304431</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>120245973565650440</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_3745509137</t>
+          <t>hy1453</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01094130627</t>
+          <t>01064627675</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>253905</t>
+          <t>226545</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410pants1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>doremige</t>
+          <t>dpfmxkdl</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01083505612</t>
+          <t>01023221625</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>304450</t>
+          <t>158745</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_4845411058</t>
+          <t>kk_4846796027</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01032450700</t>
+          <t>01052779751</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>304413</t>
+          <t>304467</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4846153585</t>
+          <t>w14721</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01071602706</t>
+          <t>01091085401</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>304439</t>
+          <t>262190</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1369,132 +1369,132 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_4846007316</t>
+          <t>kk_4845228879</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01028293928</t>
+          <t>01084451479</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>304431</t>
+          <t>304399</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>hy1453</t>
+          <t>kk_3798348150</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01064627675</t>
+          <t>01020250324</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>226545</t>
+          <t>258390</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dpfmxkdl</t>
+          <t>nmstway</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01023221625</t>
+          <t>01093823995</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>158745</t>
+          <t>304455</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_4846796027</t>
+          <t>kk_4846234119</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01052779751</t>
+          <t>01049167784</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>304467</t>
+          <t>304442</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>w14721</t>
+          <t>kk_4846778806</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01091085401</t>
+          <t>01040473668</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>262190</t>
+          <t>304466</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1504,24 +1504,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4845228879</t>
+          <t>kk_3338448571</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01084451479</t>
+          <t>01050068417</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>304399</t>
+          <t>239011</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1531,24 +1531,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_3798348150</t>
+          <t>charismasm74</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01020250324</t>
+          <t>01093438775</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>258390</t>
+          <t>303650</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1558,51 +1558,51 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>nmstway</t>
+          <t>kk_4845121902</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01093823995</t>
+          <t>01063826114</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>304455</t>
+          <t>304394</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4846234119</t>
+          <t>kk_3846547859</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01049167784</t>
+          <t>01055056387</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>304442</t>
+          <t>264802</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1619,44 +1619,44 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4846778806</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01040473668</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>304466</t>
+          <t>244625</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_3338448571</t>
+          <t>kk_3821281618</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01050068417</t>
+          <t>01088952813</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>239011</t>
+          <t>262770</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1666,105 +1666,105 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>charismasm74</t>
+          <t>kk_2804147495</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01093438775</t>
+          <t>01046206130</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>303650</t>
+          <t>211367</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_4845121902</t>
+          <t>sughg</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01063826114</t>
+          <t>01066321444</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>304394</t>
+          <t>189932</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_3846547859</t>
+          <t>kk_4846078636</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01055056387</t>
+          <t>01099000411</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>264802</t>
+          <t>304434</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>ektlrksek</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01092231103</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>244625</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1774,159 +1774,159 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_3821281618</t>
+          <t>cseeun</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01088952813</t>
+          <t>01052533925</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>262770</t>
+          <t>171213</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_2804147495</t>
+          <t>boxyogo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01046206130</t>
+          <t>01047175275</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>211367</t>
+          <t>294173</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>sughg</t>
+          <t>kk_4845508185</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01066321444</t>
+          <t>01082736745</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>189932</t>
+          <t>304415</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4846078636</t>
+          <t>kkhgreen</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01099000411</t>
+          <t>01092780969</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>304434</t>
+          <t>256221</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ektlrksek</t>
+          <t>kk_4846360933</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01092231103</t>
+          <t>01037341293</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>304445</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>cseeun</t>
+          <t>frankseo</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01052533925</t>
+          <t>01073890799</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>171213</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1936,132 +1936,132 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>boxyogo</t>
+          <t>kk_4843461412</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01047175275</t>
+          <t>01026434270</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>294173</t>
+          <t>304316</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_4845508185</t>
+          <t>kk_4846754659</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01082736745</t>
+          <t>01091349747</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>304415</t>
+          <t>304463</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>tjsgksrlf123</t>
+          <t>kk_4845257177</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01033775889</t>
+          <t>01034081789</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51662</t>
+          <t>304403</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>EDM_0126_bestreview</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kkhgreen</t>
+          <t>kk_4846296264</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01092780969</t>
+          <t>01057718259</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>256221</t>
+          <t>304444</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4846360933</t>
+          <t>anirim</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01037341293</t>
+          <t>01026146239</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>304445</t>
+          <t>303897</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>frankseo</t>
+          <t>kk_4845481797</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01073890799</t>
+          <t>01056670020</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>10630</t>
+          <t>304414</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2098,213 +2098,213 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4843461412</t>
+          <t>ljsjsy</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01026434270</t>
+          <t>01047759562</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>304316</t>
+          <t>292623</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4846754659</t>
+          <t>kk_4502849451</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01091349747</t>
+          <t>01057550515</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>304463</t>
+          <t>285306</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4845257177</t>
+          <t>santastic</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01034081789</t>
+          <t>01064117065</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>304403</t>
+          <t>304410</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4846296264</t>
+          <t>yong9021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01057718259</t>
+          <t>01091453429</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>304444</t>
+          <t>178559</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>anirim</t>
+          <t>kk_4845728411</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01026146239</t>
+          <t>01041347851</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>303897</t>
+          <t>304427</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4845481797</t>
+          <t>kk_4842910098</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01056670020</t>
+          <t>01091798172</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>304414</t>
+          <t>304259</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naversa_mo</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ljsjsy</t>
+          <t>kk_4006977661</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01047759562</t>
+          <t>01027938030</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>292623</t>
+          <t>271755</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4502849451</t>
+          <t>kk_3623213220</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01057550515</t>
+          <t>01065959020</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>285306</t>
+          <t>247746</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2314,105 +2314,105 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>santastic</t>
+          <t>kk_3788170304</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01064117065</t>
+          <t>01071502244</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>304410</t>
+          <t>256604</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>yong9021</t>
+          <t>kk_4837577772</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01091453429</t>
+          <t>01084837878</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>178559</t>
+          <t>303999</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4845728411</t>
+          <t>kk_4845023359</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01041347851</t>
+          <t>01020760617</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>304427</t>
+          <t>304387</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4842910098</t>
+          <t>kk_4520177358</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01091798172</t>
+          <t>01039211233</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>304259</t>
+          <t>286186</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2422,24 +2422,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>jsy90</t>
+          <t>jjunghaha</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01055153689</t>
+          <t>01053895722</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>304378</t>
+          <t>17630</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2449,24 +2449,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410pants2</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4006977661</t>
+          <t>kk_4804517522</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01027938030</t>
+          <t>01027141942</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>271755</t>
+          <t>302419</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2476,402 +2476,402 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>da</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_3623213220</t>
+          <t>kk_4845889920</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01065959020</t>
+          <t>01041965899</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>247746</t>
+          <t>304430</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_3788170304</t>
+          <t>kk_4750424051</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01071502244</t>
+          <t>01064958365</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>256604</t>
+          <t>300863</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>260210_Konos</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4837577772</t>
+          <t>kk_4845276986</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01084837878</t>
+          <t>01099470418</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>303999</t>
+          <t>304404</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4845023359</t>
+          <t>smapumki</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01020760617</t>
+          <t>01091110988</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>304387</t>
+          <t>51742</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4520177358</t>
+          <t>kk_4504731355</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01039211233</t>
+          <t>01030391478</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>286186</t>
+          <t>285364</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EDM_0209_LIGHTBAG</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>jjunghaha</t>
+          <t>kk_2794135395</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01053895722</t>
+          <t>01094224624</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>17630</t>
+          <t>210420</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6941110100332</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4804517522</t>
+          <t>abril80</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01027141942</t>
+          <t>01032942835</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>302419</t>
+          <t>192610</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4845889920</t>
+          <t>kang481127</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01041965899</t>
+          <t>01053764012</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>304430</t>
+          <t>304276</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_NEWMEMBER</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4750424051</t>
+          <t>kk_4469973568</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01064958365</t>
+          <t>01087158602</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>300863</t>
+          <t>283741</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>260210_Konos</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_4845276986</t>
+          <t>kk_3210379887</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01099470418</t>
+          <t>01024748405</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>304404</t>
+          <t>231651</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>smapumki</t>
+          <t>kk_4715265153</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01091110988</t>
+          <t>01077714623</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>51742</t>
+          <t>297043</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4504731355</t>
+          <t>twinswoo</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01030391478</t>
+          <t>01056545433</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>285364</t>
+          <t>208155</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>EDM_0209_LIGHTBAG</t>
+          <t>maintitle</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_2794135395</t>
+          <t>kk_2706830356</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01094224624</t>
+          <t>01020264590</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>210420</t>
+          <t>303409</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>6941110100332</t>
+          <t>EDM_0402</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>abril80</t>
+          <t>kk_2860000961</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01032942835</t>
+          <t>01086061074</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>192610</t>
+          <t>213449</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kang481127</t>
+          <t>kk_4837400672</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01053764012</t>
+          <t>01093667007</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>304276</t>
+          <t>303984</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2888,17 +2888,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>wodl8077</t>
+          <t>kk_2881959901</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01097558077</t>
+          <t>01065516593</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>144037</t>
+          <t>214614</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2908,159 +2908,159 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_3210379887</t>
+          <t>aijene</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01024748405</t>
+          <t>01024942984</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>231651</t>
+          <t>43582</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4469973568</t>
+          <t>kk_4845555835</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01087158602</t>
+          <t>01032274369</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>283741</t>
+          <t>304418</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>swonh77</t>
+          <t>dohyunahn</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01083828396</t>
+          <t>01038817179</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>295604</t>
+          <t>304469</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4715265153</t>
+          <t>tandjh</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01077714623</t>
+          <t>01030676796</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>297043</t>
+          <t>59328</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>twinswoo</t>
+          <t>abckk3390</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01056545433</t>
+          <t>01062023390</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>208155</t>
+          <t>71493</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_2706830356</t>
+          <t>kk_2800477789</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01020264590</t>
+          <t>01035177105</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>303409</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3070,24 +3070,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>EDM_0402</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_2860000961</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01086061074</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>213449</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3097,655 +3097,412 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4837400672</t>
+          <t>aumteail</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01093667007</t>
+          <t>01065702230</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>303984</t>
+          <t>261499</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_2881959901</t>
+          <t>kk_4846749411</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01065516593</t>
+          <t>01031226749</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>214614</t>
+          <t>304462</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>aijene</t>
+          <t>kk_4846692829</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01024942984</t>
+          <t>01023649887</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>43582</t>
+          <t>304457</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4845555835</t>
+          <t>kk_4651201605</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01032274369</t>
+          <t>01045489411</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>304418</t>
+          <t>293053</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EDM_0411</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>dohyunahn</t>
+          <t>kk_4846761310</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01038817179</t>
+          <t>01091189951</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>304469</t>
+          <t>304464</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-         